--- a/DSA/DSA-Euron-2026/codeverra - BreakthroughDSA with Python sheet.xlsx
+++ b/DSA/DSA-Euron-2026/codeverra - BreakthroughDSA with Python sheet.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Structures-Algorithms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Structures-Algorithms\DSA\DSA-Euron-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF88F887-8E6A-4586-8416-0B38FDEFBC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2F9874-4707-447C-9E28-C242134025B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Problem List" sheetId="1" r:id="rId1"/>
-    <sheet name="Blind75" sheetId="2" r:id="rId2"/>
+    <sheet name="Practice-Problems" sheetId="3" r:id="rId2"/>
+    <sheet name="Blind75" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Blind75!$A$1:$Z$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Blind75!$A$1:$Z$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Problem List'!$A$4:$Z$255</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -3456,9 +3457,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>solve by storing  the differences in a freq_dict dictionary</t>
-  </si>
-  <si>
     <t>done</t>
   </si>
   <si>
@@ -3491,6 +3489,9 @@
   </si>
   <si>
     <t>Two pointer approach with a constant space of O(1). Just start with left and right pointers, and add both and compare with the target, if target is more than current sum then increase left pointer or else decrease right pointer.</t>
+  </si>
+  <si>
+    <t>solve by calculating the differences and storing the difference with its index in "freq_dict", then move your pointer forward and find new diffference then check if the new diff is present in "freq_dict" or not. If present simply return current idx and freq dict value idx.</t>
   </si>
 </sst>
 </file>
@@ -4013,7 +4014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4084,8 +4085,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4157,8 +4156,9 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4387,14 +4387,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -4495,14 +4495,14 @@
       <c r="F4" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="I4" s="92" t="s">
-        <v>568</v>
+      <c r="I4" s="90" t="s">
+        <v>567</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -4523,32 +4523,32 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="13.8">
-      <c r="A5" s="45">
+      <c r="A5" s="43">
         <v>1</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="46" t="s">
+        <v>571</v>
+      </c>
+      <c r="F5" s="47" t="s">
         <v>565</v>
       </c>
-      <c r="F5" s="49" t="s">
-        <v>566</v>
-      </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="93">
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="91">
         <v>1</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -4565,32 +4565,32 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="13.8">
-      <c r="A6" s="45">
+      <c r="A6" s="43">
         <v>2</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="97" t="s">
+        <v>569</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="46" t="s">
         <v>570</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="99" t="s">
-        <v>571</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>566</v>
-      </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="93">
+      <c r="F6" s="47" t="s">
+        <v>565</v>
+      </c>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="91">
         <v>4</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -4607,28 +4607,28 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="13.8">
-      <c r="A7" s="45">
+      <c r="A7" s="43">
         <v>3</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="46" t="s">
         <v>564</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -4645,32 +4645,32 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="13.8">
-      <c r="A8" s="45">
+      <c r="A8" s="43">
         <v>4</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="99" t="s">
-        <v>569</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>566</v>
-      </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="93">
+      <c r="E8" s="46" t="s">
+        <v>568</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>565</v>
+      </c>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="91">
         <v>3</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -4687,32 +4687,32 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="13.8">
-      <c r="A9" s="45">
+      <c r="A9" s="43">
         <v>5</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="46" t="s">
-        <v>567</v>
-      </c>
-      <c r="F9" s="51" t="s">
+      <c r="E9" s="44" t="s">
         <v>566</v>
       </c>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="93">
+      <c r="F9" s="49" t="s">
+        <v>565</v>
+      </c>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="91">
         <v>2</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -4729,26 +4729,26 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="13.8">
-      <c r="A10" s="45">
+      <c r="A10" s="43">
         <v>6</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -4765,24 +4765,24 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="13.8">
-      <c r="A11" s="45">
+      <c r="A11" s="43">
         <v>7</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4799,26 +4799,26 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="13.8">
-      <c r="A12" s="45">
+      <c r="A12" s="43">
         <v>8</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -4835,24 +4835,24 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="13.8">
-      <c r="A13" s="45">
+      <c r="A13" s="43">
         <v>9</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -4869,26 +4869,26 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="13.8">
-      <c r="A14" s="45">
+      <c r="A14" s="43">
         <v>10</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4905,24 +4905,24 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="13.8">
-      <c r="A15" s="45">
+      <c r="A15" s="43">
         <v>11</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -4939,26 +4939,26 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26" ht="13.8">
-      <c r="A16" s="45">
+      <c r="A16" s="43">
         <v>12</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4975,24 +4975,24 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" spans="1:26" ht="13.8">
-      <c r="A17" s="45">
+      <c r="A17" s="43">
         <v>13</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -5009,24 +5009,24 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26" ht="13.8">
-      <c r="A18" s="45">
+      <c r="A18" s="43">
         <v>14</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -5043,24 +5043,24 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" spans="1:26" ht="13.8">
-      <c r="A19" s="45">
+      <c r="A19" s="43">
         <v>15</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -5077,24 +5077,24 @@
       <c r="Z19" s="6"/>
     </row>
     <row r="20" spans="1:26" ht="13.8">
-      <c r="A20" s="45">
+      <c r="A20" s="43">
         <v>16</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5111,26 +5111,26 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21" spans="1:26" ht="13.8">
-      <c r="A21" s="45">
+      <c r="A21" s="43">
         <v>17</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5147,24 +5147,24 @@
       <c r="Z21" s="2"/>
     </row>
     <row r="22" spans="1:26" ht="13.8">
-      <c r="A22" s="45">
+      <c r="A22" s="43">
         <v>18</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5181,24 +5181,24 @@
       <c r="Z22" s="2"/>
     </row>
     <row r="23" spans="1:26" ht="13.8">
-      <c r="A23" s="45">
+      <c r="A23" s="43">
         <v>19</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5215,24 +5215,24 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="13.8">
-      <c r="A24" s="45">
+      <c r="A24" s="43">
         <v>20</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
@@ -5249,24 +5249,24 @@
       <c r="Z24" s="6"/>
     </row>
     <row r="25" spans="1:26" ht="13.8">
-      <c r="A25" s="45">
+      <c r="A25" s="43">
         <v>21</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5283,24 +5283,24 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" spans="1:26" ht="13.8">
-      <c r="A26" s="45">
+      <c r="A26" s="43">
         <v>22</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5317,24 +5317,24 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" spans="1:26" ht="13.8">
-      <c r="A27" s="45">
+      <c r="A27" s="43">
         <v>23</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5351,24 +5351,24 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="13.8">
-      <c r="A28" s="45">
+      <c r="A28" s="43">
         <v>24</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5385,24 +5385,24 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" spans="1:26" ht="13.8">
-      <c r="A29" s="45">
+      <c r="A29" s="43">
         <v>25</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5419,24 +5419,24 @@
       <c r="Z29" s="2"/>
     </row>
     <row r="30" spans="1:26" ht="13.8">
-      <c r="A30" s="45">
+      <c r="A30" s="43">
         <v>26</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="93"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5453,26 +5453,26 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" spans="1:26" ht="13.8">
-      <c r="A31" s="45">
+      <c r="A31" s="43">
         <v>27</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5489,24 +5489,24 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" spans="1:26" ht="13.8">
-      <c r="A32" s="45">
+      <c r="A32" s="43">
         <v>28</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="65" t="s">
+      <c r="C32" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5523,24 +5523,24 @@
       <c r="Z32" s="2"/>
     </row>
     <row r="33" spans="1:26" ht="13.8">
-      <c r="A33" s="45">
+      <c r="A33" s="43">
         <v>29</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="55"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="55"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -5557,24 +5557,24 @@
       <c r="Z33" s="6"/>
     </row>
     <row r="34" spans="1:26" ht="13.8">
-      <c r="A34" s="45">
+      <c r="A34" s="43">
         <v>30</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5591,24 +5591,24 @@
       <c r="Z34" s="2"/>
     </row>
     <row r="35" spans="1:26" ht="13.8">
-      <c r="A35" s="45">
+      <c r="A35" s="43">
         <v>31</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="91"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
+      <c r="L35" s="44"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5625,24 +5625,24 @@
       <c r="Z35" s="2"/>
     </row>
     <row r="36" spans="1:26" ht="13.8">
-      <c r="A36" s="45">
+      <c r="A36" s="43">
         <v>32</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="65" t="s">
+      <c r="C36" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
+      <c r="L36" s="44"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5659,24 +5659,24 @@
       <c r="Z36" s="2"/>
     </row>
     <row r="37" spans="1:26" ht="13.8">
-      <c r="A37" s="45">
+      <c r="A37" s="43">
         <v>33</v>
       </c>
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="91"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5693,24 +5693,24 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" spans="1:26" ht="13.8">
-      <c r="A38" s="45">
+      <c r="A38" s="43">
         <v>34</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5727,24 +5727,24 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" spans="1:26" ht="13.8">
-      <c r="A39" s="45">
+      <c r="A39" s="43">
         <v>35</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5761,26 +5761,26 @@
       <c r="Z39" s="2"/>
     </row>
     <row r="40" spans="1:26" ht="13.8">
-      <c r="A40" s="45">
+      <c r="A40" s="43">
         <v>36</v>
       </c>
-      <c r="B40" s="46" t="s">
+      <c r="B40" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="67" t="s">
+      <c r="C40" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="D40" s="46" t="s">
+      <c r="D40" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="44"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5797,24 +5797,24 @@
       <c r="Z40" s="2"/>
     </row>
     <row r="41" spans="1:26" ht="13.8">
-      <c r="A41" s="45">
+      <c r="A41" s="43">
         <v>37</v>
       </c>
-      <c r="B41" s="46" t="s">
+      <c r="B41" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="44"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5831,24 +5831,24 @@
       <c r="Z41" s="2"/>
     </row>
     <row r="42" spans="1:26" ht="15.6">
-      <c r="A42" s="45">
+      <c r="A42" s="43">
         <v>38</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46"/>
-      <c r="I42" s="93"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="91"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="44"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5865,24 +5865,24 @@
       <c r="Z42" s="2"/>
     </row>
     <row r="43" spans="1:26" ht="15.6">
-      <c r="A43" s="45">
+      <c r="A43" s="43">
         <v>39</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="93"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="91"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="44"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5899,24 +5899,24 @@
       <c r="Z43" s="2"/>
     </row>
     <row r="44" spans="1:26" ht="15.6">
-      <c r="A44" s="45">
+      <c r="A44" s="43">
         <v>40</v>
       </c>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="93"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="91"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="44"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5933,26 +5933,26 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" spans="1:26" ht="13.8">
-      <c r="A45" s="45">
+      <c r="A45" s="43">
         <v>41</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="46" t="s">
+      <c r="D45" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="93"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="91"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5969,26 +5969,26 @@
       <c r="Z45" s="2"/>
     </row>
     <row r="46" spans="1:26" ht="13.8">
-      <c r="A46" s="45">
+      <c r="A46" s="43">
         <v>42</v>
       </c>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="59" t="s">
+      <c r="C46" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="46" t="s">
+      <c r="D46" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="95"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
-      <c r="L46" s="69"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="93"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -6005,26 +6005,26 @@
       <c r="Z46" s="7"/>
     </row>
     <row r="47" spans="1:26" ht="13.8">
-      <c r="A47" s="45">
+      <c r="A47" s="43">
         <v>43</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="46" t="s">
+      <c r="D47" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="93"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6041,24 +6041,24 @@
       <c r="Z47" s="2"/>
     </row>
     <row r="48" spans="1:26" ht="13.8">
-      <c r="A48" s="45">
+      <c r="A48" s="43">
         <v>44</v>
       </c>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="59" t="s">
+      <c r="C48" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="94"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
-      <c r="L48" s="55"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="92"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="53"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
@@ -6075,24 +6075,24 @@
       <c r="Z48" s="6"/>
     </row>
     <row r="49" spans="1:26" ht="13.8">
-      <c r="A49" s="45">
+      <c r="A49" s="43">
         <v>45</v>
       </c>
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C49" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="93"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6109,24 +6109,24 @@
       <c r="Z49" s="2"/>
     </row>
     <row r="50" spans="1:26" ht="13.8">
-      <c r="A50" s="45">
+      <c r="A50" s="43">
         <v>46</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="93"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="91"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="44"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6143,26 +6143,26 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51" spans="1:26" ht="13.8">
-      <c r="A51" s="45">
+      <c r="A51" s="43">
         <v>47</v>
       </c>
-      <c r="B51" s="46" t="s">
+      <c r="B51" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="46" t="s">
+      <c r="D51" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="93"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="91"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="44"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6179,24 +6179,24 @@
       <c r="Z51" s="2"/>
     </row>
     <row r="52" spans="1:26" ht="13.8">
-      <c r="A52" s="45">
+      <c r="A52" s="43">
         <v>48</v>
       </c>
-      <c r="B52" s="46" t="s">
+      <c r="B52" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="93"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="46"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="91"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="44"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6213,24 +6213,24 @@
       <c r="Z52" s="2"/>
     </row>
     <row r="53" spans="1:26" ht="13.8">
-      <c r="A53" s="45">
+      <c r="A53" s="43">
         <v>49</v>
       </c>
-      <c r="B53" s="70" t="s">
+      <c r="B53" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="C53" s="71" t="s">
+      <c r="C53" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="96"/>
-      <c r="J53" s="70"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="70"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
+      <c r="H53" s="68"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="68"/>
+      <c r="K53" s="68"/>
+      <c r="L53" s="68"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
@@ -6247,24 +6247,24 @@
       <c r="Z53" s="8"/>
     </row>
     <row r="54" spans="1:26" ht="13.8">
-      <c r="A54" s="45">
+      <c r="A54" s="43">
         <v>50</v>
       </c>
-      <c r="B54" s="46" t="s">
+      <c r="B54" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="93"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="91"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="44"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6281,26 +6281,26 @@
       <c r="Z54" s="2"/>
     </row>
     <row r="55" spans="1:26" ht="13.8">
-      <c r="A55" s="45">
+      <c r="A55" s="43">
         <v>51</v>
       </c>
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="65" t="s">
+      <c r="C55" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="46" t="s">
+      <c r="D55" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="93"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="46"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="44"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6317,24 +6317,24 @@
       <c r="Z55" s="2"/>
     </row>
     <row r="56" spans="1:26" ht="13.8">
-      <c r="A56" s="45">
+      <c r="A56" s="43">
         <v>52</v>
       </c>
-      <c r="B56" s="46" t="s">
+      <c r="B56" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="65" t="s">
+      <c r="C56" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="93"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="91"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6351,26 +6351,26 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57" spans="1:26" ht="13.8">
-      <c r="A57" s="45">
+      <c r="A57" s="43">
         <v>53</v>
       </c>
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="93"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="91"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="44"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6387,24 +6387,24 @@
       <c r="Z57" s="2"/>
     </row>
     <row r="58" spans="1:26" ht="13.8">
-      <c r="A58" s="45">
+      <c r="A58" s="43">
         <v>54</v>
       </c>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C58" s="58" t="s">
+      <c r="C58" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="46"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="44"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -6421,24 +6421,24 @@
       <c r="Z58" s="2"/>
     </row>
     <row r="59" spans="1:26" ht="13.8">
-      <c r="A59" s="45">
+      <c r="A59" s="43">
         <v>55</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="65" t="s">
+      <c r="C59" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="93"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
-      <c r="L59" s="46"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="91"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="44"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -6455,24 +6455,24 @@
       <c r="Z59" s="2"/>
     </row>
     <row r="60" spans="1:26" ht="13.8">
-      <c r="A60" s="45">
+      <c r="A60" s="43">
         <v>56</v>
       </c>
-      <c r="B60" s="46" t="s">
+      <c r="B60" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="58" t="s">
+      <c r="C60" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="93"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="91"/>
+      <c r="J60" s="44"/>
+      <c r="K60" s="44"/>
+      <c r="L60" s="44"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -6489,24 +6489,24 @@
       <c r="Z60" s="2"/>
     </row>
     <row r="61" spans="1:26" ht="13.8">
-      <c r="A61" s="45">
+      <c r="A61" s="43">
         <v>57</v>
       </c>
-      <c r="B61" s="46" t="s">
+      <c r="B61" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C61" s="58" t="s">
+      <c r="C61" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="91"/>
+      <c r="J61" s="44"/>
+      <c r="K61" s="44"/>
+      <c r="L61" s="44"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -6523,24 +6523,24 @@
       <c r="Z61" s="2"/>
     </row>
     <row r="62" spans="1:26" ht="13.8">
-      <c r="A62" s="45">
+      <c r="A62" s="43">
         <v>58</v>
       </c>
-      <c r="B62" s="72" t="s">
+      <c r="B62" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="C62" s="73" t="s">
+      <c r="C62" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="97"/>
-      <c r="J62" s="72"/>
-      <c r="K62" s="72"/>
-      <c r="L62" s="72"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
       <c r="O62" s="9"/>
@@ -6557,24 +6557,24 @@
       <c r="Z62" s="9"/>
     </row>
     <row r="63" spans="1:26" ht="13.8">
-      <c r="A63" s="45">
+      <c r="A63" s="43">
         <v>59</v>
       </c>
-      <c r="B63" s="46" t="s">
+      <c r="B63" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="58" t="s">
+      <c r="C63" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="93"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="46"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="44"/>
+      <c r="K63" s="44"/>
+      <c r="L63" s="44"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -6591,24 +6591,24 @@
       <c r="Z63" s="2"/>
     </row>
     <row r="64" spans="1:26" ht="13.8">
-      <c r="A64" s="45">
+      <c r="A64" s="43">
         <v>60</v>
       </c>
-      <c r="B64" s="46" t="s">
+      <c r="B64" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="58" t="s">
+      <c r="C64" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="93"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="91"/>
+      <c r="J64" s="44"/>
+      <c r="K64" s="44"/>
+      <c r="L64" s="44"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -6625,26 +6625,26 @@
       <c r="Z64" s="2"/>
     </row>
     <row r="65" spans="1:26" ht="13.8">
-      <c r="A65" s="45">
+      <c r="A65" s="43">
         <v>61</v>
       </c>
-      <c r="B65" s="46" t="s">
+      <c r="B65" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C65" s="58" t="s">
+      <c r="C65" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="46" t="s">
+      <c r="D65" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="93"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
-      <c r="L65" s="46"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="91"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+      <c r="L65" s="44"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -6661,26 +6661,26 @@
       <c r="Z65" s="2"/>
     </row>
     <row r="66" spans="1:26" ht="13.8">
-      <c r="A66" s="45">
+      <c r="A66" s="43">
         <v>62</v>
       </c>
-      <c r="B66" s="46" t="s">
+      <c r="B66" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C66" s="58" t="s">
+      <c r="C66" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="D66" s="46" t="s">
+      <c r="D66" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="93"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="91"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="44"/>
+      <c r="L66" s="44"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -6697,26 +6697,26 @@
       <c r="Z66" s="2"/>
     </row>
     <row r="67" spans="1:26" ht="13.8">
-      <c r="A67" s="45">
+      <c r="A67" s="43">
         <v>63</v>
       </c>
-      <c r="B67" s="46" t="s">
+      <c r="B67" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C67" s="58" t="s">
+      <c r="C67" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="46" t="s">
+      <c r="D67" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="93"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="91"/>
+      <c r="J67" s="44"/>
+      <c r="K67" s="44"/>
+      <c r="L67" s="44"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -6733,26 +6733,26 @@
       <c r="Z67" s="2"/>
     </row>
     <row r="68" spans="1:26" ht="13.8">
-      <c r="A68" s="45">
+      <c r="A68" s="43">
         <v>64</v>
       </c>
-      <c r="B68" s="46" t="s">
+      <c r="B68" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="58" t="s">
+      <c r="C68" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="D68" s="46" t="s">
+      <c r="D68" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="93"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
-      <c r="L68" s="46"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="91"/>
+      <c r="J68" s="44"/>
+      <c r="K68" s="44"/>
+      <c r="L68" s="44"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -6769,26 +6769,26 @@
       <c r="Z68" s="2"/>
     </row>
     <row r="69" spans="1:26" ht="13.8">
-      <c r="A69" s="45">
+      <c r="A69" s="43">
         <v>65</v>
       </c>
-      <c r="B69" s="46" t="s">
+      <c r="B69" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C69" s="58" t="s">
+      <c r="C69" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="D69" s="46" t="s">
+      <c r="D69" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="93"/>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
-      <c r="L69" s="46"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="44"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="91"/>
+      <c r="J69" s="44"/>
+      <c r="K69" s="44"/>
+      <c r="L69" s="44"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -6805,24 +6805,24 @@
       <c r="Z69" s="2"/>
     </row>
     <row r="70" spans="1:26" ht="13.8">
-      <c r="A70" s="45">
+      <c r="A70" s="43">
         <v>66</v>
       </c>
-      <c r="B70" s="46" t="s">
+      <c r="B70" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C70" s="58" t="s">
+      <c r="C70" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="93"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="91"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="44"/>
+      <c r="L70" s="44"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -6839,24 +6839,24 @@
       <c r="Z70" s="2"/>
     </row>
     <row r="71" spans="1:26" ht="13.8">
-      <c r="A71" s="45">
+      <c r="A71" s="43">
         <v>67</v>
       </c>
-      <c r="B71" s="46" t="s">
+      <c r="B71" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C71" s="58" t="s">
+      <c r="C71" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="93"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="91"/>
+      <c r="J71" s="44"/>
+      <c r="K71" s="44"/>
+      <c r="L71" s="44"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -6873,26 +6873,26 @@
       <c r="Z71" s="2"/>
     </row>
     <row r="72" spans="1:26" ht="13.8">
-      <c r="A72" s="45">
+      <c r="A72" s="43">
         <v>68</v>
       </c>
-      <c r="B72" s="46" t="s">
+      <c r="B72" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C72" s="71" t="s">
+      <c r="C72" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D72" s="70" t="s">
+      <c r="D72" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="70"/>
-      <c r="F72" s="70"/>
-      <c r="G72" s="70"/>
-      <c r="H72" s="70"/>
-      <c r="I72" s="96"/>
-      <c r="J72" s="70"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="70"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="68"/>
+      <c r="I72" s="94"/>
+      <c r="J72" s="68"/>
+      <c r="K72" s="68"/>
+      <c r="L72" s="68"/>
       <c r="M72" s="8"/>
       <c r="N72" s="8"/>
       <c r="O72" s="8"/>
@@ -6909,24 +6909,24 @@
       <c r="Z72" s="8"/>
     </row>
     <row r="73" spans="1:26" ht="13.8">
-      <c r="A73" s="45">
+      <c r="A73" s="43">
         <v>69</v>
       </c>
-      <c r="B73" s="46" t="s">
+      <c r="B73" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C73" s="71" t="s">
+      <c r="C73" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D73" s="70"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="70"/>
-      <c r="G73" s="70"/>
-      <c r="H73" s="70"/>
-      <c r="I73" s="96"/>
-      <c r="J73" s="70"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="70"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="94"/>
+      <c r="J73" s="68"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="68"/>
       <c r="M73" s="8"/>
       <c r="N73" s="8"/>
       <c r="O73" s="8"/>
@@ -6943,24 +6943,24 @@
       <c r="Z73" s="8"/>
     </row>
     <row r="74" spans="1:26" ht="13.8">
-      <c r="A74" s="45">
+      <c r="A74" s="43">
         <v>70</v>
       </c>
-      <c r="B74" s="46" t="s">
+      <c r="B74" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="58" t="s">
+      <c r="C74" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="93"/>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-      <c r="L74" s="46"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="44"/>
+      <c r="I74" s="91"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="44"/>
+      <c r="L74" s="44"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -6977,26 +6977,26 @@
       <c r="Z74" s="2"/>
     </row>
     <row r="75" spans="1:26" ht="13.8">
-      <c r="A75" s="45">
+      <c r="A75" s="43">
         <v>71</v>
       </c>
-      <c r="B75" s="46" t="s">
+      <c r="B75" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C75" s="58" t="s">
+      <c r="C75" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46" t="s">
+      <c r="D75" s="44"/>
+      <c r="E75" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="93"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
+      <c r="H75" s="44"/>
+      <c r="I75" s="91"/>
+      <c r="J75" s="44"/>
+      <c r="K75" s="44"/>
+      <c r="L75" s="44"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -7013,24 +7013,24 @@
       <c r="Z75" s="2"/>
     </row>
     <row r="76" spans="1:26" ht="13.8">
-      <c r="A76" s="45">
+      <c r="A76" s="43">
         <v>72</v>
       </c>
-      <c r="B76" s="46" t="s">
+      <c r="B76" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="58" t="s">
+      <c r="C76" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="93"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="46"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="91"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="44"/>
+      <c r="L76" s="44"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -7047,24 +7047,24 @@
       <c r="Z76" s="2"/>
     </row>
     <row r="77" spans="1:26" ht="13.8">
-      <c r="A77" s="45">
+      <c r="A77" s="43">
         <v>73</v>
       </c>
-      <c r="B77" s="46" t="s">
+      <c r="B77" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C77" s="58" t="s">
+      <c r="C77" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="46"/>
-      <c r="E77" s="46"/>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="93"/>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
-      <c r="L77" s="46"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="91"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
+      <c r="L77" s="44"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -7081,24 +7081,24 @@
       <c r="Z77" s="2"/>
     </row>
     <row r="78" spans="1:26" ht="13.8">
-      <c r="A78" s="45">
+      <c r="A78" s="43">
         <v>74</v>
       </c>
-      <c r="B78" s="46" t="s">
+      <c r="B78" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="58" t="s">
+      <c r="C78" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="46"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="93"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44"/>
+      <c r="H78" s="44"/>
+      <c r="I78" s="91"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="44"/>
+      <c r="L78" s="44"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -7115,24 +7115,24 @@
       <c r="Z78" s="2"/>
     </row>
     <row r="79" spans="1:26" ht="13.8">
-      <c r="A79" s="45">
+      <c r="A79" s="43">
         <v>75</v>
       </c>
-      <c r="B79" s="46" t="s">
+      <c r="B79" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C79" s="58" t="s">
+      <c r="C79" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="93"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="91"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+      <c r="L79" s="44"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -7149,24 +7149,24 @@
       <c r="Z79" s="2"/>
     </row>
     <row r="80" spans="1:26" ht="13.8">
-      <c r="A80" s="45">
+      <c r="A80" s="43">
         <v>76</v>
       </c>
-      <c r="B80" s="46" t="s">
+      <c r="B80" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="58" t="s">
+      <c r="C80" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="D80" s="46"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="93"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="44"/>
+      <c r="I80" s="91"/>
+      <c r="J80" s="44"/>
+      <c r="K80" s="44"/>
+      <c r="L80" s="44"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -7183,26 +7183,26 @@
       <c r="Z80" s="2"/>
     </row>
     <row r="81" spans="1:26" ht="13.8">
-      <c r="A81" s="45">
+      <c r="A81" s="43">
         <v>77</v>
       </c>
-      <c r="B81" s="46" t="s">
+      <c r="B81" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C81" s="58" t="s">
+      <c r="C81" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="46" t="s">
+      <c r="D81" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E81" s="46"/>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="46"/>
-      <c r="I81" s="93"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
-      <c r="L81" s="46"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
+      <c r="I81" s="91"/>
+      <c r="J81" s="44"/>
+      <c r="K81" s="44"/>
+      <c r="L81" s="44"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -7219,24 +7219,24 @@
       <c r="Z81" s="2"/>
     </row>
     <row r="82" spans="1:26" ht="13.8">
-      <c r="A82" s="45">
+      <c r="A82" s="43">
         <v>78</v>
       </c>
-      <c r="B82" s="46" t="s">
+      <c r="B82" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C82" s="58" t="s">
+      <c r="C82" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="46"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="93"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="46"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="44"/>
+      <c r="I82" s="91"/>
+      <c r="J82" s="44"/>
+      <c r="K82" s="44"/>
+      <c r="L82" s="44"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -7253,24 +7253,24 @@
       <c r="Z82" s="2"/>
     </row>
     <row r="83" spans="1:26" ht="13.8">
-      <c r="A83" s="45">
+      <c r="A83" s="43">
         <v>79</v>
       </c>
-      <c r="B83" s="46" t="s">
+      <c r="B83" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C83" s="58" t="s">
+      <c r="C83" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="46"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="93"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="91"/>
+      <c r="J83" s="44"/>
+      <c r="K83" s="44"/>
+      <c r="L83" s="44"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -7287,24 +7287,24 @@
       <c r="Z83" s="2"/>
     </row>
     <row r="84" spans="1:26" ht="13.8">
-      <c r="A84" s="45">
+      <c r="A84" s="43">
         <v>80</v>
       </c>
-      <c r="B84" s="46" t="s">
+      <c r="B84" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="58" t="s">
+      <c r="C84" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="46"/>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="93"/>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
-      <c r="L84" s="46"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="91"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+      <c r="L84" s="44"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -7321,26 +7321,26 @@
       <c r="Z84" s="2"/>
     </row>
     <row r="85" spans="1:26" ht="13.8">
-      <c r="A85" s="45">
+      <c r="A85" s="43">
         <v>81</v>
       </c>
-      <c r="B85" s="46" t="s">
+      <c r="B85" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C85" s="58" t="s">
+      <c r="C85" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="46"/>
-      <c r="E85" s="46" t="s">
+      <c r="D85" s="44"/>
+      <c r="E85" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="93"/>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-      <c r="L85" s="46"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
+      <c r="I85" s="91"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
+      <c r="L85" s="44"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -7357,24 +7357,24 @@
       <c r="Z85" s="2"/>
     </row>
     <row r="86" spans="1:26" ht="13.8">
-      <c r="A86" s="45">
+      <c r="A86" s="43">
         <v>82</v>
       </c>
-      <c r="B86" s="46" t="s">
+      <c r="B86" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C86" s="58" t="s">
+      <c r="C86" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="D86" s="46"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="93"/>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-      <c r="L86" s="46"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="91"/>
+      <c r="J86" s="44"/>
+      <c r="K86" s="44"/>
+      <c r="L86" s="44"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -7391,24 +7391,24 @@
       <c r="Z86" s="2"/>
     </row>
     <row r="87" spans="1:26" ht="13.8">
-      <c r="A87" s="45">
+      <c r="A87" s="43">
         <v>83</v>
       </c>
-      <c r="B87" s="46" t="s">
+      <c r="B87" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C87" s="58" t="s">
+      <c r="C87" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="93"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="44"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="91"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="44"/>
+      <c r="L87" s="44"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -7425,24 +7425,24 @@
       <c r="Z87" s="2"/>
     </row>
     <row r="88" spans="1:26" ht="13.8">
-      <c r="A88" s="45">
+      <c r="A88" s="43">
         <v>84</v>
       </c>
-      <c r="B88" s="46" t="s">
+      <c r="B88" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="58" t="s">
+      <c r="C88" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="93"/>
-      <c r="J88" s="46"/>
-      <c r="K88" s="46"/>
-      <c r="L88" s="46"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="44"/>
+      <c r="F88" s="44"/>
+      <c r="G88" s="44"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="91"/>
+      <c r="J88" s="44"/>
+      <c r="K88" s="44"/>
+      <c r="L88" s="44"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -7459,24 +7459,24 @@
       <c r="Z88" s="2"/>
     </row>
     <row r="89" spans="1:26" ht="13.8">
-      <c r="A89" s="45">
+      <c r="A89" s="43">
         <v>85</v>
       </c>
-      <c r="B89" s="46" t="s">
+      <c r="B89" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C89" s="58" t="s">
+      <c r="C89" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="D89" s="46"/>
-      <c r="E89" s="46"/>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
-      <c r="H89" s="46"/>
-      <c r="I89" s="93"/>
-      <c r="J89" s="46"/>
-      <c r="K89" s="46"/>
-      <c r="L89" s="46"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="44"/>
+      <c r="F89" s="44"/>
+      <c r="G89" s="44"/>
+      <c r="H89" s="44"/>
+      <c r="I89" s="91"/>
+      <c r="J89" s="44"/>
+      <c r="K89" s="44"/>
+      <c r="L89" s="44"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -7493,24 +7493,24 @@
       <c r="Z89" s="2"/>
     </row>
     <row r="90" spans="1:26" ht="13.8">
-      <c r="A90" s="45">
+      <c r="A90" s="43">
         <v>86</v>
       </c>
-      <c r="B90" s="46" t="s">
+      <c r="B90" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C90" s="74" t="s">
+      <c r="C90" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="93"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="46"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="91"/>
+      <c r="J90" s="44"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="44"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -7527,24 +7527,24 @@
       <c r="Z90" s="2"/>
     </row>
     <row r="91" spans="1:26" ht="13.8">
-      <c r="A91" s="45"/>
-      <c r="B91" s="46" t="s">
+      <c r="A91" s="43"/>
+      <c r="B91" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C91" s="75" t="s">
+      <c r="C91" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="D91" s="46" t="s">
+      <c r="D91" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="93"/>
-      <c r="J91" s="46"/>
-      <c r="K91" s="46"/>
-      <c r="L91" s="46"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="44"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="91"/>
+      <c r="J91" s="44"/>
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -7561,24 +7561,24 @@
       <c r="Z91" s="2"/>
     </row>
     <row r="92" spans="1:26" ht="13.8">
-      <c r="A92" s="45">
+      <c r="A92" s="43">
         <v>87</v>
       </c>
-      <c r="B92" s="46" t="s">
+      <c r="B92" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C92" s="65" t="s">
+      <c r="C92" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="D92" s="46"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
-      <c r="H92" s="46"/>
-      <c r="I92" s="93"/>
-      <c r="J92" s="46"/>
-      <c r="K92" s="46"/>
-      <c r="L92" s="46"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="91"/>
+      <c r="J92" s="44"/>
+      <c r="K92" s="44"/>
+      <c r="L92" s="44"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -7595,24 +7595,24 @@
       <c r="Z92" s="2"/>
     </row>
     <row r="93" spans="1:26" ht="13.8">
-      <c r="A93" s="45">
+      <c r="A93" s="43">
         <v>88</v>
       </c>
-      <c r="B93" s="46" t="s">
+      <c r="B93" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C93" s="58" t="s">
+      <c r="C93" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="D93" s="46"/>
-      <c r="E93" s="46"/>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
-      <c r="H93" s="46"/>
-      <c r="I93" s="93"/>
-      <c r="J93" s="46"/>
-      <c r="K93" s="46"/>
-      <c r="L93" s="46"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="91"/>
+      <c r="J93" s="44"/>
+      <c r="K93" s="44"/>
+      <c r="L93" s="44"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -7629,24 +7629,24 @@
       <c r="Z93" s="2"/>
     </row>
     <row r="94" spans="1:26" ht="13.8">
-      <c r="A94" s="45">
+      <c r="A94" s="43">
         <v>89</v>
       </c>
-      <c r="B94" s="46" t="s">
+      <c r="B94" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C94" s="58" t="s">
+      <c r="C94" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="46"/>
-      <c r="E94" s="46"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
-      <c r="H94" s="46"/>
-      <c r="I94" s="93"/>
-      <c r="J94" s="46"/>
-      <c r="K94" s="46"/>
-      <c r="L94" s="46"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="44"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="91"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="44"/>
+      <c r="L94" s="44"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -7663,26 +7663,26 @@
       <c r="Z94" s="2"/>
     </row>
     <row r="95" spans="1:26" ht="13.8">
-      <c r="A95" s="45">
+      <c r="A95" s="43">
         <v>90</v>
       </c>
-      <c r="B95" s="46" t="s">
+      <c r="B95" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C95" s="58" t="s">
+      <c r="C95" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="D95" s="46" t="s">
+      <c r="D95" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E95" s="46"/>
-      <c r="F95" s="46"/>
-      <c r="G95" s="46"/>
-      <c r="H95" s="46"/>
-      <c r="I95" s="93"/>
-      <c r="J95" s="46"/>
-      <c r="K95" s="46"/>
-      <c r="L95" s="46"/>
+      <c r="E95" s="44"/>
+      <c r="F95" s="44"/>
+      <c r="G95" s="44"/>
+      <c r="H95" s="44"/>
+      <c r="I95" s="91"/>
+      <c r="J95" s="44"/>
+      <c r="K95" s="44"/>
+      <c r="L95" s="44"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -7699,24 +7699,24 @@
       <c r="Z95" s="2"/>
     </row>
     <row r="96" spans="1:26" ht="13.8">
-      <c r="A96" s="45">
+      <c r="A96" s="43">
         <v>91</v>
       </c>
-      <c r="B96" s="46" t="s">
+      <c r="B96" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C96" s="58" t="s">
+      <c r="C96" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="D96" s="46"/>
-      <c r="E96" s="46"/>
-      <c r="F96" s="46"/>
-      <c r="G96" s="46"/>
-      <c r="H96" s="46"/>
-      <c r="I96" s="93"/>
-      <c r="J96" s="46"/>
-      <c r="K96" s="46"/>
-      <c r="L96" s="46"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="44"/>
+      <c r="F96" s="44"/>
+      <c r="G96" s="44"/>
+      <c r="H96" s="44"/>
+      <c r="I96" s="91"/>
+      <c r="J96" s="44"/>
+      <c r="K96" s="44"/>
+      <c r="L96" s="44"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -7733,26 +7733,26 @@
       <c r="Z96" s="2"/>
     </row>
     <row r="97" spans="1:26" ht="13.8">
-      <c r="A97" s="45">
+      <c r="A97" s="43">
         <v>92</v>
       </c>
-      <c r="B97" s="46" t="s">
+      <c r="B97" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C97" s="58" t="s">
+      <c r="C97" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="D97" s="46" t="s">
+      <c r="D97" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E97" s="46"/>
-      <c r="F97" s="46"/>
-      <c r="G97" s="46"/>
-      <c r="H97" s="46"/>
-      <c r="I97" s="93"/>
-      <c r="J97" s="46"/>
-      <c r="K97" s="46"/>
-      <c r="L97" s="46"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="91"/>
+      <c r="J97" s="44"/>
+      <c r="K97" s="44"/>
+      <c r="L97" s="44"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -7769,24 +7769,24 @@
       <c r="Z97" s="2"/>
     </row>
     <row r="98" spans="1:26" ht="13.8">
-      <c r="A98" s="45">
+      <c r="A98" s="43">
         <v>93</v>
       </c>
-      <c r="B98" s="46" t="s">
+      <c r="B98" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C98" s="58" t="s">
+      <c r="C98" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="D98" s="46"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="46"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="46"/>
-      <c r="I98" s="93"/>
-      <c r="J98" s="46"/>
-      <c r="K98" s="46"/>
-      <c r="L98" s="46"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="44"/>
+      <c r="G98" s="44"/>
+      <c r="H98" s="44"/>
+      <c r="I98" s="91"/>
+      <c r="J98" s="44"/>
+      <c r="K98" s="44"/>
+      <c r="L98" s="44"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -7803,24 +7803,24 @@
       <c r="Z98" s="2"/>
     </row>
     <row r="99" spans="1:26" ht="13.8">
-      <c r="A99" s="45">
+      <c r="A99" s="43">
         <v>94</v>
       </c>
-      <c r="B99" s="46" t="s">
+      <c r="B99" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C99" s="58" t="s">
+      <c r="C99" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="93"/>
-      <c r="J99" s="46"/>
-      <c r="K99" s="46"/>
-      <c r="L99" s="46"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="44"/>
+      <c r="G99" s="44"/>
+      <c r="H99" s="44"/>
+      <c r="I99" s="91"/>
+      <c r="J99" s="44"/>
+      <c r="K99" s="44"/>
+      <c r="L99" s="44"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -7837,24 +7837,24 @@
       <c r="Z99" s="2"/>
     </row>
     <row r="100" spans="1:26" ht="13.8">
-      <c r="A100" s="45">
+      <c r="A100" s="43">
         <v>95</v>
       </c>
-      <c r="B100" s="46" t="s">
+      <c r="B100" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C100" s="58" t="s">
+      <c r="C100" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="93"/>
-      <c r="J100" s="46"/>
-      <c r="K100" s="46"/>
-      <c r="L100" s="46"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="44"/>
+      <c r="F100" s="44"/>
+      <c r="G100" s="44"/>
+      <c r="H100" s="44"/>
+      <c r="I100" s="91"/>
+      <c r="J100" s="44"/>
+      <c r="K100" s="44"/>
+      <c r="L100" s="44"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -7871,24 +7871,24 @@
       <c r="Z100" s="2"/>
     </row>
     <row r="101" spans="1:26" ht="13.8">
-      <c r="A101" s="45">
+      <c r="A101" s="43">
         <v>96</v>
       </c>
-      <c r="B101" s="46" t="s">
+      <c r="B101" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C101" s="58" t="s">
+      <c r="C101" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="93"/>
-      <c r="J101" s="46"/>
-      <c r="K101" s="46"/>
-      <c r="L101" s="46"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="44"/>
+      <c r="I101" s="91"/>
+      <c r="J101" s="44"/>
+      <c r="K101" s="44"/>
+      <c r="L101" s="44"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -7905,24 +7905,24 @@
       <c r="Z101" s="2"/>
     </row>
     <row r="102" spans="1:26" ht="13.8">
-      <c r="A102" s="45">
+      <c r="A102" s="43">
         <v>97</v>
       </c>
-      <c r="B102" s="46" t="s">
+      <c r="B102" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C102" s="58" t="s">
+      <c r="C102" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="D102" s="46"/>
-      <c r="E102" s="46"/>
-      <c r="F102" s="46"/>
-      <c r="G102" s="46"/>
-      <c r="H102" s="46"/>
-      <c r="I102" s="93"/>
-      <c r="J102" s="46"/>
-      <c r="K102" s="46"/>
-      <c r="L102" s="46"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="44"/>
+      <c r="G102" s="44"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="44"/>
+      <c r="K102" s="44"/>
+      <c r="L102" s="44"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -7939,24 +7939,24 @@
       <c r="Z102" s="2"/>
     </row>
     <row r="103" spans="1:26" ht="13.8">
-      <c r="A103" s="45">
+      <c r="A103" s="43">
         <v>98</v>
       </c>
-      <c r="B103" s="46" t="s">
+      <c r="B103" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C103" s="58" t="s">
+      <c r="C103" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="46"/>
-      <c r="E103" s="46"/>
-      <c r="F103" s="46"/>
-      <c r="G103" s="46"/>
-      <c r="H103" s="46"/>
-      <c r="I103" s="93"/>
-      <c r="J103" s="46"/>
-      <c r="K103" s="46"/>
-      <c r="L103" s="46"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="44"/>
+      <c r="F103" s="44"/>
+      <c r="G103" s="44"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="91"/>
+      <c r="J103" s="44"/>
+      <c r="K103" s="44"/>
+      <c r="L103" s="44"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -7973,24 +7973,24 @@
       <c r="Z103" s="2"/>
     </row>
     <row r="104" spans="1:26" ht="13.8">
-      <c r="A104" s="45">
+      <c r="A104" s="43">
         <v>99</v>
       </c>
-      <c r="B104" s="46" t="s">
+      <c r="B104" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C104" s="58" t="s">
+      <c r="C104" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="D104" s="46"/>
-      <c r="E104" s="46"/>
-      <c r="F104" s="46"/>
-      <c r="G104" s="46"/>
-      <c r="H104" s="46"/>
-      <c r="I104" s="93"/>
-      <c r="J104" s="46"/>
-      <c r="K104" s="46"/>
-      <c r="L104" s="46"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="44"/>
+      <c r="F104" s="44"/>
+      <c r="G104" s="44"/>
+      <c r="H104" s="44"/>
+      <c r="I104" s="91"/>
+      <c r="J104" s="44"/>
+      <c r="K104" s="44"/>
+      <c r="L104" s="44"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -8007,24 +8007,24 @@
       <c r="Z104" s="2"/>
     </row>
     <row r="105" spans="1:26" ht="13.8">
-      <c r="A105" s="45">
+      <c r="A105" s="43">
         <v>100</v>
       </c>
-      <c r="B105" s="46" t="s">
+      <c r="B105" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C105" s="58" t="s">
+      <c r="C105" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="D105" s="46"/>
-      <c r="E105" s="46"/>
-      <c r="F105" s="46"/>
-      <c r="G105" s="46"/>
-      <c r="H105" s="46"/>
-      <c r="I105" s="93"/>
-      <c r="J105" s="46"/>
-      <c r="K105" s="46"/>
-      <c r="L105" s="46"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="44"/>
+      <c r="G105" s="44"/>
+      <c r="H105" s="44"/>
+      <c r="I105" s="91"/>
+      <c r="J105" s="44"/>
+      <c r="K105" s="44"/>
+      <c r="L105" s="44"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -8041,24 +8041,24 @@
       <c r="Z105" s="2"/>
     </row>
     <row r="106" spans="1:26" ht="13.8">
-      <c r="A106" s="45">
+      <c r="A106" s="43">
         <v>101</v>
       </c>
-      <c r="B106" s="46" t="s">
+      <c r="B106" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C106" s="58" t="s">
+      <c r="C106" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="D106" s="46"/>
-      <c r="E106" s="46"/>
-      <c r="F106" s="46"/>
-      <c r="G106" s="46"/>
-      <c r="H106" s="46"/>
-      <c r="I106" s="93"/>
-      <c r="J106" s="46"/>
-      <c r="K106" s="46"/>
-      <c r="L106" s="46"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44"/>
+      <c r="G106" s="44"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="91"/>
+      <c r="J106" s="44"/>
+      <c r="K106" s="44"/>
+      <c r="L106" s="44"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -8075,24 +8075,24 @@
       <c r="Z106" s="2"/>
     </row>
     <row r="107" spans="1:26" ht="13.8">
-      <c r="A107" s="45">
+      <c r="A107" s="43">
         <v>102</v>
       </c>
-      <c r="B107" s="46" t="s">
+      <c r="B107" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C107" s="58" t="s">
+      <c r="C107" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="D107" s="46"/>
-      <c r="E107" s="46"/>
-      <c r="F107" s="46"/>
-      <c r="G107" s="46"/>
-      <c r="H107" s="46"/>
-      <c r="I107" s="93"/>
-      <c r="J107" s="46"/>
-      <c r="K107" s="46"/>
-      <c r="L107" s="46"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="44"/>
+      <c r="F107" s="44"/>
+      <c r="G107" s="44"/>
+      <c r="H107" s="44"/>
+      <c r="I107" s="91"/>
+      <c r="J107" s="44"/>
+      <c r="K107" s="44"/>
+      <c r="L107" s="44"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -8109,24 +8109,24 @@
       <c r="Z107" s="2"/>
     </row>
     <row r="108" spans="1:26" ht="13.8">
-      <c r="A108" s="45">
+      <c r="A108" s="43">
         <v>103</v>
       </c>
-      <c r="B108" s="46" t="s">
+      <c r="B108" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C108" s="58" t="s">
+      <c r="C108" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="D108" s="46"/>
-      <c r="E108" s="46"/>
-      <c r="F108" s="46"/>
-      <c r="G108" s="46"/>
-      <c r="H108" s="46"/>
-      <c r="I108" s="93"/>
-      <c r="J108" s="46"/>
-      <c r="K108" s="46"/>
-      <c r="L108" s="46"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="44"/>
+      <c r="F108" s="44"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="91"/>
+      <c r="J108" s="44"/>
+      <c r="K108" s="44"/>
+      <c r="L108" s="44"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -8143,26 +8143,26 @@
       <c r="Z108" s="2"/>
     </row>
     <row r="109" spans="1:26" ht="13.8">
-      <c r="A109" s="45">
+      <c r="A109" s="43">
         <v>104</v>
       </c>
-      <c r="B109" s="46" t="s">
+      <c r="B109" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C109" s="76" t="s">
+      <c r="C109" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="D109" s="46" t="s">
+      <c r="D109" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E109" s="46"/>
-      <c r="F109" s="46"/>
-      <c r="G109" s="46"/>
-      <c r="H109" s="46"/>
-      <c r="I109" s="93"/>
-      <c r="J109" s="46"/>
-      <c r="K109" s="46"/>
-      <c r="L109" s="46"/>
+      <c r="E109" s="44"/>
+      <c r="F109" s="44"/>
+      <c r="G109" s="44"/>
+      <c r="H109" s="44"/>
+      <c r="I109" s="91"/>
+      <c r="J109" s="44"/>
+      <c r="K109" s="44"/>
+      <c r="L109" s="44"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -8179,26 +8179,26 @@
       <c r="Z109" s="2"/>
     </row>
     <row r="110" spans="1:26" ht="13.8">
-      <c r="A110" s="45">
+      <c r="A110" s="43">
         <v>105</v>
       </c>
-      <c r="B110" s="46" t="s">
+      <c r="B110" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="76" t="s">
+      <c r="C110" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="D110" s="46" t="s">
+      <c r="D110" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E110" s="46"/>
-      <c r="F110" s="46"/>
-      <c r="G110" s="46"/>
-      <c r="H110" s="46"/>
-      <c r="I110" s="93"/>
-      <c r="J110" s="46"/>
-      <c r="K110" s="46"/>
-      <c r="L110" s="46"/>
+      <c r="E110" s="44"/>
+      <c r="F110" s="44"/>
+      <c r="G110" s="44"/>
+      <c r="H110" s="44"/>
+      <c r="I110" s="91"/>
+      <c r="J110" s="44"/>
+      <c r="K110" s="44"/>
+      <c r="L110" s="44"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -8215,24 +8215,24 @@
       <c r="Z110" s="2"/>
     </row>
     <row r="111" spans="1:26" ht="13.8">
-      <c r="A111" s="45">
+      <c r="A111" s="43">
         <v>106</v>
       </c>
-      <c r="B111" s="55" t="s">
+      <c r="B111" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="C111" s="77" t="s">
+      <c r="C111" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="D111" s="55"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55"/>
-      <c r="G111" s="55"/>
-      <c r="H111" s="55"/>
-      <c r="I111" s="94"/>
-      <c r="J111" s="55"/>
-      <c r="K111" s="55"/>
-      <c r="L111" s="55"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="53"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="53"/>
+      <c r="I111" s="92"/>
+      <c r="J111" s="53"/>
+      <c r="K111" s="53"/>
+      <c r="L111" s="53"/>
       <c r="M111" s="6"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
@@ -8249,26 +8249,26 @@
       <c r="Z111" s="6"/>
     </row>
     <row r="112" spans="1:26" ht="13.8">
-      <c r="A112" s="45">
+      <c r="A112" s="43">
         <v>107</v>
       </c>
-      <c r="B112" s="55" t="s">
+      <c r="B112" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="C112" s="77" t="s">
+      <c r="C112" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="D112" s="55" t="s">
+      <c r="D112" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E112" s="55"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="55"/>
-      <c r="H112" s="55"/>
-      <c r="I112" s="94"/>
-      <c r="J112" s="55"/>
-      <c r="K112" s="55"/>
-      <c r="L112" s="55"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="53"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+      <c r="I112" s="92"/>
+      <c r="J112" s="53"/>
+      <c r="K112" s="53"/>
+      <c r="L112" s="53"/>
       <c r="M112" s="6"/>
       <c r="N112" s="6"/>
       <c r="O112" s="6"/>
@@ -8285,24 +8285,24 @@
       <c r="Z112" s="6"/>
     </row>
     <row r="113" spans="1:26" ht="13.8">
-      <c r="A113" s="45">
+      <c r="A113" s="43">
         <v>108</v>
       </c>
-      <c r="B113" s="46" t="s">
+      <c r="B113" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C113" s="76" t="s">
+      <c r="C113" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="D113" s="46"/>
-      <c r="E113" s="46"/>
-      <c r="F113" s="46"/>
-      <c r="G113" s="46"/>
-      <c r="H113" s="46"/>
-      <c r="I113" s="93"/>
-      <c r="J113" s="46"/>
-      <c r="K113" s="46"/>
-      <c r="L113" s="46"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="44"/>
+      <c r="G113" s="44"/>
+      <c r="H113" s="44"/>
+      <c r="I113" s="91"/>
+      <c r="J113" s="44"/>
+      <c r="K113" s="44"/>
+      <c r="L113" s="44"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -8319,26 +8319,26 @@
       <c r="Z113" s="2"/>
     </row>
     <row r="114" spans="1:26" ht="13.8">
-      <c r="A114" s="45">
+      <c r="A114" s="43">
         <v>109</v>
       </c>
-      <c r="B114" s="72" t="s">
+      <c r="B114" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="C114" s="78" t="s">
+      <c r="C114" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="D114" s="72" t="s">
+      <c r="D114" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E114" s="72"/>
-      <c r="F114" s="72"/>
-      <c r="G114" s="72"/>
-      <c r="H114" s="72"/>
-      <c r="I114" s="97"/>
-      <c r="J114" s="72"/>
-      <c r="K114" s="72"/>
-      <c r="L114" s="72"/>
+      <c r="E114" s="70"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="70"/>
+      <c r="H114" s="70"/>
+      <c r="I114" s="95"/>
+      <c r="J114" s="70"/>
+      <c r="K114" s="70"/>
+      <c r="L114" s="70"/>
       <c r="M114" s="9"/>
       <c r="N114" s="9"/>
       <c r="O114" s="9"/>
@@ -8355,26 +8355,26 @@
       <c r="Z114" s="9"/>
     </row>
     <row r="115" spans="1:26" ht="13.8">
-      <c r="A115" s="45">
+      <c r="A115" s="43">
         <v>110</v>
       </c>
-      <c r="B115" s="72" t="s">
+      <c r="B115" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="79" t="s">
+      <c r="C115" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="D115" s="72" t="s">
+      <c r="D115" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E115" s="72"/>
-      <c r="F115" s="72"/>
-      <c r="G115" s="72"/>
-      <c r="H115" s="72"/>
-      <c r="I115" s="97"/>
-      <c r="J115" s="72"/>
-      <c r="K115" s="72"/>
-      <c r="L115" s="72"/>
+      <c r="E115" s="70"/>
+      <c r="F115" s="70"/>
+      <c r="G115" s="70"/>
+      <c r="H115" s="70"/>
+      <c r="I115" s="95"/>
+      <c r="J115" s="70"/>
+      <c r="K115" s="70"/>
+      <c r="L115" s="70"/>
       <c r="M115" s="9"/>
       <c r="N115" s="9"/>
       <c r="O115" s="9"/>
@@ -8391,24 +8391,24 @@
       <c r="Z115" s="9"/>
     </row>
     <row r="116" spans="1:26" ht="13.8">
-      <c r="A116" s="45">
+      <c r="A116" s="43">
         <v>111</v>
       </c>
-      <c r="B116" s="46" t="s">
+      <c r="B116" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C116" s="66" t="s">
+      <c r="C116" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="D116" s="46"/>
-      <c r="E116" s="46"/>
-      <c r="F116" s="46"/>
-      <c r="G116" s="46"/>
-      <c r="H116" s="46"/>
-      <c r="I116" s="93"/>
-      <c r="J116" s="46"/>
-      <c r="K116" s="46"/>
-      <c r="L116" s="46"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="44"/>
+      <c r="G116" s="44"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="91"/>
+      <c r="J116" s="44"/>
+      <c r="K116" s="44"/>
+      <c r="L116" s="44"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -8425,24 +8425,24 @@
       <c r="Z116" s="2"/>
     </row>
     <row r="117" spans="1:26" ht="13.8">
-      <c r="A117" s="45">
+      <c r="A117" s="43">
         <v>112</v>
       </c>
-      <c r="B117" s="46" t="s">
+      <c r="B117" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C117" s="66" t="s">
+      <c r="C117" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="D117" s="46"/>
-      <c r="E117" s="46"/>
-      <c r="F117" s="46"/>
-      <c r="G117" s="46"/>
-      <c r="H117" s="46"/>
-      <c r="I117" s="93"/>
-      <c r="J117" s="46"/>
-      <c r="K117" s="46"/>
-      <c r="L117" s="46"/>
+      <c r="D117" s="44"/>
+      <c r="E117" s="44"/>
+      <c r="F117" s="44"/>
+      <c r="G117" s="44"/>
+      <c r="H117" s="44"/>
+      <c r="I117" s="91"/>
+      <c r="J117" s="44"/>
+      <c r="K117" s="44"/>
+      <c r="L117" s="44"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -8459,24 +8459,24 @@
       <c r="Z117" s="2"/>
     </row>
     <row r="118" spans="1:26" ht="13.8">
-      <c r="A118" s="45">
+      <c r="A118" s="43">
         <v>113</v>
       </c>
-      <c r="B118" s="46" t="s">
+      <c r="B118" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C118" s="76" t="s">
+      <c r="C118" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="D118" s="46"/>
-      <c r="E118" s="46"/>
-      <c r="F118" s="46"/>
-      <c r="G118" s="46"/>
-      <c r="H118" s="46"/>
-      <c r="I118" s="93"/>
-      <c r="J118" s="46"/>
-      <c r="K118" s="46"/>
-      <c r="L118" s="46"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="44"/>
+      <c r="G118" s="44"/>
+      <c r="H118" s="44"/>
+      <c r="I118" s="91"/>
+      <c r="J118" s="44"/>
+      <c r="K118" s="44"/>
+      <c r="L118" s="44"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -8493,24 +8493,24 @@
       <c r="Z118" s="2"/>
     </row>
     <row r="119" spans="1:26" ht="13.8">
-      <c r="A119" s="45">
+      <c r="A119" s="43">
         <v>114</v>
       </c>
-      <c r="B119" s="46" t="s">
+      <c r="B119" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="C119" s="66" t="s">
+      <c r="C119" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D119" s="46"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="46"/>
-      <c r="G119" s="46"/>
-      <c r="H119" s="46"/>
-      <c r="I119" s="93"/>
-      <c r="J119" s="46"/>
-      <c r="K119" s="46"/>
-      <c r="L119" s="46"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
+      <c r="H119" s="44"/>
+      <c r="I119" s="91"/>
+      <c r="J119" s="44"/>
+      <c r="K119" s="44"/>
+      <c r="L119" s="44"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -8527,24 +8527,24 @@
       <c r="Z119" s="2"/>
     </row>
     <row r="120" spans="1:26" ht="13.8">
-      <c r="A120" s="45">
+      <c r="A120" s="43">
         <v>115</v>
       </c>
-      <c r="B120" s="77" t="s">
+      <c r="B120" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="C120" s="64" t="s">
+      <c r="C120" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="D120" s="55"/>
-      <c r="E120" s="55"/>
-      <c r="F120" s="55"/>
-      <c r="G120" s="55"/>
-      <c r="H120" s="55"/>
-      <c r="I120" s="94"/>
-      <c r="J120" s="55"/>
-      <c r="K120" s="55"/>
-      <c r="L120" s="55"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="53"/>
+      <c r="G120" s="53"/>
+      <c r="H120" s="53"/>
+      <c r="I120" s="92"/>
+      <c r="J120" s="53"/>
+      <c r="K120" s="53"/>
+      <c r="L120" s="53"/>
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
@@ -8561,24 +8561,24 @@
       <c r="Z120" s="6"/>
     </row>
     <row r="121" spans="1:26" ht="13.8">
-      <c r="A121" s="45">
+      <c r="A121" s="43">
         <v>116</v>
       </c>
-      <c r="B121" s="77" t="s">
+      <c r="B121" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="C121" s="64" t="s">
+      <c r="C121" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="D121" s="55"/>
-      <c r="E121" s="55"/>
-      <c r="F121" s="55"/>
-      <c r="G121" s="55"/>
-      <c r="H121" s="55"/>
-      <c r="I121" s="94"/>
-      <c r="J121" s="55"/>
-      <c r="K121" s="55"/>
-      <c r="L121" s="55"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="53"/>
+      <c r="F121" s="53"/>
+      <c r="G121" s="53"/>
+      <c r="H121" s="53"/>
+      <c r="I121" s="92"/>
+      <c r="J121" s="53"/>
+      <c r="K121" s="53"/>
+      <c r="L121" s="53"/>
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
       <c r="O121" s="6"/>
@@ -8595,26 +8595,26 @@
       <c r="Z121" s="6"/>
     </row>
     <row r="122" spans="1:26" ht="13.8">
-      <c r="A122" s="45">
+      <c r="A122" s="43">
         <v>117</v>
       </c>
-      <c r="B122" s="80" t="s">
+      <c r="B122" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="C122" s="81" t="s">
+      <c r="C122" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="D122" s="70" t="s">
+      <c r="D122" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E122" s="70"/>
-      <c r="F122" s="70"/>
-      <c r="G122" s="70"/>
-      <c r="H122" s="70"/>
-      <c r="I122" s="96"/>
-      <c r="J122" s="70"/>
-      <c r="K122" s="70"/>
-      <c r="L122" s="70"/>
+      <c r="E122" s="68"/>
+      <c r="F122" s="68"/>
+      <c r="G122" s="68"/>
+      <c r="H122" s="68"/>
+      <c r="I122" s="94"/>
+      <c r="J122" s="68"/>
+      <c r="K122" s="68"/>
+      <c r="L122" s="68"/>
       <c r="M122" s="8"/>
       <c r="N122" s="8"/>
       <c r="O122" s="8"/>
@@ -8631,24 +8631,24 @@
       <c r="Z122" s="8"/>
     </row>
     <row r="123" spans="1:26" ht="13.8">
-      <c r="A123" s="45">
+      <c r="A123" s="43">
         <v>118</v>
       </c>
-      <c r="B123" s="76" t="s">
+      <c r="B123" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C123" s="66" t="s">
+      <c r="C123" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="D123" s="46"/>
-      <c r="E123" s="46"/>
-      <c r="F123" s="46"/>
-      <c r="G123" s="46"/>
-      <c r="H123" s="46"/>
-      <c r="I123" s="93"/>
-      <c r="J123" s="46"/>
-      <c r="K123" s="46"/>
-      <c r="L123" s="46"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="44"/>
+      <c r="F123" s="44"/>
+      <c r="G123" s="44"/>
+      <c r="H123" s="44"/>
+      <c r="I123" s="91"/>
+      <c r="J123" s="44"/>
+      <c r="K123" s="44"/>
+      <c r="L123" s="44"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -8665,24 +8665,24 @@
       <c r="Z123" s="2"/>
     </row>
     <row r="124" spans="1:26" ht="13.8">
-      <c r="A124" s="45">
+      <c r="A124" s="43">
         <v>119</v>
       </c>
-      <c r="B124" s="76" t="s">
+      <c r="B124" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C124" s="66" t="s">
+      <c r="C124" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D124" s="46"/>
-      <c r="E124" s="46"/>
-      <c r="F124" s="46"/>
-      <c r="G124" s="46"/>
-      <c r="H124" s="46"/>
-      <c r="I124" s="93"/>
-      <c r="J124" s="46"/>
-      <c r="K124" s="46"/>
-      <c r="L124" s="46"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="44"/>
+      <c r="F124" s="44"/>
+      <c r="G124" s="44"/>
+      <c r="H124" s="44"/>
+      <c r="I124" s="91"/>
+      <c r="J124" s="44"/>
+      <c r="K124" s="44"/>
+      <c r="L124" s="44"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -8699,24 +8699,24 @@
       <c r="Z124" s="2"/>
     </row>
     <row r="125" spans="1:26" ht="13.8">
-      <c r="A125" s="45">
+      <c r="A125" s="43">
         <v>120</v>
       </c>
-      <c r="B125" s="76" t="s">
+      <c r="B125" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C125" s="66" t="s">
+      <c r="C125" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="D125" s="46"/>
-      <c r="E125" s="46"/>
-      <c r="F125" s="46"/>
-      <c r="G125" s="46"/>
-      <c r="H125" s="46"/>
-      <c r="I125" s="93"/>
-      <c r="J125" s="46"/>
-      <c r="K125" s="46"/>
-      <c r="L125" s="46"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="44"/>
+      <c r="F125" s="44"/>
+      <c r="G125" s="44"/>
+      <c r="H125" s="44"/>
+      <c r="I125" s="91"/>
+      <c r="J125" s="44"/>
+      <c r="K125" s="44"/>
+      <c r="L125" s="44"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -8733,26 +8733,26 @@
       <c r="Z125" s="2"/>
     </row>
     <row r="126" spans="1:26" ht="13.8">
-      <c r="A126" s="45">
+      <c r="A126" s="43">
         <v>121</v>
       </c>
-      <c r="B126" s="76" t="s">
+      <c r="B126" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C126" s="66" t="s">
+      <c r="C126" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="D126" s="70" t="s">
+      <c r="D126" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E126" s="46"/>
-      <c r="F126" s="46"/>
-      <c r="G126" s="46"/>
-      <c r="H126" s="46"/>
-      <c r="I126" s="93"/>
-      <c r="J126" s="46"/>
-      <c r="K126" s="46"/>
-      <c r="L126" s="46"/>
+      <c r="E126" s="44"/>
+      <c r="F126" s="44"/>
+      <c r="G126" s="44"/>
+      <c r="H126" s="44"/>
+      <c r="I126" s="91"/>
+      <c r="J126" s="44"/>
+      <c r="K126" s="44"/>
+      <c r="L126" s="44"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -8769,26 +8769,26 @@
       <c r="Z126" s="2"/>
     </row>
     <row r="127" spans="1:26" ht="13.8">
-      <c r="A127" s="45">
+      <c r="A127" s="43">
         <v>122</v>
       </c>
-      <c r="B127" s="76" t="s">
+      <c r="B127" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C127" s="66" t="s">
+      <c r="C127" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="D127" s="70" t="s">
+      <c r="D127" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E127" s="46"/>
-      <c r="F127" s="46"/>
-      <c r="G127" s="46"/>
-      <c r="H127" s="46"/>
-      <c r="I127" s="93"/>
-      <c r="J127" s="46"/>
-      <c r="K127" s="46"/>
-      <c r="L127" s="46"/>
+      <c r="E127" s="44"/>
+      <c r="F127" s="44"/>
+      <c r="G127" s="44"/>
+      <c r="H127" s="44"/>
+      <c r="I127" s="91"/>
+      <c r="J127" s="44"/>
+      <c r="K127" s="44"/>
+      <c r="L127" s="44"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -8805,24 +8805,24 @@
       <c r="Z127" s="2"/>
     </row>
     <row r="128" spans="1:26" ht="13.8">
-      <c r="A128" s="45">
+      <c r="A128" s="43">
         <v>123</v>
       </c>
-      <c r="B128" s="76" t="s">
+      <c r="B128" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C128" s="66" t="s">
+      <c r="C128" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="D128" s="46"/>
-      <c r="E128" s="46"/>
-      <c r="F128" s="46"/>
-      <c r="G128" s="46"/>
-      <c r="H128" s="46"/>
-      <c r="I128" s="93"/>
-      <c r="J128" s="46"/>
-      <c r="K128" s="46"/>
-      <c r="L128" s="46"/>
+      <c r="D128" s="44"/>
+      <c r="E128" s="44"/>
+      <c r="F128" s="44"/>
+      <c r="G128" s="44"/>
+      <c r="H128" s="44"/>
+      <c r="I128" s="91"/>
+      <c r="J128" s="44"/>
+      <c r="K128" s="44"/>
+      <c r="L128" s="44"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -8839,24 +8839,24 @@
       <c r="Z128" s="2"/>
     </row>
     <row r="129" spans="1:26" ht="13.8">
-      <c r="A129" s="45">
+      <c r="A129" s="43">
         <v>124</v>
       </c>
-      <c r="B129" s="76" t="s">
+      <c r="B129" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="C129" s="66" t="s">
+      <c r="C129" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="D129" s="46"/>
-      <c r="E129" s="46"/>
-      <c r="F129" s="46"/>
-      <c r="G129" s="46"/>
-      <c r="H129" s="46"/>
-      <c r="I129" s="93"/>
-      <c r="J129" s="46"/>
-      <c r="K129" s="46"/>
-      <c r="L129" s="46"/>
+      <c r="D129" s="44"/>
+      <c r="E129" s="44"/>
+      <c r="F129" s="44"/>
+      <c r="G129" s="44"/>
+      <c r="H129" s="44"/>
+      <c r="I129" s="91"/>
+      <c r="J129" s="44"/>
+      <c r="K129" s="44"/>
+      <c r="L129" s="44"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -8873,24 +8873,24 @@
       <c r="Z129" s="2"/>
     </row>
     <row r="130" spans="1:26" ht="13.8">
-      <c r="A130" s="45">
+      <c r="A130" s="43">
         <v>125</v>
       </c>
-      <c r="B130" s="46" t="s">
+      <c r="B130" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C130" s="66" t="s">
+      <c r="C130" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="D130" s="46"/>
-      <c r="E130" s="46"/>
-      <c r="F130" s="46"/>
-      <c r="G130" s="46"/>
-      <c r="H130" s="46"/>
-      <c r="I130" s="93"/>
-      <c r="J130" s="46"/>
-      <c r="K130" s="46"/>
-      <c r="L130" s="46"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="44"/>
+      <c r="F130" s="44"/>
+      <c r="G130" s="44"/>
+      <c r="H130" s="44"/>
+      <c r="I130" s="91"/>
+      <c r="J130" s="44"/>
+      <c r="K130" s="44"/>
+      <c r="L130" s="44"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -8907,24 +8907,24 @@
       <c r="Z130" s="2"/>
     </row>
     <row r="131" spans="1:26" ht="13.8">
-      <c r="A131" s="45">
+      <c r="A131" s="43">
         <v>126</v>
       </c>
-      <c r="B131" s="46" t="s">
+      <c r="B131" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C131" s="66" t="s">
+      <c r="C131" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="D131" s="46"/>
-      <c r="E131" s="46"/>
-      <c r="F131" s="46"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="46"/>
-      <c r="I131" s="93"/>
-      <c r="J131" s="46"/>
-      <c r="K131" s="46"/>
-      <c r="L131" s="46"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="44"/>
+      <c r="F131" s="44"/>
+      <c r="G131" s="44"/>
+      <c r="H131" s="44"/>
+      <c r="I131" s="91"/>
+      <c r="J131" s="44"/>
+      <c r="K131" s="44"/>
+      <c r="L131" s="44"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -8941,24 +8941,24 @@
       <c r="Z131" s="2"/>
     </row>
     <row r="132" spans="1:26" ht="13.8">
-      <c r="A132" s="45">
+      <c r="A132" s="43">
         <v>127</v>
       </c>
-      <c r="B132" s="46" t="s">
+      <c r="B132" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C132" s="66" t="s">
+      <c r="C132" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="D132" s="46"/>
-      <c r="E132" s="46"/>
-      <c r="F132" s="46"/>
-      <c r="G132" s="46"/>
-      <c r="H132" s="46"/>
-      <c r="I132" s="93"/>
-      <c r="J132" s="46"/>
-      <c r="K132" s="46"/>
-      <c r="L132" s="46"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="44"/>
+      <c r="F132" s="44"/>
+      <c r="G132" s="44"/>
+      <c r="H132" s="44"/>
+      <c r="I132" s="91"/>
+      <c r="J132" s="44"/>
+      <c r="K132" s="44"/>
+      <c r="L132" s="44"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -8975,24 +8975,24 @@
       <c r="Z132" s="2"/>
     </row>
     <row r="133" spans="1:26" ht="13.8">
-      <c r="A133" s="45">
+      <c r="A133" s="43">
         <v>128</v>
       </c>
-      <c r="B133" s="46" t="s">
+      <c r="B133" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C133" s="66" t="s">
+      <c r="C133" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="D133" s="46"/>
-      <c r="E133" s="46"/>
-      <c r="F133" s="46"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="46"/>
-      <c r="I133" s="93"/>
-      <c r="J133" s="46"/>
-      <c r="K133" s="46"/>
-      <c r="L133" s="46"/>
+      <c r="D133" s="44"/>
+      <c r="E133" s="44"/>
+      <c r="F133" s="44"/>
+      <c r="G133" s="44"/>
+      <c r="H133" s="44"/>
+      <c r="I133" s="91"/>
+      <c r="J133" s="44"/>
+      <c r="K133" s="44"/>
+      <c r="L133" s="44"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -9009,24 +9009,24 @@
       <c r="Z133" s="2"/>
     </row>
     <row r="134" spans="1:26" ht="13.8">
-      <c r="A134" s="45">
+      <c r="A134" s="43">
         <v>129</v>
       </c>
-      <c r="B134" s="46" t="s">
+      <c r="B134" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C134" s="66" t="s">
+      <c r="C134" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="D134" s="46"/>
-      <c r="E134" s="46"/>
-      <c r="F134" s="46"/>
-      <c r="G134" s="46"/>
-      <c r="H134" s="46"/>
-      <c r="I134" s="93"/>
-      <c r="J134" s="46"/>
-      <c r="K134" s="46"/>
-      <c r="L134" s="46"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="44"/>
+      <c r="F134" s="44"/>
+      <c r="G134" s="44"/>
+      <c r="H134" s="44"/>
+      <c r="I134" s="91"/>
+      <c r="J134" s="44"/>
+      <c r="K134" s="44"/>
+      <c r="L134" s="44"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -9043,24 +9043,24 @@
       <c r="Z134" s="2"/>
     </row>
     <row r="135" spans="1:26" ht="13.8">
-      <c r="A135" s="45">
+      <c r="A135" s="43">
         <v>130</v>
       </c>
-      <c r="B135" s="46" t="s">
+      <c r="B135" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C135" s="66" t="s">
+      <c r="C135" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D135" s="46"/>
-      <c r="E135" s="46"/>
-      <c r="F135" s="46"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="46"/>
-      <c r="I135" s="93"/>
-      <c r="J135" s="46"/>
-      <c r="K135" s="46"/>
-      <c r="L135" s="46"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="44"/>
+      <c r="F135" s="44"/>
+      <c r="G135" s="44"/>
+      <c r="H135" s="44"/>
+      <c r="I135" s="91"/>
+      <c r="J135" s="44"/>
+      <c r="K135" s="44"/>
+      <c r="L135" s="44"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -9077,24 +9077,24 @@
       <c r="Z135" s="2"/>
     </row>
     <row r="136" spans="1:26" ht="13.8">
-      <c r="A136" s="45">
+      <c r="A136" s="43">
         <v>131</v>
       </c>
-      <c r="B136" s="70" t="s">
+      <c r="B136" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="C136" s="81" t="s">
+      <c r="C136" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="D136" s="70"/>
-      <c r="E136" s="70"/>
-      <c r="F136" s="70"/>
-      <c r="G136" s="70"/>
-      <c r="H136" s="70"/>
-      <c r="I136" s="96"/>
-      <c r="J136" s="70"/>
-      <c r="K136" s="70"/>
-      <c r="L136" s="70"/>
+      <c r="D136" s="68"/>
+      <c r="E136" s="68"/>
+      <c r="F136" s="68"/>
+      <c r="G136" s="68"/>
+      <c r="H136" s="68"/>
+      <c r="I136" s="94"/>
+      <c r="J136" s="68"/>
+      <c r="K136" s="68"/>
+      <c r="L136" s="68"/>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
       <c r="O136" s="8"/>
@@ -9111,24 +9111,24 @@
       <c r="Z136" s="8"/>
     </row>
     <row r="137" spans="1:26" ht="13.8">
-      <c r="A137" s="45">
+      <c r="A137" s="43">
         <v>132</v>
       </c>
-      <c r="B137" s="46" t="s">
+      <c r="B137" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C137" s="66" t="s">
+      <c r="C137" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="D137" s="46"/>
-      <c r="E137" s="46"/>
-      <c r="F137" s="46"/>
-      <c r="G137" s="46"/>
-      <c r="H137" s="46"/>
-      <c r="I137" s="93"/>
-      <c r="J137" s="46"/>
-      <c r="K137" s="46"/>
-      <c r="L137" s="46"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="44"/>
+      <c r="F137" s="44"/>
+      <c r="G137" s="44"/>
+      <c r="H137" s="44"/>
+      <c r="I137" s="91"/>
+      <c r="J137" s="44"/>
+      <c r="K137" s="44"/>
+      <c r="L137" s="44"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -9145,26 +9145,26 @@
       <c r="Z137" s="2"/>
     </row>
     <row r="138" spans="1:26" ht="13.8">
-      <c r="A138" s="45">
+      <c r="A138" s="43">
         <v>133</v>
       </c>
-      <c r="B138" s="46" t="s">
+      <c r="B138" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="D138" s="46" t="s">
+      <c r="D138" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E138" s="46"/>
-      <c r="F138" s="46"/>
-      <c r="G138" s="46"/>
-      <c r="H138" s="46"/>
-      <c r="I138" s="93"/>
-      <c r="J138" s="46"/>
-      <c r="K138" s="46"/>
-      <c r="L138" s="46"/>
+      <c r="E138" s="44"/>
+      <c r="F138" s="44"/>
+      <c r="G138" s="44"/>
+      <c r="H138" s="44"/>
+      <c r="I138" s="91"/>
+      <c r="J138" s="44"/>
+      <c r="K138" s="44"/>
+      <c r="L138" s="44"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -9181,24 +9181,24 @@
       <c r="Z138" s="2"/>
     </row>
     <row r="139" spans="1:26" ht="13.8">
-      <c r="A139" s="45">
+      <c r="A139" s="43">
         <v>134</v>
       </c>
-      <c r="B139" s="46" t="s">
+      <c r="B139" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C139" s="66" t="s">
+      <c r="C139" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="D139" s="46"/>
-      <c r="E139" s="46"/>
-      <c r="F139" s="46"/>
-      <c r="G139" s="46"/>
-      <c r="H139" s="46"/>
-      <c r="I139" s="93"/>
-      <c r="J139" s="46"/>
-      <c r="K139" s="46"/>
-      <c r="L139" s="46"/>
+      <c r="D139" s="44"/>
+      <c r="E139" s="44"/>
+      <c r="F139" s="44"/>
+      <c r="G139" s="44"/>
+      <c r="H139" s="44"/>
+      <c r="I139" s="91"/>
+      <c r="J139" s="44"/>
+      <c r="K139" s="44"/>
+      <c r="L139" s="44"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -9215,26 +9215,26 @@
       <c r="Z139" s="2"/>
     </row>
     <row r="140" spans="1:26" ht="13.8">
-      <c r="A140" s="45">
+      <c r="A140" s="43">
         <v>135</v>
       </c>
-      <c r="B140" s="46" t="s">
+      <c r="B140" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C140" s="66" t="s">
+      <c r="C140" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D140" s="46" t="s">
+      <c r="D140" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E140" s="46"/>
-      <c r="F140" s="46"/>
-      <c r="G140" s="46"/>
-      <c r="H140" s="46"/>
-      <c r="I140" s="93"/>
-      <c r="J140" s="46"/>
-      <c r="K140" s="46"/>
-      <c r="L140" s="46"/>
+      <c r="E140" s="44"/>
+      <c r="F140" s="44"/>
+      <c r="G140" s="44"/>
+      <c r="H140" s="44"/>
+      <c r="I140" s="91"/>
+      <c r="J140" s="44"/>
+      <c r="K140" s="44"/>
+      <c r="L140" s="44"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -9251,24 +9251,24 @@
       <c r="Z140" s="2"/>
     </row>
     <row r="141" spans="1:26" ht="13.8">
-      <c r="A141" s="45">
+      <c r="A141" s="43">
         <v>136</v>
       </c>
-      <c r="B141" s="46" t="s">
+      <c r="B141" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C141" s="66" t="s">
+      <c r="C141" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="D141" s="46"/>
-      <c r="E141" s="46"/>
-      <c r="F141" s="46"/>
-      <c r="G141" s="46"/>
-      <c r="H141" s="46"/>
-      <c r="I141" s="93"/>
-      <c r="J141" s="46"/>
-      <c r="K141" s="46"/>
-      <c r="L141" s="46"/>
+      <c r="D141" s="44"/>
+      <c r="E141" s="44"/>
+      <c r="F141" s="44"/>
+      <c r="G141" s="44"/>
+      <c r="H141" s="44"/>
+      <c r="I141" s="91"/>
+      <c r="J141" s="44"/>
+      <c r="K141" s="44"/>
+      <c r="L141" s="44"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -9285,24 +9285,24 @@
       <c r="Z141" s="2"/>
     </row>
     <row r="142" spans="1:26" ht="13.8">
-      <c r="A142" s="45">
+      <c r="A142" s="43">
         <v>137</v>
       </c>
-      <c r="B142" s="46" t="s">
+      <c r="B142" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C142" s="66" t="s">
+      <c r="C142" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="D142" s="46"/>
-      <c r="E142" s="46"/>
-      <c r="F142" s="46"/>
-      <c r="G142" s="46"/>
-      <c r="H142" s="46"/>
-      <c r="I142" s="93"/>
-      <c r="J142" s="46"/>
-      <c r="K142" s="46"/>
-      <c r="L142" s="46"/>
+      <c r="D142" s="44"/>
+      <c r="E142" s="44"/>
+      <c r="F142" s="44"/>
+      <c r="G142" s="44"/>
+      <c r="H142" s="44"/>
+      <c r="I142" s="91"/>
+      <c r="J142" s="44"/>
+      <c r="K142" s="44"/>
+      <c r="L142" s="44"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -9319,24 +9319,24 @@
       <c r="Z142" s="2"/>
     </row>
     <row r="143" spans="1:26" ht="13.8">
-      <c r="A143" s="45">
+      <c r="A143" s="43">
         <v>138</v>
       </c>
-      <c r="B143" s="46" t="s">
+      <c r="B143" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C143" s="66" t="s">
+      <c r="C143" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="D143" s="46"/>
-      <c r="E143" s="46"/>
-      <c r="F143" s="46"/>
-      <c r="G143" s="46"/>
-      <c r="H143" s="46"/>
-      <c r="I143" s="93"/>
-      <c r="J143" s="46"/>
-      <c r="K143" s="46"/>
-      <c r="L143" s="46"/>
+      <c r="D143" s="44"/>
+      <c r="E143" s="44"/>
+      <c r="F143" s="44"/>
+      <c r="G143" s="44"/>
+      <c r="H143" s="44"/>
+      <c r="I143" s="91"/>
+      <c r="J143" s="44"/>
+      <c r="K143" s="44"/>
+      <c r="L143" s="44"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -9353,24 +9353,24 @@
       <c r="Z143" s="2"/>
     </row>
     <row r="144" spans="1:26" ht="13.8">
-      <c r="A144" s="45">
+      <c r="A144" s="43">
         <v>139</v>
       </c>
-      <c r="B144" s="46" t="s">
+      <c r="B144" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C144" s="66" t="s">
+      <c r="C144" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="D144" s="46"/>
-      <c r="E144" s="46"/>
-      <c r="F144" s="46"/>
-      <c r="G144" s="46"/>
-      <c r="H144" s="46"/>
-      <c r="I144" s="93"/>
-      <c r="J144" s="46"/>
-      <c r="K144" s="46"/>
-      <c r="L144" s="46"/>
+      <c r="D144" s="44"/>
+      <c r="E144" s="44"/>
+      <c r="F144" s="44"/>
+      <c r="G144" s="44"/>
+      <c r="H144" s="44"/>
+      <c r="I144" s="91"/>
+      <c r="J144" s="44"/>
+      <c r="K144" s="44"/>
+      <c r="L144" s="44"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -9387,24 +9387,24 @@
       <c r="Z144" s="2"/>
     </row>
     <row r="145" spans="1:26" ht="13.8">
-      <c r="A145" s="45">
+      <c r="A145" s="43">
         <v>140</v>
       </c>
-      <c r="B145" s="46" t="s">
+      <c r="B145" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C145" s="66" t="s">
+      <c r="C145" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="D145" s="46"/>
-      <c r="E145" s="46"/>
-      <c r="F145" s="46"/>
-      <c r="G145" s="46"/>
-      <c r="H145" s="46"/>
-      <c r="I145" s="93"/>
-      <c r="J145" s="46"/>
-      <c r="K145" s="46"/>
-      <c r="L145" s="46"/>
+      <c r="D145" s="44"/>
+      <c r="E145" s="44"/>
+      <c r="F145" s="44"/>
+      <c r="G145" s="44"/>
+      <c r="H145" s="44"/>
+      <c r="I145" s="91"/>
+      <c r="J145" s="44"/>
+      <c r="K145" s="44"/>
+      <c r="L145" s="44"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -9421,24 +9421,24 @@
       <c r="Z145" s="2"/>
     </row>
     <row r="146" spans="1:26" ht="13.8">
-      <c r="A146" s="45">
+      <c r="A146" s="43">
         <v>141</v>
       </c>
-      <c r="B146" s="46" t="s">
+      <c r="B146" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C146" s="66" t="s">
+      <c r="C146" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="D146" s="46"/>
-      <c r="E146" s="46"/>
-      <c r="F146" s="46"/>
-      <c r="G146" s="46"/>
-      <c r="H146" s="46"/>
-      <c r="I146" s="93"/>
-      <c r="J146" s="46"/>
-      <c r="K146" s="46"/>
-      <c r="L146" s="46"/>
+      <c r="D146" s="44"/>
+      <c r="E146" s="44"/>
+      <c r="F146" s="44"/>
+      <c r="G146" s="44"/>
+      <c r="H146" s="44"/>
+      <c r="I146" s="91"/>
+      <c r="J146" s="44"/>
+      <c r="K146" s="44"/>
+      <c r="L146" s="44"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -9455,24 +9455,24 @@
       <c r="Z146" s="2"/>
     </row>
     <row r="147" spans="1:26" ht="13.8">
-      <c r="A147" s="45">
+      <c r="A147" s="43">
         <v>142</v>
       </c>
-      <c r="B147" s="46" t="s">
+      <c r="B147" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C147" s="66" t="s">
+      <c r="C147" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="D147" s="46"/>
-      <c r="E147" s="46"/>
-      <c r="F147" s="46"/>
-      <c r="G147" s="46"/>
-      <c r="H147" s="46"/>
-      <c r="I147" s="93"/>
-      <c r="J147" s="46"/>
-      <c r="K147" s="46"/>
-      <c r="L147" s="46"/>
+      <c r="D147" s="44"/>
+      <c r="E147" s="44"/>
+      <c r="F147" s="44"/>
+      <c r="G147" s="44"/>
+      <c r="H147" s="44"/>
+      <c r="I147" s="91"/>
+      <c r="J147" s="44"/>
+      <c r="K147" s="44"/>
+      <c r="L147" s="44"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -9489,26 +9489,26 @@
       <c r="Z147" s="2"/>
     </row>
     <row r="148" spans="1:26" ht="13.8">
-      <c r="A148" s="45">
+      <c r="A148" s="43">
         <v>143</v>
       </c>
-      <c r="B148" s="46" t="s">
+      <c r="B148" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C148" s="66" t="s">
+      <c r="C148" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="D148" s="46" t="s">
+      <c r="D148" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E148" s="46"/>
-      <c r="F148" s="46"/>
-      <c r="G148" s="46"/>
-      <c r="H148" s="46"/>
-      <c r="I148" s="93"/>
-      <c r="J148" s="46"/>
-      <c r="K148" s="46"/>
-      <c r="L148" s="46"/>
+      <c r="E148" s="44"/>
+      <c r="F148" s="44"/>
+      <c r="G148" s="44"/>
+      <c r="H148" s="44"/>
+      <c r="I148" s="91"/>
+      <c r="J148" s="44"/>
+      <c r="K148" s="44"/>
+      <c r="L148" s="44"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -9525,24 +9525,24 @@
       <c r="Z148" s="2"/>
     </row>
     <row r="149" spans="1:26" ht="13.8">
-      <c r="A149" s="45">
+      <c r="A149" s="43">
         <v>144</v>
       </c>
-      <c r="B149" s="46" t="s">
+      <c r="B149" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C149" s="66" t="s">
+      <c r="C149" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="D149" s="46"/>
-      <c r="E149" s="46"/>
-      <c r="F149" s="46"/>
-      <c r="G149" s="46"/>
-      <c r="H149" s="46"/>
-      <c r="I149" s="93"/>
-      <c r="J149" s="46"/>
-      <c r="K149" s="46"/>
-      <c r="L149" s="46"/>
+      <c r="D149" s="44"/>
+      <c r="E149" s="44"/>
+      <c r="F149" s="44"/>
+      <c r="G149" s="44"/>
+      <c r="H149" s="44"/>
+      <c r="I149" s="91"/>
+      <c r="J149" s="44"/>
+      <c r="K149" s="44"/>
+      <c r="L149" s="44"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -9559,24 +9559,24 @@
       <c r="Z149" s="2"/>
     </row>
     <row r="150" spans="1:26" ht="13.8">
-      <c r="A150" s="45">
+      <c r="A150" s="43">
         <v>145</v>
       </c>
-      <c r="B150" s="46" t="s">
+      <c r="B150" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="D150" s="46"/>
-      <c r="E150" s="46"/>
-      <c r="F150" s="46"/>
-      <c r="G150" s="46"/>
-      <c r="H150" s="46"/>
-      <c r="I150" s="93"/>
-      <c r="J150" s="46"/>
-      <c r="K150" s="46"/>
-      <c r="L150" s="46"/>
+      <c r="D150" s="44"/>
+      <c r="E150" s="44"/>
+      <c r="F150" s="44"/>
+      <c r="G150" s="44"/>
+      <c r="H150" s="44"/>
+      <c r="I150" s="91"/>
+      <c r="J150" s="44"/>
+      <c r="K150" s="44"/>
+      <c r="L150" s="44"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -9593,24 +9593,24 @@
       <c r="Z150" s="2"/>
     </row>
     <row r="151" spans="1:26" ht="13.8">
-      <c r="A151" s="45">
+      <c r="A151" s="43">
         <v>146</v>
       </c>
-      <c r="B151" s="46" t="s">
+      <c r="B151" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C151" s="66" t="s">
+      <c r="C151" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D151" s="46"/>
-      <c r="E151" s="46"/>
-      <c r="F151" s="46"/>
-      <c r="G151" s="46"/>
-      <c r="H151" s="46"/>
-      <c r="I151" s="93"/>
-      <c r="J151" s="46"/>
-      <c r="K151" s="46"/>
-      <c r="L151" s="46"/>
+      <c r="D151" s="44"/>
+      <c r="E151" s="44"/>
+      <c r="F151" s="44"/>
+      <c r="G151" s="44"/>
+      <c r="H151" s="44"/>
+      <c r="I151" s="91"/>
+      <c r="J151" s="44"/>
+      <c r="K151" s="44"/>
+      <c r="L151" s="44"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -9627,24 +9627,24 @@
       <c r="Z151" s="2"/>
     </row>
     <row r="152" spans="1:26" ht="13.8">
-      <c r="A152" s="45">
+      <c r="A152" s="43">
         <v>147</v>
       </c>
-      <c r="B152" s="46" t="s">
+      <c r="B152" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C152" s="66" t="s">
+      <c r="C152" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="D152" s="46"/>
-      <c r="E152" s="46"/>
-      <c r="F152" s="46"/>
-      <c r="G152" s="46"/>
-      <c r="H152" s="46"/>
-      <c r="I152" s="93"/>
-      <c r="J152" s="46"/>
-      <c r="K152" s="46"/>
-      <c r="L152" s="46"/>
+      <c r="D152" s="44"/>
+      <c r="E152" s="44"/>
+      <c r="F152" s="44"/>
+      <c r="G152" s="44"/>
+      <c r="H152" s="44"/>
+      <c r="I152" s="91"/>
+      <c r="J152" s="44"/>
+      <c r="K152" s="44"/>
+      <c r="L152" s="44"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -9661,24 +9661,24 @@
       <c r="Z152" s="2"/>
     </row>
     <row r="153" spans="1:26" ht="13.8">
-      <c r="A153" s="45">
+      <c r="A153" s="43">
         <v>148</v>
       </c>
-      <c r="B153" s="46" t="s">
+      <c r="B153" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>174</v>
       </c>
-      <c r="D153" s="46"/>
-      <c r="E153" s="46"/>
-      <c r="F153" s="46"/>
-      <c r="G153" s="46"/>
-      <c r="H153" s="46"/>
-      <c r="I153" s="93"/>
-      <c r="J153" s="46"/>
-      <c r="K153" s="46"/>
-      <c r="L153" s="46"/>
+      <c r="D153" s="44"/>
+      <c r="E153" s="44"/>
+      <c r="F153" s="44"/>
+      <c r="G153" s="44"/>
+      <c r="H153" s="44"/>
+      <c r="I153" s="91"/>
+      <c r="J153" s="44"/>
+      <c r="K153" s="44"/>
+      <c r="L153" s="44"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -9695,24 +9695,24 @@
       <c r="Z153" s="2"/>
     </row>
     <row r="154" spans="1:26" ht="13.8">
-      <c r="A154" s="45">
+      <c r="A154" s="43">
         <v>149</v>
       </c>
-      <c r="B154" s="46" t="s">
+      <c r="B154" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C154" s="66" t="s">
+      <c r="C154" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="D154" s="46"/>
-      <c r="E154" s="46"/>
-      <c r="F154" s="46"/>
-      <c r="G154" s="46"/>
-      <c r="H154" s="46"/>
-      <c r="I154" s="93"/>
-      <c r="J154" s="46"/>
-      <c r="K154" s="46"/>
-      <c r="L154" s="46"/>
+      <c r="D154" s="44"/>
+      <c r="E154" s="44"/>
+      <c r="F154" s="44"/>
+      <c r="G154" s="44"/>
+      <c r="H154" s="44"/>
+      <c r="I154" s="91"/>
+      <c r="J154" s="44"/>
+      <c r="K154" s="44"/>
+      <c r="L154" s="44"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -9729,24 +9729,24 @@
       <c r="Z154" s="2"/>
     </row>
     <row r="155" spans="1:26" ht="13.8">
-      <c r="A155" s="45">
+      <c r="A155" s="43">
         <v>150</v>
       </c>
-      <c r="B155" s="46" t="s">
+      <c r="B155" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C155" s="66" t="s">
+      <c r="C155" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="D155" s="46"/>
-      <c r="E155" s="46"/>
-      <c r="F155" s="46"/>
-      <c r="G155" s="46"/>
-      <c r="H155" s="46"/>
-      <c r="I155" s="93"/>
-      <c r="J155" s="46"/>
-      <c r="K155" s="46"/>
-      <c r="L155" s="46"/>
+      <c r="D155" s="44"/>
+      <c r="E155" s="44"/>
+      <c r="F155" s="44"/>
+      <c r="G155" s="44"/>
+      <c r="H155" s="44"/>
+      <c r="I155" s="91"/>
+      <c r="J155" s="44"/>
+      <c r="K155" s="44"/>
+      <c r="L155" s="44"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -9763,24 +9763,24 @@
       <c r="Z155" s="2"/>
     </row>
     <row r="156" spans="1:26" ht="13.8">
-      <c r="A156" s="45">
+      <c r="A156" s="43">
         <v>151</v>
       </c>
-      <c r="B156" s="46" t="s">
+      <c r="B156" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C156" s="66" t="s">
+      <c r="C156" s="64" t="s">
         <v>177</v>
       </c>
-      <c r="D156" s="46"/>
-      <c r="E156" s="46"/>
-      <c r="F156" s="46"/>
-      <c r="G156" s="46"/>
-      <c r="H156" s="46"/>
-      <c r="I156" s="93"/>
-      <c r="J156" s="46"/>
-      <c r="K156" s="46"/>
-      <c r="L156" s="46"/>
+      <c r="D156" s="44"/>
+      <c r="E156" s="44"/>
+      <c r="F156" s="44"/>
+      <c r="G156" s="44"/>
+      <c r="H156" s="44"/>
+      <c r="I156" s="91"/>
+      <c r="J156" s="44"/>
+      <c r="K156" s="44"/>
+      <c r="L156" s="44"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -9797,24 +9797,24 @@
       <c r="Z156" s="2"/>
     </row>
     <row r="157" spans="1:26" ht="13.8">
-      <c r="A157" s="45">
+      <c r="A157" s="43">
         <v>152</v>
       </c>
-      <c r="B157" s="46" t="s">
+      <c r="B157" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C157" s="66" t="s">
+      <c r="C157" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="D157" s="46"/>
-      <c r="E157" s="46"/>
-      <c r="F157" s="46"/>
-      <c r="G157" s="46"/>
-      <c r="H157" s="46"/>
-      <c r="I157" s="93"/>
-      <c r="J157" s="46"/>
-      <c r="K157" s="46"/>
-      <c r="L157" s="46"/>
+      <c r="D157" s="44"/>
+      <c r="E157" s="44"/>
+      <c r="F157" s="44"/>
+      <c r="G157" s="44"/>
+      <c r="H157" s="44"/>
+      <c r="I157" s="91"/>
+      <c r="J157" s="44"/>
+      <c r="K157" s="44"/>
+      <c r="L157" s="44"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -9831,24 +9831,24 @@
       <c r="Z157" s="2"/>
     </row>
     <row r="158" spans="1:26" ht="13.2">
-      <c r="A158" s="45">
+      <c r="A158" s="43">
         <v>153</v>
       </c>
-      <c r="B158" s="46" t="s">
+      <c r="B158" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="C158" s="46" t="s">
+      <c r="C158" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="D158" s="46"/>
-      <c r="E158" s="46"/>
-      <c r="F158" s="46"/>
-      <c r="G158" s="46"/>
-      <c r="H158" s="46"/>
-      <c r="I158" s="93"/>
-      <c r="J158" s="46"/>
-      <c r="K158" s="46"/>
-      <c r="L158" s="46"/>
+      <c r="D158" s="44"/>
+      <c r="E158" s="44"/>
+      <c r="F158" s="44"/>
+      <c r="G158" s="44"/>
+      <c r="H158" s="44"/>
+      <c r="I158" s="91"/>
+      <c r="J158" s="44"/>
+      <c r="K158" s="44"/>
+      <c r="L158" s="44"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -9865,24 +9865,24 @@
       <c r="Z158" s="2"/>
     </row>
     <row r="159" spans="1:26" ht="13.2">
-      <c r="A159" s="45">
+      <c r="A159" s="43">
         <v>154</v>
       </c>
-      <c r="B159" s="46" t="s">
+      <c r="B159" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="C159" s="46" t="s">
+      <c r="C159" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D159" s="46"/>
-      <c r="E159" s="46"/>
-      <c r="F159" s="46"/>
-      <c r="G159" s="46"/>
-      <c r="H159" s="46"/>
-      <c r="I159" s="93"/>
-      <c r="J159" s="46"/>
-      <c r="K159" s="46"/>
-      <c r="L159" s="46"/>
+      <c r="D159" s="44"/>
+      <c r="E159" s="44"/>
+      <c r="F159" s="44"/>
+      <c r="G159" s="44"/>
+      <c r="H159" s="44"/>
+      <c r="I159" s="91"/>
+      <c r="J159" s="44"/>
+      <c r="K159" s="44"/>
+      <c r="L159" s="44"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -9899,26 +9899,26 @@
       <c r="Z159" s="2"/>
     </row>
     <row r="160" spans="1:26" ht="13.2">
-      <c r="A160" s="45">
+      <c r="A160" s="43">
         <v>155</v>
       </c>
-      <c r="B160" s="46" t="s">
+      <c r="B160" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C160" s="82" t="s">
+      <c r="C160" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="D160" s="83"/>
-      <c r="E160" s="46" t="s">
+      <c r="D160" s="81"/>
+      <c r="E160" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="F160" s="46"/>
-      <c r="G160" s="46"/>
-      <c r="H160" s="46"/>
-      <c r="I160" s="93"/>
-      <c r="J160" s="46"/>
-      <c r="K160" s="46"/>
-      <c r="L160" s="46"/>
+      <c r="F160" s="44"/>
+      <c r="G160" s="44"/>
+      <c r="H160" s="44"/>
+      <c r="I160" s="91"/>
+      <c r="J160" s="44"/>
+      <c r="K160" s="44"/>
+      <c r="L160" s="44"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -9935,26 +9935,26 @@
       <c r="Z160" s="2"/>
     </row>
     <row r="161" spans="1:26" ht="13.2">
-      <c r="A161" s="45">
+      <c r="A161" s="43">
         <v>156</v>
       </c>
-      <c r="B161" s="46" t="s">
+      <c r="B161" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C161" s="82" t="s">
+      <c r="C161" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="D161" s="83"/>
-      <c r="E161" s="46" t="s">
+      <c r="D161" s="81"/>
+      <c r="E161" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="F161" s="46"/>
-      <c r="G161" s="46"/>
-      <c r="H161" s="46"/>
-      <c r="I161" s="93"/>
-      <c r="J161" s="46"/>
-      <c r="K161" s="46"/>
-      <c r="L161" s="46"/>
+      <c r="F161" s="44"/>
+      <c r="G161" s="44"/>
+      <c r="H161" s="44"/>
+      <c r="I161" s="91"/>
+      <c r="J161" s="44"/>
+      <c r="K161" s="44"/>
+      <c r="L161" s="44"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -9971,26 +9971,26 @@
       <c r="Z161" s="2"/>
     </row>
     <row r="162" spans="1:26" ht="13.2">
-      <c r="A162" s="45">
+      <c r="A162" s="43">
         <v>157</v>
       </c>
-      <c r="B162" s="46" t="s">
+      <c r="B162" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C162" s="82" t="s">
+      <c r="C162" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="D162" s="83"/>
-      <c r="E162" s="46" t="s">
+      <c r="D162" s="81"/>
+      <c r="E162" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="F162" s="46"/>
-      <c r="G162" s="46"/>
-      <c r="H162" s="46"/>
-      <c r="I162" s="93"/>
-      <c r="J162" s="46"/>
-      <c r="K162" s="46"/>
-      <c r="L162" s="46"/>
+      <c r="F162" s="44"/>
+      <c r="G162" s="44"/>
+      <c r="H162" s="44"/>
+      <c r="I162" s="91"/>
+      <c r="J162" s="44"/>
+      <c r="K162" s="44"/>
+      <c r="L162" s="44"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -10007,26 +10007,26 @@
       <c r="Z162" s="2"/>
     </row>
     <row r="163" spans="1:26" ht="13.2">
-      <c r="A163" s="45">
+      <c r="A163" s="43">
         <v>158</v>
       </c>
-      <c r="B163" s="46" t="s">
+      <c r="B163" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C163" s="82" t="s">
+      <c r="C163" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="D163" s="83"/>
-      <c r="E163" s="46" t="s">
+      <c r="D163" s="81"/>
+      <c r="E163" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="F163" s="46"/>
-      <c r="G163" s="46"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="93"/>
-      <c r="J163" s="46"/>
-      <c r="K163" s="46"/>
-      <c r="L163" s="46"/>
+      <c r="F163" s="44"/>
+      <c r="G163" s="44"/>
+      <c r="H163" s="44"/>
+      <c r="I163" s="91"/>
+      <c r="J163" s="44"/>
+      <c r="K163" s="44"/>
+      <c r="L163" s="44"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -10043,26 +10043,26 @@
       <c r="Z163" s="2"/>
     </row>
     <row r="164" spans="1:26" ht="13.2">
-      <c r="A164" s="45">
+      <c r="A164" s="43">
         <v>159</v>
       </c>
-      <c r="B164" s="46" t="s">
+      <c r="B164" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C164" s="82" t="s">
+      <c r="C164" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="D164" s="83"/>
-      <c r="E164" s="46" t="s">
+      <c r="D164" s="81"/>
+      <c r="E164" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="F164" s="46"/>
-      <c r="G164" s="46"/>
-      <c r="H164" s="46"/>
-      <c r="I164" s="93"/>
-      <c r="J164" s="46"/>
-      <c r="K164" s="46"/>
-      <c r="L164" s="46"/>
+      <c r="F164" s="44"/>
+      <c r="G164" s="44"/>
+      <c r="H164" s="44"/>
+      <c r="I164" s="91"/>
+      <c r="J164" s="44"/>
+      <c r="K164" s="44"/>
+      <c r="L164" s="44"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -10079,26 +10079,26 @@
       <c r="Z164" s="2"/>
     </row>
     <row r="165" spans="1:26" ht="13.2">
-      <c r="A165" s="45">
+      <c r="A165" s="43">
         <v>160</v>
       </c>
-      <c r="B165" s="46" t="s">
+      <c r="B165" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C165" s="82" t="s">
+      <c r="C165" s="80" t="s">
         <v>192</v>
       </c>
-      <c r="D165" s="83"/>
-      <c r="E165" s="46" t="s">
+      <c r="D165" s="81"/>
+      <c r="E165" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="F165" s="46"/>
-      <c r="G165" s="46"/>
-      <c r="H165" s="46"/>
-      <c r="I165" s="93"/>
-      <c r="J165" s="46"/>
-      <c r="K165" s="46"/>
-      <c r="L165" s="46"/>
+      <c r="F165" s="44"/>
+      <c r="G165" s="44"/>
+      <c r="H165" s="44"/>
+      <c r="I165" s="91"/>
+      <c r="J165" s="44"/>
+      <c r="K165" s="44"/>
+      <c r="L165" s="44"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -10115,26 +10115,26 @@
       <c r="Z165" s="2"/>
     </row>
     <row r="166" spans="1:26" ht="13.2">
-      <c r="A166" s="45">
+      <c r="A166" s="43">
         <v>161</v>
       </c>
-      <c r="B166" s="46" t="s">
+      <c r="B166" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C166" s="82" t="s">
+      <c r="C166" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="D166" s="83"/>
-      <c r="E166" s="46" t="s">
+      <c r="D166" s="81"/>
+      <c r="E166" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="F166" s="46"/>
-      <c r="G166" s="46"/>
-      <c r="H166" s="46"/>
-      <c r="I166" s="93"/>
-      <c r="J166" s="46"/>
-      <c r="K166" s="46"/>
-      <c r="L166" s="46"/>
+      <c r="F166" s="44"/>
+      <c r="G166" s="44"/>
+      <c r="H166" s="44"/>
+      <c r="I166" s="91"/>
+      <c r="J166" s="44"/>
+      <c r="K166" s="44"/>
+      <c r="L166" s="44"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -10151,24 +10151,24 @@
       <c r="Z166" s="2"/>
     </row>
     <row r="167" spans="1:26" ht="13.2">
-      <c r="A167" s="45">
+      <c r="A167" s="43">
         <v>162</v>
       </c>
-      <c r="B167" s="46" t="s">
+      <c r="B167" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="C167" s="46" t="s">
+      <c r="C167" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="D167" s="46"/>
-      <c r="E167" s="46"/>
-      <c r="F167" s="46"/>
-      <c r="G167" s="46"/>
-      <c r="H167" s="46"/>
-      <c r="I167" s="93"/>
-      <c r="J167" s="46"/>
-      <c r="K167" s="46"/>
-      <c r="L167" s="46"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="44"/>
+      <c r="F167" s="44"/>
+      <c r="G167" s="44"/>
+      <c r="H167" s="44"/>
+      <c r="I167" s="91"/>
+      <c r="J167" s="44"/>
+      <c r="K167" s="44"/>
+      <c r="L167" s="44"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -10185,26 +10185,26 @@
       <c r="Z167" s="2"/>
     </row>
     <row r="168" spans="1:26" ht="13.2">
-      <c r="A168" s="45">
+      <c r="A168" s="43">
         <v>163</v>
       </c>
-      <c r="B168" s="46" t="s">
+      <c r="B168" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C168" s="46" t="s">
+      <c r="C168" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="D168" s="46" t="s">
+      <c r="D168" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E168" s="46"/>
-      <c r="F168" s="46"/>
-      <c r="G168" s="46"/>
-      <c r="H168" s="46"/>
-      <c r="I168" s="93"/>
-      <c r="J168" s="46"/>
-      <c r="K168" s="46"/>
-      <c r="L168" s="46"/>
+      <c r="E168" s="44"/>
+      <c r="F168" s="44"/>
+      <c r="G168" s="44"/>
+      <c r="H168" s="44"/>
+      <c r="I168" s="91"/>
+      <c r="J168" s="44"/>
+      <c r="K168" s="44"/>
+      <c r="L168" s="44"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -10221,26 +10221,26 @@
       <c r="Z168" s="2"/>
     </row>
     <row r="169" spans="1:26" ht="13.2">
-      <c r="A169" s="45">
+      <c r="A169" s="43">
         <v>164</v>
       </c>
-      <c r="B169" s="46" t="s">
+      <c r="B169" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C169" s="46" t="s">
+      <c r="C169" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="D169" s="46" t="s">
+      <c r="D169" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E169" s="46"/>
-      <c r="F169" s="46"/>
-      <c r="G169" s="46"/>
-      <c r="H169" s="46"/>
-      <c r="I169" s="93"/>
-      <c r="J169" s="46"/>
-      <c r="K169" s="46"/>
-      <c r="L169" s="46"/>
+      <c r="E169" s="44"/>
+      <c r="F169" s="44"/>
+      <c r="G169" s="44"/>
+      <c r="H169" s="44"/>
+      <c r="I169" s="91"/>
+      <c r="J169" s="44"/>
+      <c r="K169" s="44"/>
+      <c r="L169" s="44"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -10257,26 +10257,26 @@
       <c r="Z169" s="2"/>
     </row>
     <row r="170" spans="1:26" ht="13.2">
-      <c r="A170" s="45">
+      <c r="A170" s="43">
         <v>165</v>
       </c>
-      <c r="B170" s="72" t="s">
+      <c r="B170" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C170" s="72" t="s">
+      <c r="C170" s="70" t="s">
         <v>200</v>
       </c>
-      <c r="D170" s="72" t="s">
+      <c r="D170" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E170" s="72"/>
-      <c r="F170" s="72"/>
-      <c r="G170" s="72"/>
-      <c r="H170" s="72"/>
-      <c r="I170" s="97"/>
-      <c r="J170" s="72"/>
-      <c r="K170" s="72"/>
-      <c r="L170" s="72"/>
+      <c r="E170" s="70"/>
+      <c r="F170" s="70"/>
+      <c r="G170" s="70"/>
+      <c r="H170" s="70"/>
+      <c r="I170" s="95"/>
+      <c r="J170" s="70"/>
+      <c r="K170" s="70"/>
+      <c r="L170" s="70"/>
       <c r="M170" s="9"/>
       <c r="N170" s="9"/>
       <c r="O170" s="9"/>
@@ -10293,26 +10293,26 @@
       <c r="Z170" s="9"/>
     </row>
     <row r="171" spans="1:26" ht="13.2">
-      <c r="A171" s="45">
+      <c r="A171" s="43">
         <v>166</v>
       </c>
-      <c r="B171" s="46" t="s">
+      <c r="B171" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C171" s="46" t="s">
+      <c r="C171" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="D171" s="46" t="s">
+      <c r="D171" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E171" s="46"/>
-      <c r="F171" s="46"/>
-      <c r="G171" s="46"/>
-      <c r="H171" s="46"/>
-      <c r="I171" s="93"/>
-      <c r="J171" s="46"/>
-      <c r="K171" s="46"/>
-      <c r="L171" s="46"/>
+      <c r="E171" s="44"/>
+      <c r="F171" s="44"/>
+      <c r="G171" s="44"/>
+      <c r="H171" s="44"/>
+      <c r="I171" s="91"/>
+      <c r="J171" s="44"/>
+      <c r="K171" s="44"/>
+      <c r="L171" s="44"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -10329,26 +10329,26 @@
       <c r="Z171" s="2"/>
     </row>
     <row r="172" spans="1:26" ht="13.2">
-      <c r="A172" s="45">
+      <c r="A172" s="43">
         <v>167</v>
       </c>
-      <c r="B172" s="46" t="s">
+      <c r="B172" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C172" s="46" t="s">
+      <c r="C172" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="D172" s="46" t="s">
+      <c r="D172" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E172" s="46"/>
-      <c r="F172" s="46"/>
-      <c r="G172" s="46"/>
-      <c r="H172" s="46"/>
-      <c r="I172" s="93"/>
-      <c r="J172" s="46"/>
-      <c r="K172" s="46"/>
-      <c r="L172" s="46"/>
+      <c r="E172" s="44"/>
+      <c r="F172" s="44"/>
+      <c r="G172" s="44"/>
+      <c r="H172" s="44"/>
+      <c r="I172" s="91"/>
+      <c r="J172" s="44"/>
+      <c r="K172" s="44"/>
+      <c r="L172" s="44"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -10365,26 +10365,26 @@
       <c r="Z172" s="2"/>
     </row>
     <row r="173" spans="1:26" ht="13.2">
-      <c r="A173" s="45">
+      <c r="A173" s="43">
         <v>168</v>
       </c>
-      <c r="B173" s="46" t="s">
+      <c r="B173" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C173" s="46" t="s">
+      <c r="C173" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="D173" s="46" t="s">
+      <c r="D173" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E173" s="46"/>
-      <c r="F173" s="46"/>
-      <c r="G173" s="46"/>
-      <c r="H173" s="46"/>
-      <c r="I173" s="93"/>
-      <c r="J173" s="46"/>
-      <c r="K173" s="46"/>
-      <c r="L173" s="46"/>
+      <c r="E173" s="44"/>
+      <c r="F173" s="44"/>
+      <c r="G173" s="44"/>
+      <c r="H173" s="44"/>
+      <c r="I173" s="91"/>
+      <c r="J173" s="44"/>
+      <c r="K173" s="44"/>
+      <c r="L173" s="44"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -10401,26 +10401,26 @@
       <c r="Z173" s="2"/>
     </row>
     <row r="174" spans="1:26" ht="13.2">
-      <c r="A174" s="45">
+      <c r="A174" s="43">
         <v>169</v>
       </c>
-      <c r="B174" s="46" t="s">
+      <c r="B174" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C174" s="46" t="s">
+      <c r="C174" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="D174" s="46" t="s">
+      <c r="D174" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E174" s="46"/>
-      <c r="F174" s="46"/>
-      <c r="G174" s="46"/>
-      <c r="H174" s="46"/>
-      <c r="I174" s="93"/>
-      <c r="J174" s="46"/>
-      <c r="K174" s="46"/>
-      <c r="L174" s="46"/>
+      <c r="E174" s="44"/>
+      <c r="F174" s="44"/>
+      <c r="G174" s="44"/>
+      <c r="H174" s="44"/>
+      <c r="I174" s="91"/>
+      <c r="J174" s="44"/>
+      <c r="K174" s="44"/>
+      <c r="L174" s="44"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -10437,26 +10437,26 @@
       <c r="Z174" s="2"/>
     </row>
     <row r="175" spans="1:26" ht="13.2">
-      <c r="A175" s="45">
+      <c r="A175" s="43">
         <v>170</v>
       </c>
-      <c r="B175" s="46" t="s">
+      <c r="B175" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C175" s="46" t="s">
+      <c r="C175" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="D175" s="46" t="s">
+      <c r="D175" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E175" s="46"/>
-      <c r="F175" s="46"/>
-      <c r="G175" s="46"/>
-      <c r="H175" s="46"/>
-      <c r="I175" s="93"/>
-      <c r="J175" s="46"/>
-      <c r="K175" s="46"/>
-      <c r="L175" s="46"/>
+      <c r="E175" s="44"/>
+      <c r="F175" s="44"/>
+      <c r="G175" s="44"/>
+      <c r="H175" s="44"/>
+      <c r="I175" s="91"/>
+      <c r="J175" s="44"/>
+      <c r="K175" s="44"/>
+      <c r="L175" s="44"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -10473,26 +10473,26 @@
       <c r="Z175" s="2"/>
     </row>
     <row r="176" spans="1:26" ht="13.2">
-      <c r="A176" s="45">
+      <c r="A176" s="43">
         <v>171</v>
       </c>
-      <c r="B176" s="46" t="s">
+      <c r="B176" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C176" s="46" t="s">
+      <c r="C176" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="D176" s="46" t="s">
+      <c r="D176" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E176" s="46"/>
-      <c r="F176" s="46"/>
-      <c r="G176" s="46"/>
-      <c r="H176" s="46"/>
-      <c r="I176" s="93"/>
-      <c r="J176" s="46"/>
-      <c r="K176" s="46"/>
-      <c r="L176" s="46"/>
+      <c r="E176" s="44"/>
+      <c r="F176" s="44"/>
+      <c r="G176" s="44"/>
+      <c r="H176" s="44"/>
+      <c r="I176" s="91"/>
+      <c r="J176" s="44"/>
+      <c r="K176" s="44"/>
+      <c r="L176" s="44"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -10509,26 +10509,26 @@
       <c r="Z176" s="2"/>
     </row>
     <row r="177" spans="1:26" ht="13.2">
-      <c r="A177" s="45">
+      <c r="A177" s="43">
         <v>172</v>
       </c>
-      <c r="B177" s="72" t="s">
+      <c r="B177" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C177" s="72" t="s">
+      <c r="C177" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="D177" s="72" t="s">
+      <c r="D177" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E177" s="72"/>
-      <c r="F177" s="72"/>
-      <c r="G177" s="72"/>
-      <c r="H177" s="72"/>
-      <c r="I177" s="97"/>
-      <c r="J177" s="72"/>
-      <c r="K177" s="72"/>
-      <c r="L177" s="72"/>
+      <c r="E177" s="70"/>
+      <c r="F177" s="70"/>
+      <c r="G177" s="70"/>
+      <c r="H177" s="70"/>
+      <c r="I177" s="95"/>
+      <c r="J177" s="70"/>
+      <c r="K177" s="70"/>
+      <c r="L177" s="70"/>
       <c r="M177" s="9"/>
       <c r="N177" s="9"/>
       <c r="O177" s="9"/>
@@ -10545,26 +10545,26 @@
       <c r="Z177" s="9"/>
     </row>
     <row r="178" spans="1:26" ht="13.2">
-      <c r="A178" s="45">
+      <c r="A178" s="43">
         <v>173</v>
       </c>
-      <c r="B178" s="72" t="s">
+      <c r="B178" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C178" s="72" t="s">
+      <c r="C178" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="D178" s="72" t="s">
+      <c r="D178" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E178" s="72"/>
-      <c r="F178" s="72"/>
-      <c r="G178" s="72"/>
-      <c r="H178" s="72"/>
-      <c r="I178" s="97"/>
-      <c r="J178" s="72"/>
-      <c r="K178" s="72"/>
-      <c r="L178" s="72"/>
+      <c r="E178" s="70"/>
+      <c r="F178" s="70"/>
+      <c r="G178" s="70"/>
+      <c r="H178" s="70"/>
+      <c r="I178" s="95"/>
+      <c r="J178" s="70"/>
+      <c r="K178" s="70"/>
+      <c r="L178" s="70"/>
       <c r="M178" s="9"/>
       <c r="N178" s="9"/>
       <c r="O178" s="9"/>
@@ -10581,26 +10581,26 @@
       <c r="Z178" s="9"/>
     </row>
     <row r="179" spans="1:26" ht="13.2">
-      <c r="A179" s="45">
+      <c r="A179" s="43">
         <v>174</v>
       </c>
-      <c r="B179" s="46" t="s">
+      <c r="B179" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C179" s="46" t="s">
+      <c r="C179" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="D179" s="46" t="s">
+      <c r="D179" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E179" s="46"/>
-      <c r="F179" s="46"/>
-      <c r="G179" s="46"/>
-      <c r="H179" s="46"/>
-      <c r="I179" s="93"/>
-      <c r="J179" s="46"/>
-      <c r="K179" s="46"/>
-      <c r="L179" s="46"/>
+      <c r="E179" s="44"/>
+      <c r="F179" s="44"/>
+      <c r="G179" s="44"/>
+      <c r="H179" s="44"/>
+      <c r="I179" s="91"/>
+      <c r="J179" s="44"/>
+      <c r="K179" s="44"/>
+      <c r="L179" s="44"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -10617,26 +10617,26 @@
       <c r="Z179" s="2"/>
     </row>
     <row r="180" spans="1:26" ht="13.2">
-      <c r="A180" s="45">
+      <c r="A180" s="43">
         <v>175</v>
       </c>
-      <c r="B180" s="72" t="s">
+      <c r="B180" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C180" s="72" t="s">
+      <c r="C180" s="70" t="s">
         <v>210</v>
       </c>
-      <c r="D180" s="72" t="s">
+      <c r="D180" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E180" s="72"/>
-      <c r="F180" s="72"/>
-      <c r="G180" s="72"/>
-      <c r="H180" s="72"/>
-      <c r="I180" s="97"/>
-      <c r="J180" s="72"/>
-      <c r="K180" s="72"/>
-      <c r="L180" s="72"/>
+      <c r="E180" s="70"/>
+      <c r="F180" s="70"/>
+      <c r="G180" s="70"/>
+      <c r="H180" s="70"/>
+      <c r="I180" s="95"/>
+      <c r="J180" s="70"/>
+      <c r="K180" s="70"/>
+      <c r="L180" s="70"/>
       <c r="M180" s="9"/>
       <c r="N180" s="9"/>
       <c r="O180" s="9"/>
@@ -10653,24 +10653,24 @@
       <c r="Z180" s="9"/>
     </row>
     <row r="181" spans="1:26" ht="13.2">
-      <c r="A181" s="45">
+      <c r="A181" s="43">
         <v>176</v>
       </c>
-      <c r="B181" s="46" t="s">
+      <c r="B181" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C181" s="46" t="s">
+      <c r="C181" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="D181" s="46"/>
-      <c r="E181" s="46"/>
-      <c r="F181" s="46"/>
-      <c r="G181" s="46"/>
-      <c r="H181" s="46"/>
-      <c r="I181" s="93"/>
-      <c r="J181" s="46"/>
-      <c r="K181" s="46"/>
-      <c r="L181" s="46"/>
+      <c r="D181" s="44"/>
+      <c r="E181" s="44"/>
+      <c r="F181" s="44"/>
+      <c r="G181" s="44"/>
+      <c r="H181" s="44"/>
+      <c r="I181" s="91"/>
+      <c r="J181" s="44"/>
+      <c r="K181" s="44"/>
+      <c r="L181" s="44"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -10687,24 +10687,24 @@
       <c r="Z181" s="2"/>
     </row>
     <row r="182" spans="1:26" ht="13.2">
-      <c r="A182" s="45">
+      <c r="A182" s="43">
         <v>177</v>
       </c>
-      <c r="B182" s="46" t="s">
+      <c r="B182" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C182" s="46" t="s">
+      <c r="C182" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="D182" s="46"/>
-      <c r="E182" s="46"/>
-      <c r="F182" s="46"/>
-      <c r="G182" s="46"/>
-      <c r="H182" s="46"/>
-      <c r="I182" s="93"/>
-      <c r="J182" s="46"/>
-      <c r="K182" s="46"/>
-      <c r="L182" s="46"/>
+      <c r="D182" s="44"/>
+      <c r="E182" s="44"/>
+      <c r="F182" s="44"/>
+      <c r="G182" s="44"/>
+      <c r="H182" s="44"/>
+      <c r="I182" s="91"/>
+      <c r="J182" s="44"/>
+      <c r="K182" s="44"/>
+      <c r="L182" s="44"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -10721,26 +10721,26 @@
       <c r="Z182" s="2"/>
     </row>
     <row r="183" spans="1:26" ht="13.2">
-      <c r="A183" s="45">
+      <c r="A183" s="43">
         <v>178</v>
       </c>
-      <c r="B183" s="72" t="s">
+      <c r="B183" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C183" s="72" t="s">
+      <c r="C183" s="70" t="s">
         <v>213</v>
       </c>
-      <c r="D183" s="72" t="s">
+      <c r="D183" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E183" s="72"/>
-      <c r="F183" s="72"/>
-      <c r="G183" s="72"/>
-      <c r="H183" s="72"/>
-      <c r="I183" s="97"/>
-      <c r="J183" s="72"/>
-      <c r="K183" s="72"/>
-      <c r="L183" s="72"/>
+      <c r="E183" s="70"/>
+      <c r="F183" s="70"/>
+      <c r="G183" s="70"/>
+      <c r="H183" s="70"/>
+      <c r="I183" s="95"/>
+      <c r="J183" s="70"/>
+      <c r="K183" s="70"/>
+      <c r="L183" s="70"/>
       <c r="M183" s="9"/>
       <c r="N183" s="9"/>
       <c r="O183" s="9"/>
@@ -10757,24 +10757,24 @@
       <c r="Z183" s="9"/>
     </row>
     <row r="184" spans="1:26" ht="13.2">
-      <c r="A184" s="45">
+      <c r="A184" s="43">
         <v>179</v>
       </c>
-      <c r="B184" s="46" t="s">
+      <c r="B184" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C184" s="46" t="s">
+      <c r="C184" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="D184" s="46"/>
-      <c r="E184" s="46"/>
-      <c r="F184" s="46"/>
-      <c r="G184" s="46"/>
-      <c r="H184" s="46"/>
-      <c r="I184" s="93"/>
-      <c r="J184" s="46"/>
-      <c r="K184" s="46"/>
-      <c r="L184" s="46"/>
+      <c r="D184" s="44"/>
+      <c r="E184" s="44"/>
+      <c r="F184" s="44"/>
+      <c r="G184" s="44"/>
+      <c r="H184" s="44"/>
+      <c r="I184" s="91"/>
+      <c r="J184" s="44"/>
+      <c r="K184" s="44"/>
+      <c r="L184" s="44"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -10791,26 +10791,26 @@
       <c r="Z184" s="2"/>
     </row>
     <row r="185" spans="1:26" ht="13.2">
-      <c r="A185" s="45">
+      <c r="A185" s="43">
         <v>180</v>
       </c>
-      <c r="B185" s="72" t="s">
+      <c r="B185" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C185" s="72" t="s">
+      <c r="C185" s="70" t="s">
         <v>215</v>
       </c>
-      <c r="D185" s="72" t="s">
+      <c r="D185" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E185" s="72"/>
-      <c r="F185" s="72"/>
-      <c r="G185" s="72"/>
-      <c r="H185" s="72"/>
-      <c r="I185" s="97"/>
-      <c r="J185" s="72"/>
-      <c r="K185" s="72"/>
-      <c r="L185" s="72"/>
+      <c r="E185" s="70"/>
+      <c r="F185" s="70"/>
+      <c r="G185" s="70"/>
+      <c r="H185" s="70"/>
+      <c r="I185" s="95"/>
+      <c r="J185" s="70"/>
+      <c r="K185" s="70"/>
+      <c r="L185" s="70"/>
       <c r="M185" s="9"/>
       <c r="N185" s="9"/>
       <c r="O185" s="9"/>
@@ -10827,26 +10827,26 @@
       <c r="Z185" s="9"/>
     </row>
     <row r="186" spans="1:26" ht="13.2">
-      <c r="A186" s="45">
+      <c r="A186" s="43">
         <v>181</v>
       </c>
-      <c r="B186" s="72" t="s">
+      <c r="B186" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="C186" s="72" t="s">
+      <c r="C186" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="D186" s="72" t="s">
+      <c r="D186" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="E186" s="72"/>
-      <c r="F186" s="72"/>
-      <c r="G186" s="72"/>
-      <c r="H186" s="72"/>
-      <c r="I186" s="97"/>
-      <c r="J186" s="72"/>
-      <c r="K186" s="72"/>
-      <c r="L186" s="72"/>
+      <c r="E186" s="70"/>
+      <c r="F186" s="70"/>
+      <c r="G186" s="70"/>
+      <c r="H186" s="70"/>
+      <c r="I186" s="95"/>
+      <c r="J186" s="70"/>
+      <c r="K186" s="70"/>
+      <c r="L186" s="70"/>
       <c r="M186" s="9"/>
       <c r="N186" s="9"/>
       <c r="O186" s="9"/>
@@ -10863,24 +10863,24 @@
       <c r="Z186" s="9"/>
     </row>
     <row r="187" spans="1:26" ht="13.2">
-      <c r="A187" s="45">
+      <c r="A187" s="43">
         <v>182</v>
       </c>
-      <c r="B187" s="46" t="s">
+      <c r="B187" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C187" s="46" t="s">
+      <c r="C187" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="D187" s="46"/>
-      <c r="E187" s="46"/>
-      <c r="F187" s="46"/>
-      <c r="G187" s="46"/>
-      <c r="H187" s="46"/>
-      <c r="I187" s="93"/>
-      <c r="J187" s="46"/>
-      <c r="K187" s="46"/>
-      <c r="L187" s="46"/>
+      <c r="D187" s="44"/>
+      <c r="E187" s="44"/>
+      <c r="F187" s="44"/>
+      <c r="G187" s="44"/>
+      <c r="H187" s="44"/>
+      <c r="I187" s="91"/>
+      <c r="J187" s="44"/>
+      <c r="K187" s="44"/>
+      <c r="L187" s="44"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -10897,24 +10897,24 @@
       <c r="Z187" s="2"/>
     </row>
     <row r="188" spans="1:26" ht="13.2">
-      <c r="A188" s="45">
+      <c r="A188" s="43">
         <v>183</v>
       </c>
-      <c r="B188" s="46" t="s">
+      <c r="B188" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C188" s="46" t="s">
+      <c r="C188" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="D188" s="46"/>
-      <c r="E188" s="46"/>
-      <c r="F188" s="46"/>
-      <c r="G188" s="46"/>
-      <c r="H188" s="46"/>
-      <c r="I188" s="93"/>
-      <c r="J188" s="46"/>
-      <c r="K188" s="46"/>
-      <c r="L188" s="46"/>
+      <c r="D188" s="44"/>
+      <c r="E188" s="44"/>
+      <c r="F188" s="44"/>
+      <c r="G188" s="44"/>
+      <c r="H188" s="44"/>
+      <c r="I188" s="91"/>
+      <c r="J188" s="44"/>
+      <c r="K188" s="44"/>
+      <c r="L188" s="44"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -10931,24 +10931,24 @@
       <c r="Z188" s="2"/>
     </row>
     <row r="189" spans="1:26" ht="13.2">
-      <c r="A189" s="45">
+      <c r="A189" s="43">
         <v>184</v>
       </c>
-      <c r="B189" s="46" t="s">
+      <c r="B189" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C189" s="46" t="s">
+      <c r="C189" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="D189" s="46"/>
-      <c r="E189" s="46"/>
-      <c r="F189" s="46"/>
-      <c r="G189" s="46"/>
-      <c r="H189" s="46"/>
-      <c r="I189" s="93"/>
-      <c r="J189" s="46"/>
-      <c r="K189" s="46"/>
-      <c r="L189" s="46"/>
+      <c r="D189" s="44"/>
+      <c r="E189" s="44"/>
+      <c r="F189" s="44"/>
+      <c r="G189" s="44"/>
+      <c r="H189" s="44"/>
+      <c r="I189" s="91"/>
+      <c r="J189" s="44"/>
+      <c r="K189" s="44"/>
+      <c r="L189" s="44"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -10965,24 +10965,24 @@
       <c r="Z189" s="2"/>
     </row>
     <row r="190" spans="1:26" ht="13.2">
-      <c r="A190" s="45">
+      <c r="A190" s="43">
         <v>185</v>
       </c>
-      <c r="B190" s="72" t="s">
+      <c r="B190" s="70" t="s">
         <v>137</v>
       </c>
-      <c r="C190" s="72" t="s">
+      <c r="C190" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="D190" s="72"/>
-      <c r="E190" s="72"/>
-      <c r="F190" s="72"/>
-      <c r="G190" s="72"/>
-      <c r="H190" s="72"/>
-      <c r="I190" s="97"/>
-      <c r="J190" s="72"/>
-      <c r="K190" s="72"/>
-      <c r="L190" s="72"/>
+      <c r="D190" s="70"/>
+      <c r="E190" s="70"/>
+      <c r="F190" s="70"/>
+      <c r="G190" s="70"/>
+      <c r="H190" s="70"/>
+      <c r="I190" s="95"/>
+      <c r="J190" s="70"/>
+      <c r="K190" s="70"/>
+      <c r="L190" s="70"/>
       <c r="M190" s="9"/>
       <c r="N190" s="9"/>
       <c r="O190" s="9"/>
@@ -10999,24 +10999,24 @@
       <c r="Z190" s="9"/>
     </row>
     <row r="191" spans="1:26" ht="13.2">
-      <c r="A191" s="45">
+      <c r="A191" s="43">
         <v>186</v>
       </c>
-      <c r="B191" s="46" t="s">
+      <c r="B191" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="46" t="s">
+      <c r="C191" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="D191" s="46"/>
-      <c r="E191" s="46"/>
-      <c r="F191" s="46"/>
-      <c r="G191" s="46"/>
-      <c r="H191" s="46"/>
-      <c r="I191" s="93"/>
-      <c r="J191" s="46"/>
-      <c r="K191" s="46"/>
-      <c r="L191" s="46"/>
+      <c r="D191" s="44"/>
+      <c r="E191" s="44"/>
+      <c r="F191" s="44"/>
+      <c r="G191" s="44"/>
+      <c r="H191" s="44"/>
+      <c r="I191" s="91"/>
+      <c r="J191" s="44"/>
+      <c r="K191" s="44"/>
+      <c r="L191" s="44"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -11033,24 +11033,24 @@
       <c r="Z191" s="2"/>
     </row>
     <row r="192" spans="1:26" ht="13.2">
-      <c r="A192" s="45">
+      <c r="A192" s="43">
         <v>187</v>
       </c>
-      <c r="B192" s="46" t="s">
+      <c r="B192" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C192" s="46" t="s">
+      <c r="C192" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="D192" s="46"/>
-      <c r="E192" s="46"/>
-      <c r="F192" s="46"/>
-      <c r="G192" s="46"/>
-      <c r="H192" s="46"/>
-      <c r="I192" s="93"/>
-      <c r="J192" s="46"/>
-      <c r="K192" s="46"/>
-      <c r="L192" s="46"/>
+      <c r="D192" s="44"/>
+      <c r="E192" s="44"/>
+      <c r="F192" s="44"/>
+      <c r="G192" s="44"/>
+      <c r="H192" s="44"/>
+      <c r="I192" s="91"/>
+      <c r="J192" s="44"/>
+      <c r="K192" s="44"/>
+      <c r="L192" s="44"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -11067,26 +11067,26 @@
       <c r="Z192" s="2"/>
     </row>
     <row r="193" spans="1:26" ht="13.2">
-      <c r="A193" s="45">
+      <c r="A193" s="43">
         <v>188</v>
       </c>
-      <c r="B193" s="46" t="s">
+      <c r="B193" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C193" s="46" t="s">
+      <c r="C193" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="D193" s="46" t="s">
+      <c r="D193" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E193" s="46"/>
-      <c r="F193" s="46"/>
-      <c r="G193" s="46"/>
-      <c r="H193" s="46"/>
-      <c r="I193" s="93"/>
-      <c r="J193" s="46"/>
-      <c r="K193" s="46"/>
-      <c r="L193" s="46"/>
+      <c r="E193" s="44"/>
+      <c r="F193" s="44"/>
+      <c r="G193" s="44"/>
+      <c r="H193" s="44"/>
+      <c r="I193" s="91"/>
+      <c r="J193" s="44"/>
+      <c r="K193" s="44"/>
+      <c r="L193" s="44"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -11103,24 +11103,24 @@
       <c r="Z193" s="2"/>
     </row>
     <row r="194" spans="1:26" ht="13.2">
-      <c r="A194" s="45">
+      <c r="A194" s="43">
         <v>189</v>
       </c>
-      <c r="B194" s="46" t="s">
+      <c r="B194" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C194" s="46" t="s">
+      <c r="C194" s="44" t="s">
         <v>224</v>
       </c>
-      <c r="D194" s="46"/>
-      <c r="E194" s="46"/>
-      <c r="F194" s="46"/>
-      <c r="G194" s="46"/>
-      <c r="H194" s="46"/>
-      <c r="I194" s="93"/>
-      <c r="J194" s="46"/>
-      <c r="K194" s="46"/>
-      <c r="L194" s="46"/>
+      <c r="D194" s="44"/>
+      <c r="E194" s="44"/>
+      <c r="F194" s="44"/>
+      <c r="G194" s="44"/>
+      <c r="H194" s="44"/>
+      <c r="I194" s="91"/>
+      <c r="J194" s="44"/>
+      <c r="K194" s="44"/>
+      <c r="L194" s="44"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -11137,24 +11137,24 @@
       <c r="Z194" s="2"/>
     </row>
     <row r="195" spans="1:26" ht="13.2">
-      <c r="A195" s="45">
+      <c r="A195" s="43">
         <v>190</v>
       </c>
-      <c r="B195" s="46" t="s">
+      <c r="B195" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C195" s="46" t="s">
+      <c r="C195" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="D195" s="46"/>
-      <c r="E195" s="46"/>
-      <c r="F195" s="46"/>
-      <c r="G195" s="46"/>
-      <c r="H195" s="46"/>
-      <c r="I195" s="93"/>
-      <c r="J195" s="46"/>
-      <c r="K195" s="46"/>
-      <c r="L195" s="46"/>
+      <c r="D195" s="44"/>
+      <c r="E195" s="44"/>
+      <c r="F195" s="44"/>
+      <c r="G195" s="44"/>
+      <c r="H195" s="44"/>
+      <c r="I195" s="91"/>
+      <c r="J195" s="44"/>
+      <c r="K195" s="44"/>
+      <c r="L195" s="44"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -11171,24 +11171,24 @@
       <c r="Z195" s="2"/>
     </row>
     <row r="196" spans="1:26" ht="13.2">
-      <c r="A196" s="45">
+      <c r="A196" s="43">
         <v>191</v>
       </c>
-      <c r="B196" s="46" t="s">
+      <c r="B196" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C196" s="46" t="s">
+      <c r="C196" s="44" t="s">
         <v>226</v>
       </c>
-      <c r="D196" s="46"/>
-      <c r="E196" s="46"/>
-      <c r="F196" s="46"/>
-      <c r="G196" s="46"/>
-      <c r="H196" s="46"/>
-      <c r="I196" s="93"/>
-      <c r="J196" s="46"/>
-      <c r="K196" s="46"/>
-      <c r="L196" s="46"/>
+      <c r="D196" s="44"/>
+      <c r="E196" s="44"/>
+      <c r="F196" s="44"/>
+      <c r="G196" s="44"/>
+      <c r="H196" s="44"/>
+      <c r="I196" s="91"/>
+      <c r="J196" s="44"/>
+      <c r="K196" s="44"/>
+      <c r="L196" s="44"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -11205,26 +11205,26 @@
       <c r="Z196" s="2"/>
     </row>
     <row r="197" spans="1:26" ht="13.2">
-      <c r="A197" s="45">
+      <c r="A197" s="43">
         <v>192</v>
       </c>
-      <c r="B197" s="84" t="s">
+      <c r="B197" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="C197" s="84" t="s">
+      <c r="C197" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="D197" s="84" t="s">
+      <c r="D197" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E197" s="84"/>
-      <c r="F197" s="84"/>
-      <c r="G197" s="84"/>
-      <c r="H197" s="84"/>
-      <c r="I197" s="98"/>
-      <c r="J197" s="84"/>
-      <c r="K197" s="84"/>
-      <c r="L197" s="84"/>
+      <c r="E197" s="82"/>
+      <c r="F197" s="82"/>
+      <c r="G197" s="82"/>
+      <c r="H197" s="82"/>
+      <c r="I197" s="96"/>
+      <c r="J197" s="82"/>
+      <c r="K197" s="82"/>
+      <c r="L197" s="82"/>
       <c r="M197" s="10"/>
       <c r="N197" s="10"/>
       <c r="O197" s="10"/>
@@ -11241,24 +11241,24 @@
       <c r="Z197" s="10"/>
     </row>
     <row r="198" spans="1:26" ht="13.2">
-      <c r="A198" s="45">
+      <c r="A198" s="43">
         <v>193</v>
       </c>
-      <c r="B198" s="46" t="s">
+      <c r="B198" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C198" s="46" t="s">
+      <c r="C198" s="44" t="s">
         <v>228</v>
       </c>
-      <c r="D198" s="46"/>
-      <c r="E198" s="46"/>
-      <c r="F198" s="46"/>
-      <c r="G198" s="46"/>
-      <c r="H198" s="46"/>
-      <c r="I198" s="93"/>
-      <c r="J198" s="46"/>
-      <c r="K198" s="46"/>
-      <c r="L198" s="46"/>
+      <c r="D198" s="44"/>
+      <c r="E198" s="44"/>
+      <c r="F198" s="44"/>
+      <c r="G198" s="44"/>
+      <c r="H198" s="44"/>
+      <c r="I198" s="91"/>
+      <c r="J198" s="44"/>
+      <c r="K198" s="44"/>
+      <c r="L198" s="44"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -11275,24 +11275,24 @@
       <c r="Z198" s="2"/>
     </row>
     <row r="199" spans="1:26" ht="13.2">
-      <c r="A199" s="45">
+      <c r="A199" s="43">
         <v>194</v>
       </c>
-      <c r="B199" s="46" t="s">
+      <c r="B199" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C199" s="46" t="s">
+      <c r="C199" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="D199" s="46"/>
-      <c r="E199" s="46"/>
-      <c r="F199" s="46"/>
-      <c r="G199" s="46"/>
-      <c r="H199" s="46"/>
-      <c r="I199" s="93"/>
-      <c r="J199" s="46"/>
-      <c r="K199" s="46"/>
-      <c r="L199" s="46"/>
+      <c r="D199" s="44"/>
+      <c r="E199" s="44"/>
+      <c r="F199" s="44"/>
+      <c r="G199" s="44"/>
+      <c r="H199" s="44"/>
+      <c r="I199" s="91"/>
+      <c r="J199" s="44"/>
+      <c r="K199" s="44"/>
+      <c r="L199" s="44"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -11309,24 +11309,24 @@
       <c r="Z199" s="2"/>
     </row>
     <row r="200" spans="1:26" ht="13.2">
-      <c r="A200" s="45">
+      <c r="A200" s="43">
         <v>195</v>
       </c>
-      <c r="B200" s="46" t="s">
+      <c r="B200" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C200" s="46" t="s">
+      <c r="C200" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="D200" s="46"/>
-      <c r="E200" s="46"/>
-      <c r="F200" s="46"/>
-      <c r="G200" s="46"/>
-      <c r="H200" s="46"/>
-      <c r="I200" s="93"/>
-      <c r="J200" s="46"/>
-      <c r="K200" s="46"/>
-      <c r="L200" s="46"/>
+      <c r="D200" s="44"/>
+      <c r="E200" s="44"/>
+      <c r="F200" s="44"/>
+      <c r="G200" s="44"/>
+      <c r="H200" s="44"/>
+      <c r="I200" s="91"/>
+      <c r="J200" s="44"/>
+      <c r="K200" s="44"/>
+      <c r="L200" s="44"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -11343,24 +11343,24 @@
       <c r="Z200" s="2"/>
     </row>
     <row r="201" spans="1:26" ht="13.2">
-      <c r="A201" s="45">
+      <c r="A201" s="43">
         <v>196</v>
       </c>
-      <c r="B201" s="46" t="s">
+      <c r="B201" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C201" s="46" t="s">
+      <c r="C201" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="D201" s="46"/>
-      <c r="E201" s="46"/>
-      <c r="F201" s="46"/>
-      <c r="G201" s="46"/>
-      <c r="H201" s="46"/>
-      <c r="I201" s="93"/>
-      <c r="J201" s="46"/>
-      <c r="K201" s="46"/>
-      <c r="L201" s="46"/>
+      <c r="D201" s="44"/>
+      <c r="E201" s="44"/>
+      <c r="F201" s="44"/>
+      <c r="G201" s="44"/>
+      <c r="H201" s="44"/>
+      <c r="I201" s="91"/>
+      <c r="J201" s="44"/>
+      <c r="K201" s="44"/>
+      <c r="L201" s="44"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -11377,24 +11377,24 @@
       <c r="Z201" s="2"/>
     </row>
     <row r="202" spans="1:26" ht="13.2">
-      <c r="A202" s="45">
+      <c r="A202" s="43">
         <v>197</v>
       </c>
-      <c r="B202" s="46" t="s">
+      <c r="B202" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C202" s="46" t="s">
+      <c r="C202" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="D202" s="46"/>
-      <c r="E202" s="46"/>
-      <c r="F202" s="46"/>
-      <c r="G202" s="46"/>
-      <c r="H202" s="46"/>
-      <c r="I202" s="93"/>
-      <c r="J202" s="46"/>
-      <c r="K202" s="46"/>
-      <c r="L202" s="46"/>
+      <c r="D202" s="44"/>
+      <c r="E202" s="44"/>
+      <c r="F202" s="44"/>
+      <c r="G202" s="44"/>
+      <c r="H202" s="44"/>
+      <c r="I202" s="91"/>
+      <c r="J202" s="44"/>
+      <c r="K202" s="44"/>
+      <c r="L202" s="44"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -11411,24 +11411,24 @@
       <c r="Z202" s="2"/>
     </row>
     <row r="203" spans="1:26" ht="13.2">
-      <c r="A203" s="45">
+      <c r="A203" s="43">
         <v>198</v>
       </c>
-      <c r="B203" s="46" t="s">
+      <c r="B203" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C203" s="46" t="s">
+      <c r="C203" s="44" t="s">
         <v>233</v>
       </c>
-      <c r="D203" s="46"/>
-      <c r="E203" s="46"/>
-      <c r="F203" s="46"/>
-      <c r="G203" s="46"/>
-      <c r="H203" s="46"/>
-      <c r="I203" s="93"/>
-      <c r="J203" s="46"/>
-      <c r="K203" s="46"/>
-      <c r="L203" s="46"/>
+      <c r="D203" s="44"/>
+      <c r="E203" s="44"/>
+      <c r="F203" s="44"/>
+      <c r="G203" s="44"/>
+      <c r="H203" s="44"/>
+      <c r="I203" s="91"/>
+      <c r="J203" s="44"/>
+      <c r="K203" s="44"/>
+      <c r="L203" s="44"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -11445,24 +11445,24 @@
       <c r="Z203" s="2"/>
     </row>
     <row r="204" spans="1:26" ht="13.2">
-      <c r="A204" s="45">
+      <c r="A204" s="43">
         <v>199</v>
       </c>
-      <c r="B204" s="46" t="s">
+      <c r="B204" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C204" s="46" t="s">
+      <c r="C204" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="D204" s="46"/>
-      <c r="E204" s="46"/>
-      <c r="F204" s="46"/>
-      <c r="G204" s="46"/>
-      <c r="H204" s="46"/>
-      <c r="I204" s="93"/>
-      <c r="J204" s="46"/>
-      <c r="K204" s="46"/>
-      <c r="L204" s="46"/>
+      <c r="D204" s="44"/>
+      <c r="E204" s="44"/>
+      <c r="F204" s="44"/>
+      <c r="G204" s="44"/>
+      <c r="H204" s="44"/>
+      <c r="I204" s="91"/>
+      <c r="J204" s="44"/>
+      <c r="K204" s="44"/>
+      <c r="L204" s="44"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -11479,24 +11479,24 @@
       <c r="Z204" s="2"/>
     </row>
     <row r="205" spans="1:26" ht="13.2">
-      <c r="A205" s="45">
+      <c r="A205" s="43">
         <v>200</v>
       </c>
-      <c r="B205" s="46" t="s">
+      <c r="B205" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C205" s="46" t="s">
+      <c r="C205" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="D205" s="46"/>
-      <c r="E205" s="46"/>
-      <c r="F205" s="46"/>
-      <c r="G205" s="46"/>
-      <c r="H205" s="46"/>
-      <c r="I205" s="93"/>
-      <c r="J205" s="46"/>
-      <c r="K205" s="46"/>
-      <c r="L205" s="46"/>
+      <c r="D205" s="44"/>
+      <c r="E205" s="44"/>
+      <c r="F205" s="44"/>
+      <c r="G205" s="44"/>
+      <c r="H205" s="44"/>
+      <c r="I205" s="91"/>
+      <c r="J205" s="44"/>
+      <c r="K205" s="44"/>
+      <c r="L205" s="44"/>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -11513,24 +11513,24 @@
       <c r="Z205" s="2"/>
     </row>
     <row r="206" spans="1:26" ht="13.2">
-      <c r="A206" s="45">
+      <c r="A206" s="43">
         <v>201</v>
       </c>
-      <c r="B206" s="46" t="s">
+      <c r="B206" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C206" s="46" t="s">
+      <c r="C206" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="D206" s="46"/>
-      <c r="E206" s="46"/>
-      <c r="F206" s="46"/>
-      <c r="G206" s="46"/>
-      <c r="H206" s="46"/>
-      <c r="I206" s="93"/>
-      <c r="J206" s="46"/>
-      <c r="K206" s="46"/>
-      <c r="L206" s="46"/>
+      <c r="D206" s="44"/>
+      <c r="E206" s="44"/>
+      <c r="F206" s="44"/>
+      <c r="G206" s="44"/>
+      <c r="H206" s="44"/>
+      <c r="I206" s="91"/>
+      <c r="J206" s="44"/>
+      <c r="K206" s="44"/>
+      <c r="L206" s="44"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -11547,24 +11547,24 @@
       <c r="Z206" s="2"/>
     </row>
     <row r="207" spans="1:26" ht="13.2">
-      <c r="A207" s="45">
+      <c r="A207" s="43">
         <v>202</v>
       </c>
-      <c r="B207" s="46" t="s">
+      <c r="B207" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C207" s="46" t="s">
+      <c r="C207" s="44" t="s">
         <v>237</v>
       </c>
-      <c r="D207" s="46"/>
-      <c r="E207" s="46"/>
-      <c r="F207" s="46"/>
-      <c r="G207" s="46"/>
-      <c r="H207" s="46"/>
-      <c r="I207" s="93"/>
-      <c r="J207" s="46"/>
-      <c r="K207" s="46"/>
-      <c r="L207" s="46"/>
+      <c r="D207" s="44"/>
+      <c r="E207" s="44"/>
+      <c r="F207" s="44"/>
+      <c r="G207" s="44"/>
+      <c r="H207" s="44"/>
+      <c r="I207" s="91"/>
+      <c r="J207" s="44"/>
+      <c r="K207" s="44"/>
+      <c r="L207" s="44"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -11581,24 +11581,24 @@
       <c r="Z207" s="2"/>
     </row>
     <row r="208" spans="1:26" ht="13.2">
-      <c r="A208" s="45">
+      <c r="A208" s="43">
         <v>203</v>
       </c>
-      <c r="B208" s="46" t="s">
+      <c r="B208" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C208" s="46" t="s">
+      <c r="C208" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="D208" s="46"/>
-      <c r="E208" s="46"/>
-      <c r="F208" s="46"/>
-      <c r="G208" s="46"/>
-      <c r="H208" s="46"/>
-      <c r="I208" s="93"/>
-      <c r="J208" s="46"/>
-      <c r="K208" s="46"/>
-      <c r="L208" s="46"/>
+      <c r="D208" s="44"/>
+      <c r="E208" s="44"/>
+      <c r="F208" s="44"/>
+      <c r="G208" s="44"/>
+      <c r="H208" s="44"/>
+      <c r="I208" s="91"/>
+      <c r="J208" s="44"/>
+      <c r="K208" s="44"/>
+      <c r="L208" s="44"/>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -11615,26 +11615,26 @@
       <c r="Z208" s="2"/>
     </row>
     <row r="209" spans="1:26" ht="13.8">
-      <c r="A209" s="45">
+      <c r="A209" s="43">
         <v>204</v>
       </c>
-      <c r="B209" s="70" t="s">
+      <c r="B209" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="C209" s="85" t="s">
+      <c r="C209" s="83" t="s">
         <v>239</v>
       </c>
-      <c r="D209" s="70" t="s">
+      <c r="D209" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E209" s="70"/>
-      <c r="F209" s="70"/>
-      <c r="G209" s="70"/>
-      <c r="H209" s="70"/>
-      <c r="I209" s="96"/>
-      <c r="J209" s="70"/>
-      <c r="K209" s="70"/>
-      <c r="L209" s="70"/>
+      <c r="E209" s="68"/>
+      <c r="F209" s="68"/>
+      <c r="G209" s="68"/>
+      <c r="H209" s="68"/>
+      <c r="I209" s="94"/>
+      <c r="J209" s="68"/>
+      <c r="K209" s="68"/>
+      <c r="L209" s="68"/>
       <c r="M209" s="8"/>
       <c r="N209" s="8"/>
       <c r="O209" s="8"/>
@@ -11651,26 +11651,26 @@
       <c r="Z209" s="8"/>
     </row>
     <row r="210" spans="1:26" ht="13.8">
-      <c r="A210" s="45">
+      <c r="A210" s="43">
         <v>205</v>
       </c>
-      <c r="B210" s="70" t="s">
+      <c r="B210" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="C210" s="86" t="s">
+      <c r="C210" s="84" t="s">
         <v>240</v>
       </c>
-      <c r="D210" s="70" t="s">
+      <c r="D210" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E210" s="70"/>
-      <c r="F210" s="70"/>
-      <c r="G210" s="70"/>
-      <c r="H210" s="70"/>
-      <c r="I210" s="96"/>
-      <c r="J210" s="70"/>
-      <c r="K210" s="70"/>
-      <c r="L210" s="70"/>
+      <c r="E210" s="68"/>
+      <c r="F210" s="68"/>
+      <c r="G210" s="68"/>
+      <c r="H210" s="68"/>
+      <c r="I210" s="94"/>
+      <c r="J210" s="68"/>
+      <c r="K210" s="68"/>
+      <c r="L210" s="68"/>
       <c r="M210" s="8"/>
       <c r="N210" s="8"/>
       <c r="O210" s="8"/>
@@ -11687,24 +11687,24 @@
       <c r="Z210" s="8"/>
     </row>
     <row r="211" spans="1:26" ht="13.8">
-      <c r="A211" s="45">
+      <c r="A211" s="43">
         <v>206</v>
       </c>
-      <c r="B211" s="70" t="s">
+      <c r="B211" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="C211" s="87" t="s">
+      <c r="C211" s="85" t="s">
         <v>241</v>
       </c>
-      <c r="D211" s="70"/>
-      <c r="E211" s="70"/>
-      <c r="F211" s="70"/>
-      <c r="G211" s="70"/>
-      <c r="H211" s="70"/>
-      <c r="I211" s="96"/>
-      <c r="J211" s="70"/>
-      <c r="K211" s="70"/>
-      <c r="L211" s="70"/>
+      <c r="D211" s="68"/>
+      <c r="E211" s="68"/>
+      <c r="F211" s="68"/>
+      <c r="G211" s="68"/>
+      <c r="H211" s="68"/>
+      <c r="I211" s="94"/>
+      <c r="J211" s="68"/>
+      <c r="K211" s="68"/>
+      <c r="L211" s="68"/>
       <c r="M211" s="8"/>
       <c r="N211" s="8"/>
       <c r="O211" s="8"/>
@@ -11721,26 +11721,26 @@
       <c r="Z211" s="8"/>
     </row>
     <row r="212" spans="1:26" ht="13.8">
-      <c r="A212" s="45">
+      <c r="A212" s="43">
         <v>207</v>
       </c>
-      <c r="B212" s="46" t="s">
+      <c r="B212" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C212" s="88" t="s">
+      <c r="C212" s="86" t="s">
         <v>242</v>
       </c>
-      <c r="D212" s="46" t="s">
+      <c r="D212" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E212" s="46"/>
-      <c r="F212" s="46"/>
-      <c r="G212" s="46"/>
-      <c r="H212" s="46"/>
-      <c r="I212" s="93"/>
-      <c r="J212" s="46"/>
-      <c r="K212" s="46"/>
-      <c r="L212" s="46"/>
+      <c r="E212" s="44"/>
+      <c r="F212" s="44"/>
+      <c r="G212" s="44"/>
+      <c r="H212" s="44"/>
+      <c r="I212" s="91"/>
+      <c r="J212" s="44"/>
+      <c r="K212" s="44"/>
+      <c r="L212" s="44"/>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -11757,24 +11757,24 @@
       <c r="Z212" s="2"/>
     </row>
     <row r="213" spans="1:26" ht="13.8">
-      <c r="A213" s="45">
+      <c r="A213" s="43">
         <v>208</v>
       </c>
-      <c r="B213" s="46" t="s">
+      <c r="B213" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C213" s="65" t="s">
+      <c r="C213" s="63" t="s">
         <v>243</v>
       </c>
-      <c r="D213" s="46"/>
-      <c r="E213" s="46"/>
-      <c r="F213" s="46"/>
-      <c r="G213" s="46"/>
-      <c r="H213" s="46"/>
-      <c r="I213" s="93"/>
-      <c r="J213" s="46"/>
-      <c r="K213" s="46"/>
-      <c r="L213" s="46"/>
+      <c r="D213" s="44"/>
+      <c r="E213" s="44"/>
+      <c r="F213" s="44"/>
+      <c r="G213" s="44"/>
+      <c r="H213" s="44"/>
+      <c r="I213" s="91"/>
+      <c r="J213" s="44"/>
+      <c r="K213" s="44"/>
+      <c r="L213" s="44"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -11791,24 +11791,24 @@
       <c r="Z213" s="2"/>
     </row>
     <row r="214" spans="1:26" ht="13.8">
-      <c r="A214" s="45">
+      <c r="A214" s="43">
         <v>209</v>
       </c>
-      <c r="B214" s="46" t="s">
+      <c r="B214" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C214" s="58" t="s">
+      <c r="C214" s="56" t="s">
         <v>244</v>
       </c>
-      <c r="D214" s="46"/>
-      <c r="E214" s="46"/>
-      <c r="F214" s="46"/>
-      <c r="G214" s="46"/>
-      <c r="H214" s="46"/>
-      <c r="I214" s="93"/>
-      <c r="J214" s="46"/>
-      <c r="K214" s="46"/>
-      <c r="L214" s="46"/>
+      <c r="D214" s="44"/>
+      <c r="E214" s="44"/>
+      <c r="F214" s="44"/>
+      <c r="G214" s="44"/>
+      <c r="H214" s="44"/>
+      <c r="I214" s="91"/>
+      <c r="J214" s="44"/>
+      <c r="K214" s="44"/>
+      <c r="L214" s="44"/>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -11825,24 +11825,24 @@
       <c r="Z214" s="2"/>
     </row>
     <row r="215" spans="1:26" ht="13.8">
-      <c r="A215" s="45">
+      <c r="A215" s="43">
         <v>210</v>
       </c>
-      <c r="B215" s="46" t="s">
+      <c r="B215" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C215" s="58" t="s">
+      <c r="C215" s="56" t="s">
         <v>245</v>
       </c>
-      <c r="D215" s="46"/>
-      <c r="E215" s="46"/>
-      <c r="F215" s="46"/>
-      <c r="G215" s="46"/>
-      <c r="H215" s="46"/>
-      <c r="I215" s="93"/>
-      <c r="J215" s="46"/>
-      <c r="K215" s="46"/>
-      <c r="L215" s="46"/>
+      <c r="D215" s="44"/>
+      <c r="E215" s="44"/>
+      <c r="F215" s="44"/>
+      <c r="G215" s="44"/>
+      <c r="H215" s="44"/>
+      <c r="I215" s="91"/>
+      <c r="J215" s="44"/>
+      <c r="K215" s="44"/>
+      <c r="L215" s="44"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -11859,24 +11859,24 @@
       <c r="Z215" s="2"/>
     </row>
     <row r="216" spans="1:26" ht="13.8">
-      <c r="A216" s="45">
+      <c r="A216" s="43">
         <v>211</v>
       </c>
-      <c r="B216" s="70" t="s">
+      <c r="B216" s="68" t="s">
         <v>223</v>
       </c>
-      <c r="C216" s="89" t="s">
+      <c r="C216" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="D216" s="70"/>
-      <c r="E216" s="70"/>
-      <c r="F216" s="70"/>
-      <c r="G216" s="70"/>
-      <c r="H216" s="70"/>
-      <c r="I216" s="96"/>
-      <c r="J216" s="70"/>
-      <c r="K216" s="70"/>
-      <c r="L216" s="70"/>
+      <c r="D216" s="68"/>
+      <c r="E216" s="68"/>
+      <c r="F216" s="68"/>
+      <c r="G216" s="68"/>
+      <c r="H216" s="68"/>
+      <c r="I216" s="94"/>
+      <c r="J216" s="68"/>
+      <c r="K216" s="68"/>
+      <c r="L216" s="68"/>
       <c r="M216" s="8"/>
       <c r="N216" s="8"/>
       <c r="O216" s="8"/>
@@ -11893,24 +11893,24 @@
       <c r="Z216" s="8"/>
     </row>
     <row r="217" spans="1:26" ht="13.8">
-      <c r="A217" s="45">
+      <c r="A217" s="43">
         <v>212</v>
       </c>
-      <c r="B217" s="46" t="s">
+      <c r="B217" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C217" s="74" t="s">
+      <c r="C217" s="72" t="s">
         <v>247</v>
       </c>
-      <c r="D217" s="46"/>
-      <c r="E217" s="46"/>
-      <c r="F217" s="46"/>
-      <c r="G217" s="46"/>
-      <c r="H217" s="46"/>
-      <c r="I217" s="93"/>
-      <c r="J217" s="46"/>
-      <c r="K217" s="46"/>
-      <c r="L217" s="46"/>
+      <c r="D217" s="44"/>
+      <c r="E217" s="44"/>
+      <c r="F217" s="44"/>
+      <c r="G217" s="44"/>
+      <c r="H217" s="44"/>
+      <c r="I217" s="91"/>
+      <c r="J217" s="44"/>
+      <c r="K217" s="44"/>
+      <c r="L217" s="44"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -11927,24 +11927,24 @@
       <c r="Z217" s="2"/>
     </row>
     <row r="218" spans="1:26" ht="13.2">
-      <c r="A218" s="45">
+      <c r="A218" s="43">
         <v>213</v>
       </c>
-      <c r="B218" s="46" t="s">
+      <c r="B218" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C218" s="46" t="s">
+      <c r="C218" s="44" t="s">
         <v>249</v>
       </c>
-      <c r="D218" s="46"/>
-      <c r="E218" s="46"/>
-      <c r="F218" s="46"/>
-      <c r="G218" s="46"/>
-      <c r="H218" s="46"/>
-      <c r="I218" s="93"/>
-      <c r="J218" s="46"/>
-      <c r="K218" s="46"/>
-      <c r="L218" s="46"/>
+      <c r="D218" s="44"/>
+      <c r="E218" s="44"/>
+      <c r="F218" s="44"/>
+      <c r="G218" s="44"/>
+      <c r="H218" s="44"/>
+      <c r="I218" s="91"/>
+      <c r="J218" s="44"/>
+      <c r="K218" s="44"/>
+      <c r="L218" s="44"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -11961,24 +11961,24 @@
       <c r="Z218" s="2"/>
     </row>
     <row r="219" spans="1:26" ht="13.2">
-      <c r="A219" s="45">
+      <c r="A219" s="43">
         <v>214</v>
       </c>
-      <c r="B219" s="46" t="s">
+      <c r="B219" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C219" s="46" t="s">
+      <c r="C219" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="D219" s="46"/>
-      <c r="E219" s="46"/>
-      <c r="F219" s="46"/>
-      <c r="G219" s="46"/>
-      <c r="H219" s="46"/>
-      <c r="I219" s="93"/>
-      <c r="J219" s="46"/>
-      <c r="K219" s="46"/>
-      <c r="L219" s="46"/>
+      <c r="D219" s="44"/>
+      <c r="E219" s="44"/>
+      <c r="F219" s="44"/>
+      <c r="G219" s="44"/>
+      <c r="H219" s="44"/>
+      <c r="I219" s="91"/>
+      <c r="J219" s="44"/>
+      <c r="K219" s="44"/>
+      <c r="L219" s="44"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -11995,24 +11995,24 @@
       <c r="Z219" s="2"/>
     </row>
     <row r="220" spans="1:26" ht="13.2">
-      <c r="A220" s="45">
+      <c r="A220" s="43">
         <v>215</v>
       </c>
-      <c r="B220" s="46" t="s">
+      <c r="B220" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C220" s="46" t="s">
+      <c r="C220" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="D220" s="46"/>
-      <c r="E220" s="46"/>
-      <c r="F220" s="46"/>
-      <c r="G220" s="46"/>
-      <c r="H220" s="46"/>
-      <c r="I220" s="93"/>
-      <c r="J220" s="46"/>
-      <c r="K220" s="46"/>
-      <c r="L220" s="46"/>
+      <c r="D220" s="44"/>
+      <c r="E220" s="44"/>
+      <c r="F220" s="44"/>
+      <c r="G220" s="44"/>
+      <c r="H220" s="44"/>
+      <c r="I220" s="91"/>
+      <c r="J220" s="44"/>
+      <c r="K220" s="44"/>
+      <c r="L220" s="44"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -12029,24 +12029,24 @@
       <c r="Z220" s="2"/>
     </row>
     <row r="221" spans="1:26" ht="13.2">
-      <c r="A221" s="45">
+      <c r="A221" s="43">
         <v>216</v>
       </c>
-      <c r="B221" s="46" t="s">
+      <c r="B221" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C221" s="46" t="s">
+      <c r="C221" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="D221" s="46"/>
-      <c r="E221" s="46"/>
-      <c r="F221" s="46"/>
-      <c r="G221" s="46"/>
-      <c r="H221" s="46"/>
-      <c r="I221" s="93"/>
-      <c r="J221" s="46"/>
-      <c r="K221" s="46"/>
-      <c r="L221" s="46"/>
+      <c r="D221" s="44"/>
+      <c r="E221" s="44"/>
+      <c r="F221" s="44"/>
+      <c r="G221" s="44"/>
+      <c r="H221" s="44"/>
+      <c r="I221" s="91"/>
+      <c r="J221" s="44"/>
+      <c r="K221" s="44"/>
+      <c r="L221" s="44"/>
       <c r="M221" s="2"/>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -12063,26 +12063,26 @@
       <c r="Z221" s="2"/>
     </row>
     <row r="222" spans="1:26" ht="13.2">
-      <c r="A222" s="45">
+      <c r="A222" s="43">
         <v>217</v>
       </c>
-      <c r="B222" s="70" t="s">
+      <c r="B222" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="C222" s="70" t="s">
+      <c r="C222" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="D222" s="70" t="s">
+      <c r="D222" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E222" s="70"/>
-      <c r="F222" s="70"/>
-      <c r="G222" s="70"/>
-      <c r="H222" s="70"/>
-      <c r="I222" s="96"/>
-      <c r="J222" s="70"/>
-      <c r="K222" s="70"/>
-      <c r="L222" s="70"/>
+      <c r="E222" s="68"/>
+      <c r="F222" s="68"/>
+      <c r="G222" s="68"/>
+      <c r="H222" s="68"/>
+      <c r="I222" s="94"/>
+      <c r="J222" s="68"/>
+      <c r="K222" s="68"/>
+      <c r="L222" s="68"/>
       <c r="M222" s="8"/>
       <c r="N222" s="8"/>
       <c r="O222" s="8"/>
@@ -12099,24 +12099,24 @@
       <c r="Z222" s="8"/>
     </row>
     <row r="223" spans="1:26" ht="13.2">
-      <c r="A223" s="45">
+      <c r="A223" s="43">
         <v>218</v>
       </c>
-      <c r="B223" s="46" t="s">
+      <c r="B223" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C223" s="46" t="s">
+      <c r="C223" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="D223" s="46"/>
-      <c r="E223" s="46"/>
-      <c r="F223" s="46"/>
-      <c r="G223" s="46"/>
-      <c r="H223" s="46"/>
-      <c r="I223" s="93"/>
-      <c r="J223" s="46"/>
-      <c r="K223" s="46"/>
-      <c r="L223" s="46"/>
+      <c r="D223" s="44"/>
+      <c r="E223" s="44"/>
+      <c r="F223" s="44"/>
+      <c r="G223" s="44"/>
+      <c r="H223" s="44"/>
+      <c r="I223" s="91"/>
+      <c r="J223" s="44"/>
+      <c r="K223" s="44"/>
+      <c r="L223" s="44"/>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -12133,24 +12133,24 @@
       <c r="Z223" s="2"/>
     </row>
     <row r="224" spans="1:26" ht="13.2">
-      <c r="A224" s="45">
+      <c r="A224" s="43">
         <v>219</v>
       </c>
-      <c r="B224" s="46" t="s">
+      <c r="B224" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C224" s="46" t="s">
+      <c r="C224" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="D224" s="46"/>
-      <c r="E224" s="46"/>
-      <c r="F224" s="46"/>
-      <c r="G224" s="46"/>
-      <c r="H224" s="46"/>
-      <c r="I224" s="93"/>
-      <c r="J224" s="46"/>
-      <c r="K224" s="46"/>
-      <c r="L224" s="46"/>
+      <c r="D224" s="44"/>
+      <c r="E224" s="44"/>
+      <c r="F224" s="44"/>
+      <c r="G224" s="44"/>
+      <c r="H224" s="44"/>
+      <c r="I224" s="91"/>
+      <c r="J224" s="44"/>
+      <c r="K224" s="44"/>
+      <c r="L224" s="44"/>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -12167,24 +12167,24 @@
       <c r="Z224" s="2"/>
     </row>
     <row r="225" spans="1:26" ht="13.2">
-      <c r="A225" s="45">
+      <c r="A225" s="43">
         <v>220</v>
       </c>
-      <c r="B225" s="46" t="s">
+      <c r="B225" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C225" s="46" t="s">
+      <c r="C225" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="D225" s="46"/>
-      <c r="E225" s="46"/>
-      <c r="F225" s="46"/>
-      <c r="G225" s="46"/>
-      <c r="H225" s="46"/>
-      <c r="I225" s="93"/>
-      <c r="J225" s="46"/>
-      <c r="K225" s="46"/>
-      <c r="L225" s="46"/>
+      <c r="D225" s="44"/>
+      <c r="E225" s="44"/>
+      <c r="F225" s="44"/>
+      <c r="G225" s="44"/>
+      <c r="H225" s="44"/>
+      <c r="I225" s="91"/>
+      <c r="J225" s="44"/>
+      <c r="K225" s="44"/>
+      <c r="L225" s="44"/>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -12201,24 +12201,24 @@
       <c r="Z225" s="2"/>
     </row>
     <row r="226" spans="1:26" ht="13.2">
-      <c r="A226" s="45">
+      <c r="A226" s="43">
         <v>222</v>
       </c>
-      <c r="B226" s="46" t="s">
+      <c r="B226" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C226" s="46" t="s">
+      <c r="C226" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="D226" s="46"/>
-      <c r="E226" s="46"/>
-      <c r="F226" s="46"/>
-      <c r="G226" s="46"/>
-      <c r="H226" s="46"/>
-      <c r="I226" s="93"/>
-      <c r="J226" s="46"/>
-      <c r="K226" s="46"/>
-      <c r="L226" s="46"/>
+      <c r="D226" s="44"/>
+      <c r="E226" s="44"/>
+      <c r="F226" s="44"/>
+      <c r="G226" s="44"/>
+      <c r="H226" s="44"/>
+      <c r="I226" s="91"/>
+      <c r="J226" s="44"/>
+      <c r="K226" s="44"/>
+      <c r="L226" s="44"/>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -12235,24 +12235,24 @@
       <c r="Z226" s="2"/>
     </row>
     <row r="227" spans="1:26" ht="13.2">
-      <c r="A227" s="45">
+      <c r="A227" s="43">
         <v>223</v>
       </c>
-      <c r="B227" s="46" t="s">
+      <c r="B227" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C227" s="46" t="s">
+      <c r="C227" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="D227" s="46"/>
-      <c r="E227" s="46"/>
-      <c r="F227" s="46"/>
-      <c r="G227" s="46"/>
-      <c r="H227" s="46"/>
-      <c r="I227" s="93"/>
-      <c r="J227" s="46"/>
-      <c r="K227" s="46"/>
-      <c r="L227" s="46"/>
+      <c r="D227" s="44"/>
+      <c r="E227" s="44"/>
+      <c r="F227" s="44"/>
+      <c r="G227" s="44"/>
+      <c r="H227" s="44"/>
+      <c r="I227" s="91"/>
+      <c r="J227" s="44"/>
+      <c r="K227" s="44"/>
+      <c r="L227" s="44"/>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -12269,24 +12269,24 @@
       <c r="Z227" s="2"/>
     </row>
     <row r="228" spans="1:26" ht="13.2">
-      <c r="A228" s="45">
+      <c r="A228" s="43">
         <v>224</v>
       </c>
-      <c r="B228" s="46" t="s">
+      <c r="B228" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C228" s="46" t="s">
+      <c r="C228" s="44" t="s">
         <v>259</v>
       </c>
-      <c r="D228" s="46"/>
-      <c r="E228" s="46"/>
-      <c r="F228" s="46"/>
-      <c r="G228" s="46"/>
-      <c r="H228" s="46"/>
-      <c r="I228" s="93"/>
-      <c r="J228" s="46"/>
-      <c r="K228" s="46"/>
-      <c r="L228" s="46"/>
+      <c r="D228" s="44"/>
+      <c r="E228" s="44"/>
+      <c r="F228" s="44"/>
+      <c r="G228" s="44"/>
+      <c r="H228" s="44"/>
+      <c r="I228" s="91"/>
+      <c r="J228" s="44"/>
+      <c r="K228" s="44"/>
+      <c r="L228" s="44"/>
       <c r="M228" s="2"/>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -12303,24 +12303,24 @@
       <c r="Z228" s="2"/>
     </row>
     <row r="229" spans="1:26" ht="13.2">
-      <c r="A229" s="45">
+      <c r="A229" s="43">
         <v>225</v>
       </c>
-      <c r="B229" s="46" t="s">
+      <c r="B229" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C229" s="46" t="s">
+      <c r="C229" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="D229" s="46"/>
-      <c r="E229" s="46"/>
-      <c r="F229" s="46"/>
-      <c r="G229" s="46"/>
-      <c r="H229" s="46"/>
-      <c r="I229" s="93"/>
-      <c r="J229" s="46"/>
-      <c r="K229" s="46"/>
-      <c r="L229" s="46"/>
+      <c r="D229" s="44"/>
+      <c r="E229" s="44"/>
+      <c r="F229" s="44"/>
+      <c r="G229" s="44"/>
+      <c r="H229" s="44"/>
+      <c r="I229" s="91"/>
+      <c r="J229" s="44"/>
+      <c r="K229" s="44"/>
+      <c r="L229" s="44"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -12337,24 +12337,24 @@
       <c r="Z229" s="2"/>
     </row>
     <row r="230" spans="1:26" ht="13.2">
-      <c r="A230" s="45">
+      <c r="A230" s="43">
         <v>226</v>
       </c>
-      <c r="B230" s="46" t="s">
+      <c r="B230" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C230" s="46" t="s">
+      <c r="C230" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="D230" s="46"/>
-      <c r="E230" s="46"/>
-      <c r="F230" s="46"/>
-      <c r="G230" s="46"/>
-      <c r="H230" s="46"/>
-      <c r="I230" s="93"/>
-      <c r="J230" s="46"/>
-      <c r="K230" s="46"/>
-      <c r="L230" s="46"/>
+      <c r="D230" s="44"/>
+      <c r="E230" s="44"/>
+      <c r="F230" s="44"/>
+      <c r="G230" s="44"/>
+      <c r="H230" s="44"/>
+      <c r="I230" s="91"/>
+      <c r="J230" s="44"/>
+      <c r="K230" s="44"/>
+      <c r="L230" s="44"/>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -12371,24 +12371,24 @@
       <c r="Z230" s="2"/>
     </row>
     <row r="231" spans="1:26" ht="13.2">
-      <c r="A231" s="45">
+      <c r="A231" s="43">
         <v>227</v>
       </c>
-      <c r="B231" s="46" t="s">
+      <c r="B231" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C231" s="46" t="s">
+      <c r="C231" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="D231" s="46"/>
-      <c r="E231" s="46"/>
-      <c r="F231" s="46"/>
-      <c r="G231" s="46"/>
-      <c r="H231" s="46"/>
-      <c r="I231" s="93"/>
-      <c r="J231" s="46"/>
-      <c r="K231" s="46"/>
-      <c r="L231" s="46"/>
+      <c r="D231" s="44"/>
+      <c r="E231" s="44"/>
+      <c r="F231" s="44"/>
+      <c r="G231" s="44"/>
+      <c r="H231" s="44"/>
+      <c r="I231" s="91"/>
+      <c r="J231" s="44"/>
+      <c r="K231" s="44"/>
+      <c r="L231" s="44"/>
       <c r="M231" s="2"/>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -12405,24 +12405,24 @@
       <c r="Z231" s="2"/>
     </row>
     <row r="232" spans="1:26" ht="13.2">
-      <c r="A232" s="45">
+      <c r="A232" s="43">
         <v>228</v>
       </c>
-      <c r="B232" s="46" t="s">
+      <c r="B232" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C232" s="46" t="s">
+      <c r="C232" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="D232" s="46"/>
-      <c r="E232" s="46"/>
-      <c r="F232" s="46"/>
-      <c r="G232" s="46"/>
-      <c r="H232" s="46"/>
-      <c r="I232" s="93"/>
-      <c r="J232" s="46"/>
-      <c r="K232" s="46"/>
-      <c r="L232" s="46"/>
+      <c r="D232" s="44"/>
+      <c r="E232" s="44"/>
+      <c r="F232" s="44"/>
+      <c r="G232" s="44"/>
+      <c r="H232" s="44"/>
+      <c r="I232" s="91"/>
+      <c r="J232" s="44"/>
+      <c r="K232" s="44"/>
+      <c r="L232" s="44"/>
       <c r="M232" s="2"/>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -12439,24 +12439,24 @@
       <c r="Z232" s="2"/>
     </row>
     <row r="233" spans="1:26" ht="13.2">
-      <c r="A233" s="45">
+      <c r="A233" s="43">
         <v>229</v>
       </c>
-      <c r="B233" s="46" t="s">
+      <c r="B233" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C233" s="46" t="s">
+      <c r="C233" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="D233" s="46"/>
-      <c r="E233" s="46"/>
-      <c r="F233" s="46"/>
-      <c r="G233" s="46"/>
-      <c r="H233" s="46"/>
-      <c r="I233" s="93"/>
-      <c r="J233" s="46"/>
-      <c r="K233" s="46"/>
-      <c r="L233" s="46"/>
+      <c r="D233" s="44"/>
+      <c r="E233" s="44"/>
+      <c r="F233" s="44"/>
+      <c r="G233" s="44"/>
+      <c r="H233" s="44"/>
+      <c r="I233" s="91"/>
+      <c r="J233" s="44"/>
+      <c r="K233" s="44"/>
+      <c r="L233" s="44"/>
       <c r="M233" s="2"/>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -12473,24 +12473,24 @@
       <c r="Z233" s="2"/>
     </row>
     <row r="234" spans="1:26" ht="13.2">
-      <c r="A234" s="45">
+      <c r="A234" s="43">
         <v>230</v>
       </c>
-      <c r="B234" s="46" t="s">
+      <c r="B234" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C234" s="46" t="s">
+      <c r="C234" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="D234" s="46"/>
-      <c r="E234" s="46"/>
-      <c r="F234" s="46"/>
-      <c r="G234" s="46"/>
-      <c r="H234" s="46"/>
-      <c r="I234" s="93"/>
-      <c r="J234" s="46"/>
-      <c r="K234" s="46"/>
-      <c r="L234" s="46"/>
+      <c r="D234" s="44"/>
+      <c r="E234" s="44"/>
+      <c r="F234" s="44"/>
+      <c r="G234" s="44"/>
+      <c r="H234" s="44"/>
+      <c r="I234" s="91"/>
+      <c r="J234" s="44"/>
+      <c r="K234" s="44"/>
+      <c r="L234" s="44"/>
       <c r="M234" s="2"/>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -12507,24 +12507,24 @@
       <c r="Z234" s="2"/>
     </row>
     <row r="235" spans="1:26" ht="13.2">
-      <c r="A235" s="45">
+      <c r="A235" s="43">
         <v>231</v>
       </c>
-      <c r="B235" s="46" t="s">
+      <c r="B235" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C235" s="46" t="s">
+      <c r="C235" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="D235" s="46"/>
-      <c r="E235" s="46"/>
-      <c r="F235" s="46"/>
-      <c r="G235" s="46"/>
-      <c r="H235" s="46"/>
-      <c r="I235" s="93"/>
-      <c r="J235" s="46"/>
-      <c r="K235" s="46"/>
-      <c r="L235" s="46"/>
+      <c r="D235" s="44"/>
+      <c r="E235" s="44"/>
+      <c r="F235" s="44"/>
+      <c r="G235" s="44"/>
+      <c r="H235" s="44"/>
+      <c r="I235" s="91"/>
+      <c r="J235" s="44"/>
+      <c r="K235" s="44"/>
+      <c r="L235" s="44"/>
       <c r="M235" s="2"/>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -12541,24 +12541,24 @@
       <c r="Z235" s="2"/>
     </row>
     <row r="236" spans="1:26" ht="13.2">
-      <c r="A236" s="45">
+      <c r="A236" s="43">
         <v>232</v>
       </c>
-      <c r="B236" s="46" t="s">
+      <c r="B236" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C236" s="46" t="s">
+      <c r="C236" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="D236" s="46"/>
-      <c r="E236" s="46"/>
-      <c r="F236" s="46"/>
-      <c r="G236" s="46"/>
-      <c r="H236" s="46"/>
-      <c r="I236" s="93"/>
-      <c r="J236" s="46"/>
-      <c r="K236" s="46"/>
-      <c r="L236" s="46"/>
+      <c r="D236" s="44"/>
+      <c r="E236" s="44"/>
+      <c r="F236" s="44"/>
+      <c r="G236" s="44"/>
+      <c r="H236" s="44"/>
+      <c r="I236" s="91"/>
+      <c r="J236" s="44"/>
+      <c r="K236" s="44"/>
+      <c r="L236" s="44"/>
       <c r="M236" s="2"/>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -12575,26 +12575,26 @@
       <c r="Z236" s="2"/>
     </row>
     <row r="237" spans="1:26" ht="13.2">
-      <c r="A237" s="45">
+      <c r="A237" s="43">
         <v>233</v>
       </c>
-      <c r="B237" s="46" t="s">
+      <c r="B237" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C237" s="46" t="s">
+      <c r="C237" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="D237" s="46" t="s">
+      <c r="D237" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E237" s="46"/>
-      <c r="F237" s="46"/>
-      <c r="G237" s="46"/>
-      <c r="H237" s="46"/>
-      <c r="I237" s="93"/>
-      <c r="J237" s="46"/>
-      <c r="K237" s="46"/>
-      <c r="L237" s="46"/>
+      <c r="E237" s="44"/>
+      <c r="F237" s="44"/>
+      <c r="G237" s="44"/>
+      <c r="H237" s="44"/>
+      <c r="I237" s="91"/>
+      <c r="J237" s="44"/>
+      <c r="K237" s="44"/>
+      <c r="L237" s="44"/>
       <c r="M237" s="2"/>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -12611,26 +12611,26 @@
       <c r="Z237" s="2"/>
     </row>
     <row r="238" spans="1:26" ht="13.2">
-      <c r="A238" s="45">
+      <c r="A238" s="43">
         <v>234</v>
       </c>
-      <c r="B238" s="46" t="s">
+      <c r="B238" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C238" s="46" t="s">
+      <c r="C238" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="D238" s="46" t="s">
+      <c r="D238" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E238" s="46"/>
-      <c r="F238" s="46"/>
-      <c r="G238" s="46"/>
-      <c r="H238" s="46"/>
-      <c r="I238" s="93"/>
-      <c r="J238" s="46"/>
-      <c r="K238" s="46"/>
-      <c r="L238" s="46"/>
+      <c r="E238" s="44"/>
+      <c r="F238" s="44"/>
+      <c r="G238" s="44"/>
+      <c r="H238" s="44"/>
+      <c r="I238" s="91"/>
+      <c r="J238" s="44"/>
+      <c r="K238" s="44"/>
+      <c r="L238" s="44"/>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -12647,26 +12647,26 @@
       <c r="Z238" s="2"/>
     </row>
     <row r="239" spans="1:26" ht="13.2">
-      <c r="A239" s="45">
+      <c r="A239" s="43">
         <v>235</v>
       </c>
-      <c r="B239" s="46" t="s">
+      <c r="B239" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C239" s="46" t="s">
+      <c r="C239" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="D239" s="46" t="s">
+      <c r="D239" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E239" s="46"/>
-      <c r="F239" s="46"/>
-      <c r="G239" s="46"/>
-      <c r="H239" s="46"/>
-      <c r="I239" s="93"/>
-      <c r="J239" s="46"/>
-      <c r="K239" s="46"/>
-      <c r="L239" s="46"/>
+      <c r="E239" s="44"/>
+      <c r="F239" s="44"/>
+      <c r="G239" s="44"/>
+      <c r="H239" s="44"/>
+      <c r="I239" s="91"/>
+      <c r="J239" s="44"/>
+      <c r="K239" s="44"/>
+      <c r="L239" s="44"/>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -12683,26 +12683,26 @@
       <c r="Z239" s="2"/>
     </row>
     <row r="240" spans="1:26" ht="13.2">
-      <c r="A240" s="45">
+      <c r="A240" s="43">
         <v>236</v>
       </c>
-      <c r="B240" s="46" t="s">
+      <c r="B240" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C240" s="46" t="s">
+      <c r="C240" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="D240" s="46" t="s">
+      <c r="D240" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E240" s="46"/>
-      <c r="F240" s="46"/>
-      <c r="G240" s="46"/>
-      <c r="H240" s="46"/>
-      <c r="I240" s="93"/>
-      <c r="J240" s="46"/>
-      <c r="K240" s="46"/>
-      <c r="L240" s="46"/>
+      <c r="E240" s="44"/>
+      <c r="F240" s="44"/>
+      <c r="G240" s="44"/>
+      <c r="H240" s="44"/>
+      <c r="I240" s="91"/>
+      <c r="J240" s="44"/>
+      <c r="K240" s="44"/>
+      <c r="L240" s="44"/>
       <c r="M240" s="2"/>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -12719,26 +12719,26 @@
       <c r="Z240" s="2"/>
     </row>
     <row r="241" spans="1:26" ht="13.2">
-      <c r="A241" s="45">
+      <c r="A241" s="43">
         <v>237</v>
       </c>
-      <c r="B241" s="46" t="s">
+      <c r="B241" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C241" s="46" t="s">
+      <c r="C241" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="D241" s="46" t="s">
+      <c r="D241" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E241" s="46"/>
-      <c r="F241" s="46"/>
-      <c r="G241" s="46"/>
-      <c r="H241" s="46"/>
-      <c r="I241" s="93"/>
-      <c r="J241" s="46"/>
-      <c r="K241" s="46"/>
-      <c r="L241" s="46"/>
+      <c r="E241" s="44"/>
+      <c r="F241" s="44"/>
+      <c r="G241" s="44"/>
+      <c r="H241" s="44"/>
+      <c r="I241" s="91"/>
+      <c r="J241" s="44"/>
+      <c r="K241" s="44"/>
+      <c r="L241" s="44"/>
       <c r="M241" s="2"/>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -12755,24 +12755,24 @@
       <c r="Z241" s="2"/>
     </row>
     <row r="242" spans="1:26" ht="13.2">
-      <c r="A242" s="45">
+      <c r="A242" s="43">
         <v>238</v>
       </c>
-      <c r="B242" s="46" t="s">
+      <c r="B242" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C242" s="46" t="s">
+      <c r="C242" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="D242" s="46"/>
-      <c r="E242" s="46"/>
-      <c r="F242" s="46"/>
-      <c r="G242" s="46"/>
-      <c r="H242" s="46"/>
-      <c r="I242" s="93"/>
-      <c r="J242" s="46"/>
-      <c r="K242" s="46"/>
-      <c r="L242" s="46"/>
+      <c r="D242" s="44"/>
+      <c r="E242" s="44"/>
+      <c r="F242" s="44"/>
+      <c r="G242" s="44"/>
+      <c r="H242" s="44"/>
+      <c r="I242" s="91"/>
+      <c r="J242" s="44"/>
+      <c r="K242" s="44"/>
+      <c r="L242" s="44"/>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -12789,26 +12789,26 @@
       <c r="Z242" s="2"/>
     </row>
     <row r="243" spans="1:26" ht="13.2">
-      <c r="A243" s="45">
+      <c r="A243" s="43">
         <v>239</v>
       </c>
-      <c r="B243" s="46" t="s">
+      <c r="B243" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C243" s="46" t="s">
+      <c r="C243" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="D243" s="46" t="s">
+      <c r="D243" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E243" s="46"/>
-      <c r="F243" s="46"/>
-      <c r="G243" s="46"/>
-      <c r="H243" s="46"/>
-      <c r="I243" s="93"/>
-      <c r="J243" s="46"/>
-      <c r="K243" s="46"/>
-      <c r="L243" s="46"/>
+      <c r="E243" s="44"/>
+      <c r="F243" s="44"/>
+      <c r="G243" s="44"/>
+      <c r="H243" s="44"/>
+      <c r="I243" s="91"/>
+      <c r="J243" s="44"/>
+      <c r="K243" s="44"/>
+      <c r="L243" s="44"/>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -12825,24 +12825,24 @@
       <c r="Z243" s="2"/>
     </row>
     <row r="244" spans="1:26" ht="13.2">
-      <c r="A244" s="45">
+      <c r="A244" s="43">
         <v>240</v>
       </c>
-      <c r="B244" s="46" t="s">
+      <c r="B244" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C244" s="46" t="s">
+      <c r="C244" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="D244" s="46"/>
-      <c r="E244" s="46"/>
-      <c r="F244" s="46"/>
-      <c r="G244" s="46"/>
-      <c r="H244" s="46"/>
-      <c r="I244" s="93"/>
-      <c r="J244" s="46"/>
-      <c r="K244" s="46"/>
-      <c r="L244" s="46"/>
+      <c r="D244" s="44"/>
+      <c r="E244" s="44"/>
+      <c r="F244" s="44"/>
+      <c r="G244" s="44"/>
+      <c r="H244" s="44"/>
+      <c r="I244" s="91"/>
+      <c r="J244" s="44"/>
+      <c r="K244" s="44"/>
+      <c r="L244" s="44"/>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -12859,24 +12859,24 @@
       <c r="Z244" s="2"/>
     </row>
     <row r="245" spans="1:26" ht="13.2">
-      <c r="A245" s="45">
+      <c r="A245" s="43">
         <v>241</v>
       </c>
-      <c r="B245" s="46" t="s">
+      <c r="B245" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="C245" s="90" t="s">
+      <c r="C245" s="88" t="s">
         <v>274</v>
       </c>
-      <c r="D245" s="46"/>
-      <c r="E245" s="46"/>
-      <c r="F245" s="46"/>
-      <c r="G245" s="46"/>
-      <c r="H245" s="46"/>
-      <c r="I245" s="93"/>
-      <c r="J245" s="46"/>
-      <c r="K245" s="46"/>
-      <c r="L245" s="46"/>
+      <c r="D245" s="44"/>
+      <c r="E245" s="44"/>
+      <c r="F245" s="44"/>
+      <c r="G245" s="44"/>
+      <c r="H245" s="44"/>
+      <c r="I245" s="91"/>
+      <c r="J245" s="44"/>
+      <c r="K245" s="44"/>
+      <c r="L245" s="44"/>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -12893,24 +12893,24 @@
       <c r="Z245" s="2"/>
     </row>
     <row r="246" spans="1:26" ht="13.8">
-      <c r="A246" s="45">
+      <c r="A246" s="43">
         <v>242</v>
       </c>
-      <c r="B246" s="46" t="s">
+      <c r="B246" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C246" s="58" t="s">
+      <c r="C246" s="56" t="s">
         <v>276</v>
       </c>
-      <c r="D246" s="46"/>
-      <c r="E246" s="46"/>
-      <c r="F246" s="46"/>
-      <c r="G246" s="46"/>
-      <c r="H246" s="46"/>
-      <c r="I246" s="93"/>
-      <c r="J246" s="46"/>
-      <c r="K246" s="46"/>
-      <c r="L246" s="46"/>
+      <c r="D246" s="44"/>
+      <c r="E246" s="44"/>
+      <c r="F246" s="44"/>
+      <c r="G246" s="44"/>
+      <c r="H246" s="44"/>
+      <c r="I246" s="91"/>
+      <c r="J246" s="44"/>
+      <c r="K246" s="44"/>
+      <c r="L246" s="44"/>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -12927,24 +12927,24 @@
       <c r="Z246" s="2"/>
     </row>
     <row r="247" spans="1:26" ht="13.8">
-      <c r="A247" s="45">
+      <c r="A247" s="43">
         <v>243</v>
       </c>
-      <c r="B247" s="46" t="s">
+      <c r="B247" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C247" s="65" t="s">
+      <c r="C247" s="63" t="s">
         <v>277</v>
       </c>
-      <c r="D247" s="46"/>
-      <c r="E247" s="46"/>
-      <c r="F247" s="46"/>
-      <c r="G247" s="46"/>
-      <c r="H247" s="46"/>
-      <c r="I247" s="93"/>
-      <c r="J247" s="46"/>
-      <c r="K247" s="46"/>
-      <c r="L247" s="46"/>
+      <c r="D247" s="44"/>
+      <c r="E247" s="44"/>
+      <c r="F247" s="44"/>
+      <c r="G247" s="44"/>
+      <c r="H247" s="44"/>
+      <c r="I247" s="91"/>
+      <c r="J247" s="44"/>
+      <c r="K247" s="44"/>
+      <c r="L247" s="44"/>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -12961,24 +12961,24 @@
       <c r="Z247" s="2"/>
     </row>
     <row r="248" spans="1:26" ht="13.8">
-      <c r="A248" s="45">
+      <c r="A248" s="43">
         <v>244</v>
       </c>
-      <c r="B248" s="46" t="s">
+      <c r="B248" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C248" s="65" t="s">
+      <c r="C248" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="D248" s="46"/>
-      <c r="E248" s="46"/>
-      <c r="F248" s="46"/>
-      <c r="G248" s="46"/>
-      <c r="H248" s="46"/>
-      <c r="I248" s="93"/>
-      <c r="J248" s="46"/>
-      <c r="K248" s="46"/>
-      <c r="L248" s="46"/>
+      <c r="D248" s="44"/>
+      <c r="E248" s="44"/>
+      <c r="F248" s="44"/>
+      <c r="G248" s="44"/>
+      <c r="H248" s="44"/>
+      <c r="I248" s="91"/>
+      <c r="J248" s="44"/>
+      <c r="K248" s="44"/>
+      <c r="L248" s="44"/>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -12995,24 +12995,24 @@
       <c r="Z248" s="2"/>
     </row>
     <row r="249" spans="1:26" ht="13.8">
-      <c r="A249" s="45">
+      <c r="A249" s="43">
         <v>245</v>
       </c>
-      <c r="B249" s="46" t="s">
+      <c r="B249" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C249" s="65" t="s">
+      <c r="C249" s="63" t="s">
         <v>279</v>
       </c>
-      <c r="D249" s="46"/>
-      <c r="E249" s="46"/>
-      <c r="F249" s="46"/>
-      <c r="G249" s="46"/>
-      <c r="H249" s="46"/>
-      <c r="I249" s="93"/>
-      <c r="J249" s="46"/>
-      <c r="K249" s="46"/>
-      <c r="L249" s="46"/>
+      <c r="D249" s="44"/>
+      <c r="E249" s="44"/>
+      <c r="F249" s="44"/>
+      <c r="G249" s="44"/>
+      <c r="H249" s="44"/>
+      <c r="I249" s="91"/>
+      <c r="J249" s="44"/>
+      <c r="K249" s="44"/>
+      <c r="L249" s="44"/>
       <c r="M249" s="2"/>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -13029,24 +13029,24 @@
       <c r="Z249" s="2"/>
     </row>
     <row r="250" spans="1:26" ht="13.8">
-      <c r="A250" s="45">
+      <c r="A250" s="43">
         <v>246</v>
       </c>
-      <c r="B250" s="46" t="s">
+      <c r="B250" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C250" s="65" t="s">
+      <c r="C250" s="63" t="s">
         <v>280</v>
       </c>
-      <c r="D250" s="46"/>
-      <c r="E250" s="46"/>
-      <c r="F250" s="46"/>
-      <c r="G250" s="46"/>
-      <c r="H250" s="46"/>
-      <c r="I250" s="93"/>
-      <c r="J250" s="46"/>
-      <c r="K250" s="46"/>
-      <c r="L250" s="46"/>
+      <c r="D250" s="44"/>
+      <c r="E250" s="44"/>
+      <c r="F250" s="44"/>
+      <c r="G250" s="44"/>
+      <c r="H250" s="44"/>
+      <c r="I250" s="91"/>
+      <c r="J250" s="44"/>
+      <c r="K250" s="44"/>
+      <c r="L250" s="44"/>
       <c r="M250" s="2"/>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -13063,24 +13063,24 @@
       <c r="Z250" s="2"/>
     </row>
     <row r="251" spans="1:26" ht="13.8">
-      <c r="A251" s="45">
+      <c r="A251" s="43">
         <v>247</v>
       </c>
-      <c r="B251" s="46" t="s">
+      <c r="B251" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C251" s="65" t="s">
+      <c r="C251" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="D251" s="46"/>
-      <c r="E251" s="46"/>
-      <c r="F251" s="46"/>
-      <c r="G251" s="46"/>
-      <c r="H251" s="46"/>
-      <c r="I251" s="93"/>
-      <c r="J251" s="46"/>
-      <c r="K251" s="46"/>
-      <c r="L251" s="46"/>
+      <c r="D251" s="44"/>
+      <c r="E251" s="44"/>
+      <c r="F251" s="44"/>
+      <c r="G251" s="44"/>
+      <c r="H251" s="44"/>
+      <c r="I251" s="91"/>
+      <c r="J251" s="44"/>
+      <c r="K251" s="44"/>
+      <c r="L251" s="44"/>
       <c r="M251" s="2"/>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -13097,24 +13097,24 @@
       <c r="Z251" s="2"/>
     </row>
     <row r="252" spans="1:26" ht="13.8">
-      <c r="A252" s="45">
+      <c r="A252" s="43">
         <v>248</v>
       </c>
-      <c r="B252" s="46" t="s">
+      <c r="B252" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C252" s="58" t="s">
+      <c r="C252" s="56" t="s">
         <v>282</v>
       </c>
-      <c r="D252" s="46"/>
-      <c r="E252" s="46"/>
-      <c r="F252" s="46"/>
-      <c r="G252" s="46"/>
-      <c r="H252" s="46"/>
-      <c r="I252" s="93"/>
-      <c r="J252" s="46"/>
-      <c r="K252" s="46"/>
-      <c r="L252" s="46"/>
+      <c r="D252" s="44"/>
+      <c r="E252" s="44"/>
+      <c r="F252" s="44"/>
+      <c r="G252" s="44"/>
+      <c r="H252" s="44"/>
+      <c r="I252" s="91"/>
+      <c r="J252" s="44"/>
+      <c r="K252" s="44"/>
+      <c r="L252" s="44"/>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
@@ -13131,24 +13131,24 @@
       <c r="Z252" s="2"/>
     </row>
     <row r="253" spans="1:26" ht="13.8">
-      <c r="A253" s="45">
+      <c r="A253" s="43">
         <v>249</v>
       </c>
-      <c r="B253" s="46" t="s">
+      <c r="B253" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C253" s="91" t="s">
+      <c r="C253" s="89" t="s">
         <v>283</v>
       </c>
-      <c r="D253" s="46"/>
-      <c r="E253" s="46"/>
-      <c r="F253" s="46"/>
-      <c r="G253" s="46"/>
-      <c r="H253" s="46"/>
-      <c r="I253" s="93"/>
-      <c r="J253" s="46"/>
-      <c r="K253" s="46"/>
-      <c r="L253" s="46"/>
+      <c r="D253" s="44"/>
+      <c r="E253" s="44"/>
+      <c r="F253" s="44"/>
+      <c r="G253" s="44"/>
+      <c r="H253" s="44"/>
+      <c r="I253" s="91"/>
+      <c r="J253" s="44"/>
+      <c r="K253" s="44"/>
+      <c r="L253" s="44"/>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -13165,24 +13165,24 @@
       <c r="Z253" s="2"/>
     </row>
     <row r="254" spans="1:26" ht="13.8">
-      <c r="A254" s="45">
+      <c r="A254" s="43">
         <v>250</v>
       </c>
-      <c r="B254" s="46" t="s">
+      <c r="B254" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C254" s="58" t="s">
+      <c r="C254" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="D254" s="46"/>
-      <c r="E254" s="46"/>
-      <c r="F254" s="46"/>
-      <c r="G254" s="46"/>
-      <c r="H254" s="46"/>
-      <c r="I254" s="93"/>
-      <c r="J254" s="46"/>
-      <c r="K254" s="46"/>
-      <c r="L254" s="46"/>
+      <c r="D254" s="44"/>
+      <c r="E254" s="44"/>
+      <c r="F254" s="44"/>
+      <c r="G254" s="44"/>
+      <c r="H254" s="44"/>
+      <c r="I254" s="91"/>
+      <c r="J254" s="44"/>
+      <c r="K254" s="44"/>
+      <c r="L254" s="44"/>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -13199,24 +13199,24 @@
       <c r="Z254" s="2"/>
     </row>
     <row r="255" spans="1:26" ht="13.8">
-      <c r="A255" s="45">
+      <c r="A255" s="43">
         <v>251</v>
       </c>
-      <c r="B255" s="46" t="s">
+      <c r="B255" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C255" s="58" t="s">
+      <c r="C255" s="56" t="s">
         <v>285</v>
       </c>
-      <c r="D255" s="46"/>
-      <c r="E255" s="46"/>
-      <c r="F255" s="46"/>
-      <c r="G255" s="46"/>
-      <c r="H255" s="46"/>
-      <c r="I255" s="93"/>
-      <c r="J255" s="46"/>
-      <c r="K255" s="46"/>
-      <c r="L255" s="46"/>
+      <c r="D255" s="44"/>
+      <c r="E255" s="44"/>
+      <c r="F255" s="44"/>
+      <c r="G255" s="44"/>
+      <c r="H255" s="44"/>
+      <c r="I255" s="91"/>
+      <c r="J255" s="44"/>
+      <c r="K255" s="44"/>
+      <c r="L255" s="44"/>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -13233,18 +13233,18 @@
       <c r="Z255" s="2"/>
     </row>
     <row r="256" spans="1:26" ht="13.2">
-      <c r="A256" s="46"/>
-      <c r="B256" s="46"/>
-      <c r="C256" s="46"/>
-      <c r="D256" s="46"/>
-      <c r="E256" s="46"/>
-      <c r="F256" s="46"/>
-      <c r="G256" s="46"/>
-      <c r="H256" s="46"/>
-      <c r="I256" s="93"/>
-      <c r="J256" s="46"/>
-      <c r="K256" s="46"/>
-      <c r="L256" s="46"/>
+      <c r="A256" s="44"/>
+      <c r="B256" s="44"/>
+      <c r="C256" s="44"/>
+      <c r="D256" s="44"/>
+      <c r="E256" s="44"/>
+      <c r="F256" s="44"/>
+      <c r="G256" s="44"/>
+      <c r="H256" s="44"/>
+      <c r="I256" s="91"/>
+      <c r="J256" s="44"/>
+      <c r="K256" s="44"/>
+      <c r="L256" s="44"/>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
@@ -13261,18 +13261,18 @@
       <c r="Z256" s="2"/>
     </row>
     <row r="257" spans="1:26" ht="13.2">
-      <c r="A257" s="46"/>
-      <c r="B257" s="46"/>
-      <c r="C257" s="46"/>
-      <c r="D257" s="46"/>
-      <c r="E257" s="46"/>
-      <c r="F257" s="46"/>
-      <c r="G257" s="46"/>
-      <c r="H257" s="46"/>
-      <c r="I257" s="93"/>
-      <c r="J257" s="46"/>
-      <c r="K257" s="46"/>
-      <c r="L257" s="46"/>
+      <c r="A257" s="44"/>
+      <c r="B257" s="44"/>
+      <c r="C257" s="44"/>
+      <c r="D257" s="44"/>
+      <c r="E257" s="44"/>
+      <c r="F257" s="44"/>
+      <c r="G257" s="44"/>
+      <c r="H257" s="44"/>
+      <c r="I257" s="91"/>
+      <c r="J257" s="44"/>
+      <c r="K257" s="44"/>
+      <c r="L257" s="44"/>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -13289,18 +13289,18 @@
       <c r="Z257" s="2"/>
     </row>
     <row r="258" spans="1:26" ht="13.2">
-      <c r="A258" s="46"/>
-      <c r="B258" s="46"/>
-      <c r="C258" s="46"/>
-      <c r="D258" s="46"/>
-      <c r="E258" s="46"/>
-      <c r="F258" s="46"/>
-      <c r="G258" s="46"/>
-      <c r="H258" s="46"/>
-      <c r="I258" s="93"/>
-      <c r="J258" s="46"/>
-      <c r="K258" s="46"/>
-      <c r="L258" s="46"/>
+      <c r="A258" s="44"/>
+      <c r="B258" s="44"/>
+      <c r="C258" s="44"/>
+      <c r="D258" s="44"/>
+      <c r="E258" s="44"/>
+      <c r="F258" s="44"/>
+      <c r="G258" s="44"/>
+      <c r="H258" s="44"/>
+      <c r="I258" s="91"/>
+      <c r="J258" s="44"/>
+      <c r="K258" s="44"/>
+      <c r="L258" s="44"/>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
       <c r="O258" s="2"/>
@@ -13317,18 +13317,18 @@
       <c r="Z258" s="2"/>
     </row>
     <row r="259" spans="1:26" ht="13.2">
-      <c r="A259" s="46"/>
-      <c r="B259" s="46"/>
-      <c r="C259" s="46"/>
-      <c r="D259" s="46"/>
-      <c r="E259" s="46"/>
-      <c r="F259" s="46"/>
-      <c r="G259" s="46"/>
-      <c r="H259" s="46"/>
-      <c r="I259" s="93"/>
-      <c r="J259" s="46"/>
-      <c r="K259" s="46"/>
-      <c r="L259" s="46"/>
+      <c r="A259" s="44"/>
+      <c r="B259" s="44"/>
+      <c r="C259" s="44"/>
+      <c r="D259" s="44"/>
+      <c r="E259" s="44"/>
+      <c r="F259" s="44"/>
+      <c r="G259" s="44"/>
+      <c r="H259" s="44"/>
+      <c r="I259" s="91"/>
+      <c r="J259" s="44"/>
+      <c r="K259" s="44"/>
+      <c r="L259" s="44"/>
       <c r="M259" s="2"/>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -13345,18 +13345,18 @@
       <c r="Z259" s="2"/>
     </row>
     <row r="260" spans="1:26" ht="13.2">
-      <c r="A260" s="46"/>
-      <c r="B260" s="46"/>
-      <c r="C260" s="46"/>
-      <c r="D260" s="46"/>
-      <c r="E260" s="46"/>
-      <c r="F260" s="46"/>
-      <c r="G260" s="46"/>
-      <c r="H260" s="46"/>
-      <c r="I260" s="93"/>
-      <c r="J260" s="46"/>
-      <c r="K260" s="46"/>
-      <c r="L260" s="46"/>
+      <c r="A260" s="44"/>
+      <c r="B260" s="44"/>
+      <c r="C260" s="44"/>
+      <c r="D260" s="44"/>
+      <c r="E260" s="44"/>
+      <c r="F260" s="44"/>
+      <c r="G260" s="44"/>
+      <c r="H260" s="44"/>
+      <c r="I260" s="91"/>
+      <c r="J260" s="44"/>
+      <c r="K260" s="44"/>
+      <c r="L260" s="44"/>
       <c r="M260" s="2"/>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
@@ -32378,6 +32378,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95ECCECB-9519-410C-90A9-A15EB15FC775}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
